--- a/irrigation_truffiere_2026.xlsx
+++ b/irrigation_truffiere_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="1" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Paramètres &amp; ETc" sheetId="1" state="hidden" r:id="rId3"/>
@@ -14,7 +14,8 @@
     <sheet name="Piles" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="La Fontaine" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="La baume" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Modèle saisie" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Bousquet et Riou" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Modèle saisie" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="124">
   <si>
     <t xml:space="preserve">CALENDRIER D'IRRIGATION TRUFFIÈRE — SAISON MAI–SEPTEMBRE 2026</t>
   </si>
@@ -436,7 +437,16 @@
     <t xml:space="preserve">mm</t>
   </si>
   <si>
+    <t xml:space="preserve">TOTAL Juin</t>
+  </si>
+  <si>
     <t xml:space="preserve">Durée d’arrosage (h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligne 1 Bousquet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligne 2 Riou</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1027,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="144">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1422,6 +1432,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1430,10 +1444,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="0" fillId="21" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1463,6 +1473,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="22" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1662,34 +1684,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -3714,11 +3736,13 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" s="101" customFormat="true" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="73"/>
       <c r="B16" s="73"/>
       <c r="C16" s="73"/>
       <c r="D16" s="73"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
       <c r="G16" s="92" t="n">
         <v>46198</v>
       </c>
@@ -3729,11 +3753,15 @@
         <f aca="false">(H16/C2)/10</f>
         <v>17.4216027874564</v>
       </c>
-      <c r="J16" s="95"/>
-      <c r="K16" s="96"/>
+      <c r="J16" s="95" t="n">
+        <v>46202</v>
+      </c>
+      <c r="K16" s="96" t="n">
+        <v>366</v>
+      </c>
       <c r="L16" s="97" t="n">
         <f aca="false">(K16/C3)/10</f>
-        <v>0</v>
+        <v>21.6953171310018</v>
       </c>
       <c r="M16" s="98" t="n">
         <v>46199</v>
@@ -3747,11 +3775,13 @@
         <v>54.6875</v>
       </c>
     </row>
-    <row r="17" s="103" customFormat="true" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="101"/>
-      <c r="B17" s="102"/>
-      <c r="C17" s="102"/>
-      <c r="D17" s="102"/>
+    <row r="17" customFormat="false" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="102"/>
+      <c r="B17" s="103"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="103"/>
+      <c r="E17" s="101"/>
+      <c r="F17" s="101"/>
       <c r="G17" s="104" t="n">
         <v>46200</v>
       </c>
@@ -3774,34 +3804,45 @@
       <c r="B18" s="70"/>
       <c r="C18" s="70"/>
       <c r="D18" s="70"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="105" t="n">
-        <f aca="false">H17</f>
-        <v>474.428571428571</v>
-      </c>
-      <c r="I18" s="94" t="n">
-        <f aca="false">(H18/C2)/10</f>
-        <v>27.5510204081633</v>
-      </c>
-      <c r="J18" s="106"/>
-      <c r="K18" s="107"/>
-      <c r="L18" s="108"/>
-      <c r="M18" s="109"/>
-      <c r="N18" s="110"/>
-      <c r="O18" s="111"/>
+      <c r="G18" s="112" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" s="113" t="n">
+        <f aca="false">SUM(H16:H17)</f>
+        <v>774.428571428571</v>
+      </c>
+      <c r="I18" s="114" t="n">
+        <f aca="false">SUM(I16:I17)</f>
+        <v>44.9726231956197</v>
+      </c>
+      <c r="J18" s="114"/>
+      <c r="K18" s="114" t="n">
+        <f aca="false">SUM(K16:K17)</f>
+        <v>366</v>
+      </c>
+      <c r="L18" s="114" t="n">
+        <f aca="false">SUM(L16:L17)</f>
+        <v>21.6953171310018</v>
+      </c>
+      <c r="M18" s="114"/>
+      <c r="N18" s="114" t="n">
+        <f aca="false">SUM(N16:N17)</f>
+        <v>280</v>
+      </c>
+      <c r="O18" s="114" t="n">
+        <f aca="false">SUM(O16:O17)</f>
+        <v>54.6875</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="70"/>
       <c r="C19" s="70"/>
       <c r="D19" s="70"/>
       <c r="G19" s="104"/>
-      <c r="H19" s="105" t="n">
-        <f aca="false">H18</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H19" s="105"/>
       <c r="I19" s="94" t="n">
         <f aca="false">(H19/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J19" s="106"/>
       <c r="K19" s="107"/>
@@ -3815,13 +3856,10 @@
       <c r="C20" s="70"/>
       <c r="D20" s="70"/>
       <c r="G20" s="104"/>
-      <c r="H20" s="105" t="n">
-        <f aca="false">H19</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H20" s="105"/>
       <c r="I20" s="94" t="n">
         <f aca="false">(H20/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J20" s="106"/>
       <c r="K20" s="107"/>
@@ -3835,13 +3873,10 @@
       <c r="C21" s="70"/>
       <c r="D21" s="70"/>
       <c r="G21" s="104"/>
-      <c r="H21" s="105" t="n">
-        <f aca="false">H20</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H21" s="105"/>
       <c r="I21" s="94" t="n">
         <f aca="false">(H21/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J21" s="106"/>
       <c r="K21" s="107"/>
@@ -3855,13 +3890,10 @@
       <c r="C22" s="70"/>
       <c r="D22" s="70"/>
       <c r="G22" s="104"/>
-      <c r="H22" s="105" t="n">
-        <f aca="false">H21</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H22" s="105"/>
       <c r="I22" s="94" t="n">
         <f aca="false">(H22/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J22" s="106"/>
       <c r="K22" s="107"/>
@@ -3875,13 +3907,10 @@
       <c r="C23" s="70"/>
       <c r="D23" s="70"/>
       <c r="G23" s="104"/>
-      <c r="H23" s="105" t="n">
-        <f aca="false">H22</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H23" s="105"/>
       <c r="I23" s="94" t="n">
         <f aca="false">(H23/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J23" s="106"/>
       <c r="K23" s="107"/>
@@ -3895,13 +3924,10 @@
       <c r="C24" s="70"/>
       <c r="D24" s="70"/>
       <c r="G24" s="104"/>
-      <c r="H24" s="105" t="n">
-        <f aca="false">H23</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H24" s="105"/>
       <c r="I24" s="94" t="n">
         <f aca="false">(H24/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J24" s="106"/>
       <c r="K24" s="107"/>
@@ -3915,13 +3941,10 @@
       <c r="C25" s="70"/>
       <c r="D25" s="70"/>
       <c r="G25" s="104"/>
-      <c r="H25" s="105" t="n">
-        <f aca="false">H24</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H25" s="105"/>
       <c r="I25" s="94" t="n">
         <f aca="false">(H25/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J25" s="106"/>
       <c r="K25" s="107"/>
@@ -3935,13 +3958,10 @@
       <c r="C26" s="70"/>
       <c r="D26" s="70"/>
       <c r="G26" s="104"/>
-      <c r="H26" s="105" t="n">
-        <f aca="false">H25</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H26" s="105"/>
       <c r="I26" s="94" t="n">
         <f aca="false">(H26/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J26" s="106"/>
       <c r="K26" s="107"/>
@@ -3955,13 +3975,10 @@
       <c r="C27" s="70"/>
       <c r="D27" s="70"/>
       <c r="G27" s="104"/>
-      <c r="H27" s="105" t="n">
-        <f aca="false">H26</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H27" s="105"/>
       <c r="I27" s="94" t="n">
         <f aca="false">(H27/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J27" s="106"/>
       <c r="K27" s="107"/>
@@ -3975,13 +3992,10 @@
       <c r="C28" s="70"/>
       <c r="D28" s="70"/>
       <c r="G28" s="104"/>
-      <c r="H28" s="105" t="n">
-        <f aca="false">H27</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H28" s="105"/>
       <c r="I28" s="94" t="n">
         <f aca="false">(H28/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J28" s="106"/>
       <c r="K28" s="107"/>
@@ -3995,13 +4009,10 @@
       <c r="C29" s="70"/>
       <c r="D29" s="70"/>
       <c r="G29" s="104"/>
-      <c r="H29" s="105" t="n">
-        <f aca="false">H28</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H29" s="105"/>
       <c r="I29" s="94" t="n">
         <f aca="false">(H29/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J29" s="106"/>
       <c r="K29" s="107"/>
@@ -4015,13 +4026,10 @@
       <c r="C30" s="70"/>
       <c r="D30" s="70"/>
       <c r="G30" s="104"/>
-      <c r="H30" s="105" t="n">
-        <f aca="false">H29</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H30" s="105"/>
       <c r="I30" s="94" t="n">
         <f aca="false">(H30/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J30" s="106"/>
       <c r="K30" s="107"/>
@@ -4035,13 +4043,10 @@
       <c r="C31" s="70"/>
       <c r="D31" s="70"/>
       <c r="G31" s="104"/>
-      <c r="H31" s="105" t="n">
-        <f aca="false">H30</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H31" s="105"/>
       <c r="I31" s="94" t="n">
         <f aca="false">(H31/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J31" s="106"/>
       <c r="K31" s="107"/>
@@ -4055,13 +4060,10 @@
       <c r="C32" s="70"/>
       <c r="D32" s="70"/>
       <c r="G32" s="104"/>
-      <c r="H32" s="105" t="n">
-        <f aca="false">H31</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H32" s="105"/>
       <c r="I32" s="94" t="n">
         <f aca="false">(H32/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J32" s="106"/>
       <c r="K32" s="107"/>
@@ -4075,13 +4077,10 @@
       <c r="C33" s="70"/>
       <c r="D33" s="70"/>
       <c r="G33" s="104"/>
-      <c r="H33" s="105" t="n">
-        <f aca="false">H32</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H33" s="105"/>
       <c r="I33" s="94" t="n">
         <f aca="false">(H33/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J33" s="106"/>
       <c r="K33" s="107"/>
@@ -4095,13 +4094,10 @@
       <c r="C34" s="70"/>
       <c r="D34" s="70"/>
       <c r="G34" s="104"/>
-      <c r="H34" s="105" t="n">
-        <f aca="false">H33</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H34" s="105"/>
       <c r="I34" s="94" t="n">
         <f aca="false">(H34/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J34" s="106"/>
       <c r="K34" s="107"/>
@@ -4111,17 +4107,14 @@
       <c r="O34" s="111"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="112"/>
-      <c r="C35" s="112"/>
-      <c r="D35" s="112"/>
+      <c r="B35" s="115"/>
+      <c r="C35" s="115"/>
+      <c r="D35" s="115"/>
       <c r="G35" s="104"/>
-      <c r="H35" s="105" t="n">
-        <f aca="false">H34</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H35" s="105"/>
       <c r="I35" s="94" t="n">
         <f aca="false">(H35/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J35" s="106"/>
       <c r="K35" s="107"/>
@@ -4131,17 +4124,14 @@
       <c r="O35" s="111"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="112"/>
-      <c r="C36" s="112"/>
-      <c r="D36" s="112"/>
+      <c r="B36" s="115"/>
+      <c r="C36" s="115"/>
+      <c r="D36" s="115"/>
       <c r="G36" s="104"/>
-      <c r="H36" s="105" t="n">
-        <f aca="false">H35</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H36" s="105"/>
       <c r="I36" s="94" t="n">
         <f aca="false">(H36/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J36" s="106"/>
       <c r="K36" s="107"/>
@@ -4152,13 +4142,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G37" s="104"/>
-      <c r="H37" s="105" t="n">
-        <f aca="false">H36</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H37" s="105"/>
       <c r="I37" s="94" t="n">
         <f aca="false">(H37/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J37" s="106"/>
       <c r="K37" s="107"/>
@@ -4169,13 +4156,10 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G38" s="104"/>
-      <c r="H38" s="105" t="n">
-        <f aca="false">H37</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H38" s="105"/>
       <c r="I38" s="94" t="n">
         <f aca="false">(H38/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J38" s="106"/>
       <c r="K38" s="107"/>
@@ -4186,13 +4170,10 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G39" s="104"/>
-      <c r="H39" s="105" t="n">
-        <f aca="false">H38</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H39" s="105"/>
       <c r="I39" s="94" t="n">
         <f aca="false">(H39/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J39" s="106"/>
       <c r="K39" s="107"/>
@@ -4203,13 +4184,10 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G40" s="104"/>
-      <c r="H40" s="105" t="n">
-        <f aca="false">H39</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H40" s="105"/>
       <c r="I40" s="94" t="n">
         <f aca="false">(H40/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J40" s="106"/>
       <c r="K40" s="107"/>
@@ -4220,13 +4198,10 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G41" s="104"/>
-      <c r="H41" s="105" t="n">
-        <f aca="false">H40</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H41" s="105"/>
       <c r="I41" s="94" t="n">
         <f aca="false">(H41/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J41" s="106"/>
       <c r="K41" s="107"/>
@@ -4237,13 +4212,10 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G42" s="104"/>
-      <c r="H42" s="105" t="n">
-        <f aca="false">H41</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H42" s="105"/>
       <c r="I42" s="94" t="n">
         <f aca="false">(H42/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J42" s="106"/>
       <c r="K42" s="107"/>
@@ -4254,13 +4226,10 @@
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G43" s="104"/>
-      <c r="H43" s="105" t="n">
-        <f aca="false">H42</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H43" s="105"/>
       <c r="I43" s="94" t="n">
         <f aca="false">(H43/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J43" s="106"/>
       <c r="K43" s="107"/>
@@ -4271,13 +4240,10 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G44" s="104"/>
-      <c r="H44" s="105" t="n">
-        <f aca="false">H43</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="H44" s="105"/>
       <c r="I44" s="94" t="n">
         <f aca="false">(H44/C2)/10</f>
-        <v>27.5510204081633</v>
+        <v>0</v>
       </c>
       <c r="J44" s="106"/>
       <c r="K44" s="107"/>
@@ -4287,21 +4253,18 @@
       <c r="O44" s="111"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G45" s="113"/>
-      <c r="H45" s="105" t="n">
-        <f aca="false">H44</f>
-        <v>474.428571428571</v>
-      </c>
+      <c r="G45" s="116"/>
+      <c r="H45" s="105"/>
       <c r="I45" s="94" t="n">
         <f aca="false">(H45/C2)/10</f>
-        <v>27.5510204081633</v>
-      </c>
-      <c r="J45" s="114"/>
-      <c r="K45" s="115"/>
-      <c r="L45" s="116"/>
-      <c r="M45" s="117"/>
-      <c r="N45" s="118"/>
-      <c r="O45" s="119"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="117"/>
+      <c r="K45" s="118"/>
+      <c r="L45" s="119"/>
+      <c r="M45" s="120"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4357,7 +4320,7 @@
         <v>106</v>
       </c>
       <c r="D1" s="74" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E1" s="74" t="s">
         <v>108</v>
@@ -4552,12 +4515,12 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="101"/>
-      <c r="B17" s="102"/>
-      <c r="C17" s="102"/>
-      <c r="D17" s="102"/>
-      <c r="E17" s="103"/>
-      <c r="F17" s="103"/>
+      <c r="A17" s="102"/>
+      <c r="B17" s="103"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="103"/>
+      <c r="E17" s="101"/>
+      <c r="F17" s="101"/>
       <c r="G17" s="92"/>
       <c r="H17" s="105" t="n">
         <f aca="false">E2</f>
@@ -4915,9 +4878,9 @@
       <c r="O34" s="111"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="112"/>
-      <c r="C35" s="112"/>
-      <c r="D35" s="112"/>
+      <c r="B35" s="115"/>
+      <c r="C35" s="115"/>
+      <c r="D35" s="115"/>
       <c r="G35" s="104"/>
       <c r="H35" s="105" t="n">
         <f aca="false">H34</f>
@@ -4935,9 +4898,9 @@
       <c r="O35" s="111"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="112"/>
-      <c r="C36" s="112"/>
-      <c r="D36" s="112"/>
+      <c r="B36" s="115"/>
+      <c r="C36" s="115"/>
+      <c r="D36" s="115"/>
       <c r="G36" s="104"/>
       <c r="H36" s="105" t="n">
         <f aca="false">H35</f>
@@ -5091,7 +5054,7 @@
       <c r="O44" s="111"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G45" s="113"/>
+      <c r="G45" s="116"/>
       <c r="H45" s="105" t="n">
         <f aca="false">H44</f>
         <v>362</v>
@@ -5100,12 +5063,12 @@
         <f aca="false">(H45/C2)/10</f>
         <v>51.7142857142857</v>
       </c>
-      <c r="J45" s="114"/>
-      <c r="K45" s="115"/>
-      <c r="L45" s="116"/>
-      <c r="M45" s="117"/>
-      <c r="N45" s="118"/>
-      <c r="O45" s="119"/>
+      <c r="J45" s="117"/>
+      <c r="K45" s="118"/>
+      <c r="L45" s="119"/>
+      <c r="M45" s="120"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -5134,6 +5097,655 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:L44"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="15.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="16.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="22" width="20.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="22" width="21.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="22" width="16.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="22" width="20.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="70" width="15.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="71" width="14.92"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="9" style="71" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="10" style="72" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="71" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="73"/>
+      <c r="B1" s="74" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="74" t="s">
+        <v>121</v>
+      </c>
+      <c r="E1" s="74" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="74" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="76" t="n">
+        <f aca="false">(E2/C2)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="76" t="n">
+        <f aca="false">(E3/C3)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="73"/>
+      <c r="B7" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" s="73" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="73"/>
+      <c r="E8" s="1" t="e">
+        <f aca="false">E2/D2</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="73"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G12" s="77" t="s">
+        <v>122</v>
+      </c>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="78" t="s">
+        <v>123</v>
+      </c>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G13" s="80" t="s">
+        <v>116</v>
+      </c>
+      <c r="H13" s="81" t="s">
+        <v>117</v>
+      </c>
+      <c r="I13" s="81"/>
+      <c r="J13" s="82" t="s">
+        <v>116</v>
+      </c>
+      <c r="K13" s="83" t="s">
+        <v>117</v>
+      </c>
+      <c r="L13" s="83"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G14" s="80"/>
+      <c r="H14" s="86" t="s">
+        <v>118</v>
+      </c>
+      <c r="I14" s="87" t="s">
+        <v>119</v>
+      </c>
+      <c r="J14" s="82"/>
+      <c r="K14" s="88" t="s">
+        <v>118</v>
+      </c>
+      <c r="L14" s="89" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="73"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="G15" s="92" t="n">
+        <v>46202</v>
+      </c>
+      <c r="H15" s="94" t="n">
+        <f aca="false">E2</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="94" t="n">
+        <f aca="false">F2</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="95"/>
+      <c r="K15" s="96"/>
+      <c r="L15" s="97" t="n">
+        <f aca="false">(K15/C3)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="102"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
+      <c r="E16" s="101"/>
+      <c r="F16" s="101"/>
+      <c r="G16" s="92"/>
+      <c r="H16" s="105" t="n">
+        <f aca="false">E2</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="94" t="n">
+        <f aca="false">(H16/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="106"/>
+      <c r="K16" s="107"/>
+      <c r="L16" s="108"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="70"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="105" t="n">
+        <f aca="false">H16</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="94" t="n">
+        <f aca="false">(H17/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="106"/>
+      <c r="K17" s="107"/>
+      <c r="L17" s="108"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="70"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="105" t="n">
+        <f aca="false">H17</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="94" t="n">
+        <f aca="false">(H18/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="106"/>
+      <c r="K18" s="107"/>
+      <c r="L18" s="108"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="70"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="105" t="n">
+        <f aca="false">H18</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="94" t="n">
+        <f aca="false">(H19/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="106"/>
+      <c r="K19" s="107"/>
+      <c r="L19" s="108"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="70"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="105" t="n">
+        <f aca="false">H19</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="94" t="n">
+        <f aca="false">(H20/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="106"/>
+      <c r="K20" s="107"/>
+      <c r="L20" s="108"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="70"/>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="105" t="n">
+        <f aca="false">H20</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="94" t="n">
+        <f aca="false">(H21/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="106"/>
+      <c r="K21" s="107"/>
+      <c r="L21" s="108"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="70"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="105" t="n">
+        <f aca="false">H21</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="94" t="n">
+        <f aca="false">(H22/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="106"/>
+      <c r="K22" s="107"/>
+      <c r="L22" s="108"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="70"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="105" t="n">
+        <f aca="false">H22</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="94" t="n">
+        <f aca="false">(H23/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="106"/>
+      <c r="K23" s="107"/>
+      <c r="L23" s="108"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="70"/>
+      <c r="C24" s="70"/>
+      <c r="D24" s="70"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="105" t="n">
+        <f aca="false">H23</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="94" t="n">
+        <f aca="false">(H24/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="106"/>
+      <c r="K24" s="107"/>
+      <c r="L24" s="108"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="70"/>
+      <c r="C25" s="70"/>
+      <c r="D25" s="70"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="105" t="n">
+        <f aca="false">H24</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="94" t="n">
+        <f aca="false">(H25/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="106"/>
+      <c r="K25" s="107"/>
+      <c r="L25" s="108"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="70"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="G26" s="104"/>
+      <c r="H26" s="105" t="n">
+        <f aca="false">H25</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="94" t="n">
+        <f aca="false">(H26/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="106"/>
+      <c r="K26" s="107"/>
+      <c r="L26" s="108"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="70"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="G27" s="104"/>
+      <c r="H27" s="105" t="n">
+        <f aca="false">H26</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="94" t="n">
+        <f aca="false">(H27/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="106"/>
+      <c r="K27" s="107"/>
+      <c r="L27" s="108"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="70"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="105" t="n">
+        <f aca="false">H27</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="94" t="n">
+        <f aca="false">(H28/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="106"/>
+      <c r="K28" s="107"/>
+      <c r="L28" s="108"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="70"/>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="105" t="n">
+        <f aca="false">H28</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="94" t="n">
+        <f aca="false">(H29/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="106"/>
+      <c r="K29" s="107"/>
+      <c r="L29" s="108"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="70"/>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="105" t="n">
+        <f aca="false">H29</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="94" t="n">
+        <f aca="false">(H30/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="106"/>
+      <c r="K30" s="107"/>
+      <c r="L30" s="108"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="70"/>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="105" t="n">
+        <f aca="false">H30</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="94" t="n">
+        <f aca="false">(H31/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="106"/>
+      <c r="K31" s="107"/>
+      <c r="L31" s="108"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="70"/>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="105" t="n">
+        <f aca="false">H31</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="94" t="n">
+        <f aca="false">(H32/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="106"/>
+      <c r="K32" s="107"/>
+      <c r="L32" s="108"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="70"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="105" t="n">
+        <f aca="false">H32</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="94" t="n">
+        <f aca="false">(H33/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="106"/>
+      <c r="K33" s="107"/>
+      <c r="L33" s="108"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="115"/>
+      <c r="C34" s="115"/>
+      <c r="D34" s="115"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="105" t="n">
+        <f aca="false">H33</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="94" t="n">
+        <f aca="false">(H34/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="106"/>
+      <c r="K34" s="107"/>
+      <c r="L34" s="108"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="115"/>
+      <c r="C35" s="115"/>
+      <c r="D35" s="115"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="105" t="n">
+        <f aca="false">H34</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="94" t="n">
+        <f aca="false">(H35/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="106"/>
+      <c r="K35" s="107"/>
+      <c r="L35" s="108"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G36" s="104"/>
+      <c r="H36" s="105" t="n">
+        <f aca="false">H35</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="94" t="n">
+        <f aca="false">(H36/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="106"/>
+      <c r="K36" s="107"/>
+      <c r="L36" s="108"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G37" s="104"/>
+      <c r="H37" s="105" t="n">
+        <f aca="false">H36</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="94" t="n">
+        <f aca="false">(H37/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="106"/>
+      <c r="K37" s="107"/>
+      <c r="L37" s="108"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G38" s="104"/>
+      <c r="H38" s="105" t="n">
+        <f aca="false">H37</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="94" t="n">
+        <f aca="false">(H38/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="106"/>
+      <c r="K38" s="107"/>
+      <c r="L38" s="108"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G39" s="104"/>
+      <c r="H39" s="105" t="n">
+        <f aca="false">H38</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="94" t="n">
+        <f aca="false">(H39/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="106"/>
+      <c r="K39" s="107"/>
+      <c r="L39" s="108"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G40" s="104"/>
+      <c r="H40" s="105" t="n">
+        <f aca="false">H39</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="94" t="n">
+        <f aca="false">(H40/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="106"/>
+      <c r="K40" s="107"/>
+      <c r="L40" s="108"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G41" s="104"/>
+      <c r="H41" s="105" t="n">
+        <f aca="false">H40</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="94" t="n">
+        <f aca="false">(H41/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="106"/>
+      <c r="K41" s="107"/>
+      <c r="L41" s="108"/>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G42" s="104"/>
+      <c r="H42" s="105" t="n">
+        <f aca="false">H41</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="94" t="n">
+        <f aca="false">(H42/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="106"/>
+      <c r="K42" s="107"/>
+      <c r="L42" s="108"/>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G43" s="104"/>
+      <c r="H43" s="105" t="n">
+        <f aca="false">H42</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="94" t="n">
+        <f aca="false">(H43/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="106"/>
+      <c r="K43" s="107"/>
+      <c r="L43" s="108"/>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G44" s="116"/>
+      <c r="H44" s="105" t="n">
+        <f aca="false">H43</f>
+        <v>0</v>
+      </c>
+      <c r="I44" s="94" t="n">
+        <f aca="false">(H44/C2)/10</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="117"/>
+      <c r="K44" s="118"/>
+      <c r="L44" s="119"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:L13"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B1:J34"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
@@ -5202,334 +5814,334 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="120"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="122"/>
-      <c r="F5" s="123"/>
-      <c r="G5" s="123"/>
-      <c r="H5" s="124"/>
-      <c r="I5" s="125"/>
-      <c r="J5" s="126"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="127"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="129"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="127"/>
-      <c r="C6" s="128"/>
-      <c r="D6" s="128"/>
-      <c r="E6" s="129"/>
-      <c r="F6" s="130"/>
-      <c r="G6" s="130"/>
-      <c r="H6" s="131"/>
-      <c r="I6" s="132"/>
-      <c r="J6" s="133"/>
+      <c r="B6" s="130"/>
+      <c r="C6" s="131"/>
+      <c r="D6" s="131"/>
+      <c r="E6" s="132"/>
+      <c r="F6" s="133"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="134"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="136"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="127"/>
-      <c r="C7" s="128"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="133"/>
+      <c r="B7" s="130"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="133"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="135"/>
+      <c r="J7" s="136"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="127"/>
-      <c r="C8" s="128"/>
-      <c r="D8" s="128"/>
-      <c r="E8" s="129"/>
-      <c r="F8" s="130"/>
-      <c r="G8" s="130"/>
-      <c r="H8" s="131"/>
-      <c r="I8" s="132"/>
-      <c r="J8" s="133"/>
+      <c r="B8" s="130"/>
+      <c r="C8" s="131"/>
+      <c r="D8" s="131"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="134"/>
+      <c r="I8" s="135"/>
+      <c r="J8" s="136"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="127"/>
-      <c r="C9" s="128"/>
-      <c r="D9" s="128"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="130"/>
-      <c r="G9" s="130"/>
-      <c r="H9" s="131"/>
-      <c r="I9" s="132"/>
-      <c r="J9" s="133"/>
+      <c r="B9" s="130"/>
+      <c r="C9" s="131"/>
+      <c r="D9" s="131"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="134"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="136"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="127"/>
-      <c r="C10" s="128"/>
-      <c r="D10" s="128"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="130"/>
-      <c r="G10" s="130"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="132"/>
-      <c r="J10" s="133"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="131"/>
+      <c r="D10" s="131"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
+      <c r="H10" s="134"/>
+      <c r="I10" s="135"/>
+      <c r="J10" s="136"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="127"/>
-      <c r="C11" s="128"/>
-      <c r="D11" s="128"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="130"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="131"/>
-      <c r="I11" s="132"/>
-      <c r="J11" s="133"/>
+      <c r="B11" s="130"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="133"/>
+      <c r="G11" s="133"/>
+      <c r="H11" s="134"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="136"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="127"/>
-      <c r="C12" s="128"/>
-      <c r="D12" s="128"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="132"/>
-      <c r="J12" s="133"/>
+      <c r="B12" s="130"/>
+      <c r="C12" s="131"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="133"/>
+      <c r="H12" s="134"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="136"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="127"/>
-      <c r="C13" s="128"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="131"/>
-      <c r="I13" s="132"/>
-      <c r="J13" s="133"/>
+      <c r="B13" s="130"/>
+      <c r="C13" s="131"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="133"/>
+      <c r="H13" s="134"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="136"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="127"/>
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="130"/>
-      <c r="G14" s="130"/>
-      <c r="H14" s="131"/>
-      <c r="I14" s="132"/>
-      <c r="J14" s="133"/>
+      <c r="B14" s="130"/>
+      <c r="C14" s="131"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="133"/>
+      <c r="H14" s="134"/>
+      <c r="I14" s="135"/>
+      <c r="J14" s="136"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="127"/>
-      <c r="C15" s="128"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="130"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="131"/>
-      <c r="I15" s="132"/>
-      <c r="J15" s="133"/>
+      <c r="B15" s="130"/>
+      <c r="C15" s="131"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="134"/>
+      <c r="I15" s="135"/>
+      <c r="J15" s="136"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="127"/>
-      <c r="C16" s="128"/>
-      <c r="D16" s="128"/>
-      <c r="E16" s="129"/>
-      <c r="F16" s="130"/>
-      <c r="G16" s="130"/>
-      <c r="H16" s="131"/>
-      <c r="I16" s="132"/>
-      <c r="J16" s="133"/>
+      <c r="B16" s="130"/>
+      <c r="C16" s="131"/>
+      <c r="D16" s="131"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="133"/>
+      <c r="G16" s="133"/>
+      <c r="H16" s="134"/>
+      <c r="I16" s="135"/>
+      <c r="J16" s="136"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="127"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="128"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="130"/>
-      <c r="G17" s="130"/>
-      <c r="H17" s="131"/>
-      <c r="I17" s="132"/>
-      <c r="J17" s="133"/>
+      <c r="B17" s="130"/>
+      <c r="C17" s="131"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="133"/>
+      <c r="G17" s="133"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="135"/>
+      <c r="J17" s="136"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="127"/>
-      <c r="C18" s="128"/>
-      <c r="D18" s="128"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="130"/>
-      <c r="G18" s="130"/>
-      <c r="H18" s="131"/>
-      <c r="I18" s="132"/>
-      <c r="J18" s="133"/>
+      <c r="B18" s="130"/>
+      <c r="C18" s="131"/>
+      <c r="D18" s="131"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="133"/>
+      <c r="H18" s="134"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="136"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="127"/>
-      <c r="C19" s="128"/>
-      <c r="D19" s="128"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="130"/>
-      <c r="G19" s="130"/>
-      <c r="H19" s="131"/>
-      <c r="I19" s="132"/>
-      <c r="J19" s="133"/>
+      <c r="B19" s="130"/>
+      <c r="C19" s="131"/>
+      <c r="D19" s="131"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="134"/>
+      <c r="I19" s="135"/>
+      <c r="J19" s="136"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="127"/>
-      <c r="C20" s="128"/>
-      <c r="D20" s="128"/>
-      <c r="E20" s="129"/>
-      <c r="F20" s="130"/>
-      <c r="G20" s="130"/>
-      <c r="H20" s="131"/>
-      <c r="I20" s="132"/>
-      <c r="J20" s="133"/>
+      <c r="B20" s="130"/>
+      <c r="C20" s="131"/>
+      <c r="D20" s="131"/>
+      <c r="E20" s="132"/>
+      <c r="F20" s="133"/>
+      <c r="G20" s="133"/>
+      <c r="H20" s="134"/>
+      <c r="I20" s="135"/>
+      <c r="J20" s="136"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="127"/>
-      <c r="C21" s="128"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="130"/>
-      <c r="G21" s="130"/>
-      <c r="H21" s="131"/>
-      <c r="I21" s="132"/>
-      <c r="J21" s="133"/>
+      <c r="B21" s="130"/>
+      <c r="C21" s="131"/>
+      <c r="D21" s="131"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="134"/>
+      <c r="I21" s="135"/>
+      <c r="J21" s="136"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="127"/>
-      <c r="C22" s="128"/>
-      <c r="D22" s="128"/>
-      <c r="E22" s="129"/>
-      <c r="F22" s="130"/>
-      <c r="G22" s="130"/>
-      <c r="H22" s="131"/>
-      <c r="I22" s="132"/>
-      <c r="J22" s="133"/>
+      <c r="B22" s="130"/>
+      <c r="C22" s="131"/>
+      <c r="D22" s="131"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="134"/>
+      <c r="I22" s="135"/>
+      <c r="J22" s="136"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="127"/>
-      <c r="C23" s="128"/>
-      <c r="D23" s="128"/>
-      <c r="E23" s="129"/>
-      <c r="F23" s="130"/>
-      <c r="G23" s="130"/>
-      <c r="H23" s="131"/>
-      <c r="I23" s="132"/>
-      <c r="J23" s="133"/>
+      <c r="B23" s="130"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="131"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="134"/>
+      <c r="I23" s="135"/>
+      <c r="J23" s="136"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="127"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="128"/>
-      <c r="E24" s="129"/>
-      <c r="F24" s="130"/>
-      <c r="G24" s="130"/>
-      <c r="H24" s="131"/>
-      <c r="I24" s="132"/>
-      <c r="J24" s="133"/>
+      <c r="B24" s="130"/>
+      <c r="C24" s="131"/>
+      <c r="D24" s="131"/>
+      <c r="E24" s="132"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="134"/>
+      <c r="I24" s="135"/>
+      <c r="J24" s="136"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="127"/>
-      <c r="C25" s="128"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="129"/>
-      <c r="F25" s="130"/>
-      <c r="G25" s="130"/>
-      <c r="H25" s="131"/>
-      <c r="I25" s="132"/>
-      <c r="J25" s="133"/>
+      <c r="B25" s="130"/>
+      <c r="C25" s="131"/>
+      <c r="D25" s="131"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="133"/>
+      <c r="H25" s="134"/>
+      <c r="I25" s="135"/>
+      <c r="J25" s="136"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="127"/>
-      <c r="C26" s="128"/>
-      <c r="D26" s="128"/>
-      <c r="E26" s="129"/>
-      <c r="F26" s="130"/>
-      <c r="G26" s="130"/>
-      <c r="H26" s="131"/>
-      <c r="I26" s="132"/>
-      <c r="J26" s="133"/>
+      <c r="B26" s="130"/>
+      <c r="C26" s="131"/>
+      <c r="D26" s="131"/>
+      <c r="E26" s="132"/>
+      <c r="F26" s="133"/>
+      <c r="G26" s="133"/>
+      <c r="H26" s="134"/>
+      <c r="I26" s="135"/>
+      <c r="J26" s="136"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="127"/>
-      <c r="C27" s="128"/>
-      <c r="D27" s="128"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="130"/>
-      <c r="G27" s="130"/>
-      <c r="H27" s="131"/>
-      <c r="I27" s="132"/>
-      <c r="J27" s="133"/>
+      <c r="B27" s="130"/>
+      <c r="C27" s="131"/>
+      <c r="D27" s="131"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="134"/>
+      <c r="I27" s="135"/>
+      <c r="J27" s="136"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="127"/>
-      <c r="C28" s="128"/>
-      <c r="D28" s="128"/>
-      <c r="E28" s="129"/>
-      <c r="F28" s="130"/>
-      <c r="G28" s="130"/>
-      <c r="H28" s="131"/>
-      <c r="I28" s="132"/>
-      <c r="J28" s="133"/>
+      <c r="B28" s="130"/>
+      <c r="C28" s="131"/>
+      <c r="D28" s="131"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="133"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="134"/>
+      <c r="I28" s="135"/>
+      <c r="J28" s="136"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="127"/>
-      <c r="C29" s="128"/>
-      <c r="D29" s="128"/>
-      <c r="E29" s="129"/>
-      <c r="F29" s="130"/>
-      <c r="G29" s="130"/>
-      <c r="H29" s="131"/>
-      <c r="I29" s="132"/>
-      <c r="J29" s="133"/>
+      <c r="B29" s="130"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="131"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="133"/>
+      <c r="G29" s="133"/>
+      <c r="H29" s="134"/>
+      <c r="I29" s="135"/>
+      <c r="J29" s="136"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="127"/>
-      <c r="C30" s="128"/>
-      <c r="D30" s="128"/>
-      <c r="E30" s="129"/>
-      <c r="F30" s="130"/>
-      <c r="G30" s="130"/>
-      <c r="H30" s="131"/>
-      <c r="I30" s="132"/>
-      <c r="J30" s="133"/>
+      <c r="B30" s="130"/>
+      <c r="C30" s="131"/>
+      <c r="D30" s="131"/>
+      <c r="E30" s="132"/>
+      <c r="F30" s="133"/>
+      <c r="G30" s="133"/>
+      <c r="H30" s="134"/>
+      <c r="I30" s="135"/>
+      <c r="J30" s="136"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="127"/>
-      <c r="C31" s="128"/>
-      <c r="D31" s="128"/>
-      <c r="E31" s="129"/>
-      <c r="F31" s="130"/>
-      <c r="G31" s="130"/>
-      <c r="H31" s="131"/>
-      <c r="I31" s="132"/>
-      <c r="J31" s="133"/>
+      <c r="B31" s="130"/>
+      <c r="C31" s="131"/>
+      <c r="D31" s="131"/>
+      <c r="E31" s="132"/>
+      <c r="F31" s="133"/>
+      <c r="G31" s="133"/>
+      <c r="H31" s="134"/>
+      <c r="I31" s="135"/>
+      <c r="J31" s="136"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="127"/>
-      <c r="C32" s="128"/>
-      <c r="D32" s="128"/>
-      <c r="E32" s="129"/>
-      <c r="F32" s="130"/>
-      <c r="G32" s="130"/>
-      <c r="H32" s="131"/>
-      <c r="I32" s="132"/>
-      <c r="J32" s="133"/>
+      <c r="B32" s="130"/>
+      <c r="C32" s="131"/>
+      <c r="D32" s="131"/>
+      <c r="E32" s="132"/>
+      <c r="F32" s="133"/>
+      <c r="G32" s="133"/>
+      <c r="H32" s="134"/>
+      <c r="I32" s="135"/>
+      <c r="J32" s="136"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="127"/>
-      <c r="C33" s="128"/>
-      <c r="D33" s="128"/>
-      <c r="E33" s="129"/>
-      <c r="F33" s="130"/>
-      <c r="G33" s="130"/>
-      <c r="H33" s="131"/>
-      <c r="I33" s="132"/>
-      <c r="J33" s="133"/>
+      <c r="B33" s="130"/>
+      <c r="C33" s="131"/>
+      <c r="D33" s="131"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="133"/>
+      <c r="G33" s="133"/>
+      <c r="H33" s="134"/>
+      <c r="I33" s="135"/>
+      <c r="J33" s="136"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="134"/>
-      <c r="C34" s="135"/>
-      <c r="D34" s="135"/>
-      <c r="E34" s="136"/>
-      <c r="F34" s="137"/>
-      <c r="G34" s="137"/>
-      <c r="H34" s="138"/>
-      <c r="I34" s="139"/>
-      <c r="J34" s="140"/>
+      <c r="B34" s="137"/>
+      <c r="C34" s="138"/>
+      <c r="D34" s="138"/>
+      <c r="E34" s="139"/>
+      <c r="F34" s="140"/>
+      <c r="G34" s="140"/>
+      <c r="H34" s="141"/>
+      <c r="I34" s="142"/>
+      <c r="J34" s="143"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/irrigation_truffiere_2026.xlsx
+++ b/irrigation_truffiere_2026.xlsx
@@ -5,17 +5,17 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="1" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Paramètres &amp; ETc" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Seuils pF WETRUF" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Ajustements pluie" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Piles" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Modèle" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="La Fontaine" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="La baume" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Bousquet et Riou" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Modèle saisie" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Pilles" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Bousquet et Riou" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="130">
   <si>
     <t xml:space="preserve">CALENDRIER D'IRRIGATION TRUFFIÈRE — SAISON MAI–SEPTEMBRE 2026</t>
   </si>
@@ -321,6 +321,12 @@
   </si>
   <si>
     <t xml:space="preserve">Formule saisie en colonne F (pluie réelle) du tableau ETc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellules calculées en priorité avec la pluie réelle (si non renseigné, utilise la pluie moy.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Besoins de plante, sans pluie</t>
   </si>
   <si>
     <t xml:space="preserve">Durée arrosage pour les 5 ah (100 m3/h)
@@ -392,76 +398,89 @@
     <t xml:space="preserve">Ligne 3</t>
   </si>
   <si>
+    <t xml:space="preserve">Surface couverte (ha)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Longueur (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">Surface couverte (ha)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temps de parcours (h)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volume d’eau (m³)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hauteur d’eau (mm)</t>
+    <t xml:space="preserve">Vitesse de l’enrouleur (m/h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durée (h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compteur début</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compteur fin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Débit (m3/h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume apporté</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL Juin</t>
   </si>
   <si>
     <t xml:space="preserve">Envergure jet (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">Vitesse (m/h)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pression (bar)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Débit (m3/h)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Grand enrouleur</t>
   </si>
   <si>
     <t xml:space="preserve">Petit enrouleur</t>
   </si>
   <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volume apporté</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL Juin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Durée d’arrosage (h)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ligne 1 Bousquet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ligne 2 Riou</t>
+    <t xml:space="preserve">Ligne 1 (grande parcelle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligne 2 (sud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligne 3 (petite parcelle en bas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligne 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligne 2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligne 3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligne 1 (Bousquet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligne 2 (Riou)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
     <numFmt numFmtId="167" formatCode="d\ mmm\ yy"/>
     <numFmt numFmtId="168" formatCode="d\ mmm\ yyyy"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="#.00"/>
+    <numFmt numFmtId="170" formatCode="#"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -642,11 +661,26 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="23">
@@ -736,6 +770,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAFD095"/>
+        <bgColor rgb="FFCCCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
@@ -760,8 +800,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAFD095"/>
-        <bgColor rgb="FFAAAAAA"/>
+        <fgColor rgb="FFFFDBB6"/>
+        <bgColor rgb="FFFFDDB0"/>
       </patternFill>
     </fill>
     <fill>
@@ -772,18 +812,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFDBB6"/>
-        <bgColor rgb="FFFFDDB0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDE8CB"/>
         <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="18">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -862,19 +896,19 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="hair"/>
-      <right style="hair"/>
-      <top style="thin"/>
-      <bottom style="hair"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="hair">
         <color rgb="FF808080"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="thin"/>
+      <bottom style="hair"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -885,42 +919,6 @@
         <color rgb="FF808080"/>
       </right>
       <top style="thin"/>
-      <bottom style="hair">
-        <color rgb="FF808080"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="hair">
-        <color rgb="FF808080"/>
-      </left>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="hair">
-        <color rgb="FF808080"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="hair"/>
-      <bottom style="hair"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="hair"/>
-      <right style="hair"/>
-      <top style="hair"/>
-      <bottom style="hair"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="hair">
-        <color rgb="FF808080"/>
-      </top>
       <bottom style="hair">
         <color rgb="FF808080"/>
       </bottom>
@@ -942,9 +940,14 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="hair">
-        <color rgb="FF808080"/>
-      </left>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
       <right style="thin"/>
       <top style="hair">
         <color rgb="FF808080"/>
@@ -955,10 +958,10 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
+      <left style="hair"/>
+      <right style="hair"/>
       <top style="hair"/>
-      <bottom style="thin"/>
+      <bottom style="hair"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -983,24 +986,6 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="hair">
-        <color rgb="FF808080"/>
-      </left>
-      <right style="thin"/>
-      <top style="hair">
-        <color rgb="FF808080"/>
-      </top>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="hair"/>
-      <right style="hair"/>
-      <top style="hair"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1027,7 +1012,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="169">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1248,6 +1233,14 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1256,11 +1249,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="15" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="13" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1272,7 +1269,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="22" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1296,15 +1293,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="19" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1320,83 +1309,135 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="24" fillId="18" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="24" fillId="19" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="24" fillId="15" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="20" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="18" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="19" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="15" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="18" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="19" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="15" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="18" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="15" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="20" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="20" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="20" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="21" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="22" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="22" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="22" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="20" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="20" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="21" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="21" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="22" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="22" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="20" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="20" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="17" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="18" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="19" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="21" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="20" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="20" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="22" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="22" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="21" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="21" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="20" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="20" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="22" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="22" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="21" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="20" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="20" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="20" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="21" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1404,27 +1445,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="21" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="21" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="20" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="21" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="20" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="21" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="20" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="22" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="22" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="22" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="22" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="22" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="22" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1432,27 +1477,151 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="21" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="20" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="21" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="20" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="20" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="20" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="20" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="21" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="21" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="21" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="21" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="21" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="22" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="22" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="22" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="22" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="16" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="16" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="16" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="20" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="20" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="20" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="20" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="21" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="21" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="21" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="22" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="22" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="22" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="20" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="20" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1460,11 +1629,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="20" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="20" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="22" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="20" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="21" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="21" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="21" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="21" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="22" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1472,136 +1661,32 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="22" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="22" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="22" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="19" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="21" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="21" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="20" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="20" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="20" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="22" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="22" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="22" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="21" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="21" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="20" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="20" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="22" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="22" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="22" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="21" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="21" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="20" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="20" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="22" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="22" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="22" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="21" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="21" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="20" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="20" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="22" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="22" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="22" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1622,14 +1707,14 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FFDEE6EF"/>
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FFDDE8CB"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFAFD095"/>
+      <rgbColor rgb="FFCCCCCC"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FFAAAAFF"/>
       <rgbColor rgb="FF993366"/>
@@ -1657,14 +1742,14 @@
       <rgbColor rgb="FFFFCC80"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF729FCF"/>
-      <rgbColor rgb="FFDDE8CB"/>
+      <rgbColor rgb="FFAFD095"/>
       <rgbColor rgb="FFFFDDB0"/>
       <rgbColor rgb="FFFF8000"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF555555"/>
       <rgbColor rgb="FF888888"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FFDEE6EF"/>
+      <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -2669,20 +2754,20 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="3" min="3" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="8" min="8" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="9" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13.81"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="11" min="11" style="1" width="13"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="12" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="22" width="14.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="22" width="7.78"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="16" min="16" style="22" width="14.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="22" width="4.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="22" width="32.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="22" width="32.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="22" width="11.53"/>
@@ -2873,8 +2958,12 @@
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
       <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
+      <c r="G9" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="55"/>
       <c r="N9" s="53" t="s">
         <v>87</v>
       </c>
@@ -2891,10 +2980,14 @@
       <c r="A10" s="22"/>
       <c r="B10" s="22"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
+      <c r="D10" s="56" t="s">
+        <v>94</v>
+      </c>
       <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="55"/>
       <c r="N10" s="53" t="s">
         <v>90</v>
       </c>
@@ -2907,7 +3000,13 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="24.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="24.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D11" s="56"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="55"/>
+    </row>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
         <v>19</v>
@@ -2946,21 +3045,21 @@
         <v>29</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="O12" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="P12" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="Q12" s="56" t="s">
+      <c r="O12" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="R12" s="56"/>
+      <c r="P12" s="58" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q12" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="R12" s="58"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
@@ -2973,59 +3072,61 @@
         <f aca="false">$B$5</f>
         <v>0.65</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="59" t="n">
         <f aca="false">ROUND($B$5*B13,0)</f>
         <v>59</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="F13" s="15"/>
+      <c r="F13" s="15" t="n">
+        <v>115</v>
+      </c>
       <c r="G13" s="16" t="n">
         <f aca="false">MAX(0,D13-IF(F13="",E13,F13))</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H13" s="14" t="n">
         <f aca="false">G13*10</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I13" s="14" t="n">
         <f aca="false">IFERROR(H13/$B$6,0)</f>
-        <v>128.205128205128</v>
+        <v>0</v>
       </c>
       <c r="J13" s="16" t="n">
         <f aca="false">I13*$B$7</f>
-        <v>641.025641025641</v>
+        <v>0</v>
       </c>
       <c r="K13" s="14" t="n">
         <f aca="false">IFERROR(IF(N13=0,"—",G13/N13),0)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L13" s="14" t="n">
         <f aca="false">IFERROR(IF(N13=0,"—",K13/$B$6),"—")</f>
-        <v>12.8205128205128</v>
+        <v>0</v>
       </c>
       <c r="M13" s="17" t="n">
         <f aca="false">P13*Q13</f>
-        <v>2.13675213675214</v>
+        <v>0</v>
       </c>
       <c r="N13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O13" s="57" t="n">
+      <c r="O13" s="60" t="n">
         <f aca="false">J13/3</f>
-        <v>213.675213675214</v>
-      </c>
-      <c r="P13" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="61" t="n">
         <f aca="false">(O13/100)/N13</f>
-        <v>2.13675213675214</v>
-      </c>
-      <c r="Q13" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="62" t="n">
         <f aca="false">N13</f>
         <v>1</v>
       </c>
-      <c r="R13" s="60" t="s">
-        <v>98</v>
+      <c r="R13" s="63" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3039,59 +3140,61 @@
         <f aca="false">$B$5</f>
         <v>0.65</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="59" t="n">
         <f aca="false">ROUND($B$5*B14,0)</f>
         <v>78</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="F14" s="15"/>
+      <c r="F14" s="15" t="n">
+        <v>21</v>
+      </c>
       <c r="G14" s="16" t="n">
         <f aca="false">MAX(0,D14-IF(F14="",E14,F14))</f>
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="H14" s="14" t="n">
         <f aca="false">G14*10</f>
-        <v>390</v>
+        <v>570</v>
       </c>
       <c r="I14" s="14" t="n">
         <f aca="false">IFERROR(H14/$B$6,0)</f>
-        <v>500</v>
+        <v>730.769230769231</v>
       </c>
       <c r="J14" s="16" t="n">
         <f aca="false">I14*$B$7</f>
-        <v>2500</v>
+        <v>3653.84615384615</v>
       </c>
       <c r="K14" s="14" t="n">
         <f aca="false">IFERROR(IF(N14=0,"—",G14/N14),0)</f>
-        <v>19.5</v>
+        <v>28.5</v>
       </c>
       <c r="L14" s="14" t="n">
         <f aca="false">IFERROR(IF(N14=0,"—",K14/$B$6),"—")</f>
-        <v>25</v>
+        <v>36.5384615384615</v>
       </c>
       <c r="M14" s="17" t="n">
         <f aca="false">P14*Q14</f>
-        <v>8.33333333333333</v>
+        <v>12.1794871794872</v>
       </c>
       <c r="N14" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="O14" s="57" t="n">
+      <c r="O14" s="60" t="n">
         <f aca="false">J14/3</f>
-        <v>833.333333333333</v>
-      </c>
-      <c r="P14" s="58" t="n">
+        <v>1217.94871794872</v>
+      </c>
+      <c r="P14" s="61" t="n">
         <f aca="false">(O14/100)/N14</f>
-        <v>4.16666666666667</v>
-      </c>
-      <c r="Q14" s="59" t="n">
+        <v>6.08974358974359</v>
+      </c>
+      <c r="Q14" s="62" t="n">
         <f aca="false">N14</f>
         <v>2</v>
       </c>
-      <c r="R14" s="60" t="s">
-        <v>99</v>
+      <c r="R14" s="63" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3105,7 +3208,7 @@
         <f aca="false">$B$5</f>
         <v>0.65</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="59" t="n">
         <f aca="false">ROUND($B$5*B15,0)</f>
         <v>94</v>
       </c>
@@ -3144,20 +3247,20 @@
       <c r="N15" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="O15" s="57" t="n">
+      <c r="O15" s="60" t="n">
         <f aca="false">J15/3</f>
         <v>1495.7264957265</v>
       </c>
-      <c r="P15" s="58" t="n">
+      <c r="P15" s="61" t="n">
         <f aca="false">(O15/100)/N15</f>
         <v>3.73931623931624</v>
       </c>
-      <c r="Q15" s="59" t="n">
+      <c r="Q15" s="62" t="n">
         <f aca="false">N15</f>
         <v>4</v>
       </c>
-      <c r="R15" s="60" t="s">
-        <v>100</v>
+      <c r="R15" s="63" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3171,7 +3274,7 @@
         <f aca="false">$B$5</f>
         <v>0.65</v>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="59" t="n">
         <f aca="false">ROUND($B$5*B16,0)</f>
         <v>85</v>
       </c>
@@ -3210,20 +3313,20 @@
       <c r="N16" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="O16" s="57" t="n">
+      <c r="O16" s="60" t="n">
         <f aca="false">J16/3</f>
         <v>833.333333333333</v>
       </c>
-      <c r="P16" s="58" t="n">
+      <c r="P16" s="61" t="n">
         <f aca="false">(O16/100)/N16</f>
         <v>2.08333333333333</v>
       </c>
-      <c r="Q16" s="59" t="n">
+      <c r="Q16" s="62" t="n">
         <f aca="false">N16</f>
         <v>4</v>
       </c>
-      <c r="R16" s="60" t="s">
-        <v>101</v>
+      <c r="R16" s="63" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3237,7 +3340,7 @@
         <f aca="false">$B$5</f>
         <v>0.65</v>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="59" t="n">
         <f aca="false">ROUND($B$5*B17,0)</f>
         <v>55</v>
       </c>
@@ -3276,18 +3379,18 @@
       <c r="N17" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="57" t="n">
+      <c r="O17" s="60" t="n">
         <f aca="false">J17/3</f>
         <v>0</v>
       </c>
-      <c r="P17" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="59" t="n">
+      <c r="P17" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="62" t="n">
         <f aca="false">N17</f>
         <v>0</v>
       </c>
-      <c r="R17" s="62"/>
+      <c r="R17" s="65"/>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
@@ -3313,19 +3416,19 @@
       </c>
       <c r="G18" s="19" t="n">
         <f aca="false">SUM(G13:G17)</f>
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H18" s="19" t="n">
         <f aca="false">SUM(H13:H17)</f>
-        <v>1580</v>
+        <v>1660</v>
       </c>
       <c r="I18" s="19" t="n">
         <f aca="false">SUM(I13:I17)</f>
-        <v>2025.64102564103</v>
+        <v>2128.20512820513</v>
       </c>
       <c r="J18" s="19" t="n">
         <f aca="false">SUM(J13:J17)</f>
-        <v>10128.2051282051</v>
+        <v>10641.0256410256</v>
       </c>
       <c r="K18" s="19" t="s">
         <v>40</v>
@@ -3341,33 +3444,33 @@
       </c>
       <c r="O18" s="19" t="n">
         <f aca="false">SUM(O13:O17)</f>
-        <v>3376.06837606838</v>
-      </c>
-      <c r="P18" s="63"/>
-      <c r="Q18" s="64"/>
-      <c r="R18" s="65"/>
+        <v>3547.00854700855</v>
+      </c>
+      <c r="P18" s="66"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="68"/>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="66" t="s">
+      <c r="A19" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="66"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="66"/>
-      <c r="O19" s="66"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="66"/>
-      <c r="R19" s="66"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="69"/>
+      <c r="L19" s="69"/>
+      <c r="M19" s="69"/>
+      <c r="N19" s="69"/>
+      <c r="O19" s="69"/>
+      <c r="P19" s="69"/>
+      <c r="Q19" s="69"/>
+      <c r="R19" s="69"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="22"/>
@@ -3381,107 +3484,101 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="22"/>
-      <c r="B24" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="D24" s="69" t="s">
-        <v>104</v>
-      </c>
+      <c r="B24" s="70"/>
+      <c r="C24" s="70"/>
+      <c r="D24" s="70"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="22"/>
-      <c r="B25" s="70"/>
-      <c r="C25" s="70"/>
-      <c r="D25" s="70"/>
+      <c r="B25" s="71"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="22"/>
-      <c r="B26" s="70"/>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
+      <c r="B26" s="71"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="22"/>
-      <c r="B27" s="70"/>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
+      <c r="B27" s="71"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="22"/>
-      <c r="B28" s="70"/>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
+      <c r="B28" s="71"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="70"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="70"/>
+      <c r="B29" s="71"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="70"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
+      <c r="B30" s="71"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="70"/>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
+      <c r="B31" s="71"/>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="70"/>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
+      <c r="B32" s="71"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="70"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
+      <c r="B33" s="71"/>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="70"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
+      <c r="B34" s="71"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="70"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="70"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="70"/>
-      <c r="C36" s="70"/>
-      <c r="D36" s="70"/>
+      <c r="B36" s="71"/>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="70"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="70"/>
+      <c r="B37" s="71"/>
+      <c r="C37" s="71"/>
+      <c r="D37" s="71"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="70"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
+      <c r="B38" s="71"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="70"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="70"/>
+      <c r="B39" s="71"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="70"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
+      <c r="B41" s="71"/>
+      <c r="C41" s="71"/>
+      <c r="D41" s="71"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="20">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A3:C3"/>
@@ -3494,8 +3591,10 @@
     <mergeCell ref="P7:Q7"/>
     <mergeCell ref="N8:O8"/>
     <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="G9:J11"/>
     <mergeCell ref="N9:O9"/>
     <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="D10:D11"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="Q12:R12"/>
@@ -3514,769 +3613,1534 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFDDDDDD"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:V41"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="15.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="16.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="22" width="20.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="22" width="21.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="22" width="16.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="22" width="20.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="70" width="15.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="71" width="14.92"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="9" style="71" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="10" style="72" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="71" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="13" style="72" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="14" style="71" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="72" width="24.64"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="72" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="3" style="73" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="8" style="72" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="73"/>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="74" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="75" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
+      <c r="V1" s="76"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="77" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="74" t="s">
+      <c r="B2" s="78" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="79" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="79"/>
+      <c r="P2" s="80" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="77" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="74" t="s">
+      <c r="B3" s="81" t="n">
+        <v>246</v>
+      </c>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="82" t="n">
+        <v>241</v>
+      </c>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="83" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="83"/>
+      <c r="S3" s="83"/>
+      <c r="T3" s="83"/>
+      <c r="U3" s="83"/>
+      <c r="V3" s="83"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="77" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="71" t="n">
-        <v>246</v>
-      </c>
-      <c r="C2" s="71" t="n">
-        <f aca="false">(B9*B2)/10000</f>
-        <v>1.722</v>
-      </c>
-      <c r="D2" s="75" t="n">
-        <f aca="false">B2/C9</f>
-        <v>17.5714285714286</v>
-      </c>
-      <c r="E2" s="75" t="n">
-        <f aca="false">E9*D2</f>
-        <v>474.428571428571</v>
-      </c>
-      <c r="F2" s="76" t="n">
-        <f aca="false">(E2/C2)/10</f>
-        <v>27.5510204081633</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3" s="71" t="n">
-        <v>241</v>
-      </c>
-      <c r="C3" s="71" t="n">
-        <f aca="false">(B9*B3)/10000</f>
-        <v>1.687</v>
-      </c>
-      <c r="D3" s="75" t="n">
-        <f aca="false">B3/C9</f>
-        <v>17.2142857142857</v>
-      </c>
-      <c r="E3" s="75" t="n">
-        <f aca="false">E9*D3</f>
-        <v>464.785714285714</v>
-      </c>
-      <c r="F3" s="76" t="n">
-        <f aca="false">(E3/C3)/10</f>
-        <v>27.5510204081633</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="69" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" s="71" t="n">
-        <v>160</v>
-      </c>
-      <c r="C4" s="71" t="n">
-        <f aca="false">(B10*B4)/10000</f>
-        <v>0.512</v>
-      </c>
-      <c r="D4" s="75" t="n">
-        <f aca="false">B4/C10</f>
-        <v>10</v>
-      </c>
-      <c r="E4" s="75" t="n">
-        <f aca="false">E10*D4</f>
+      <c r="B4" s="84" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="79" t="n">
+        <f aca="false">I3/15</f>
+        <v>16.0666666666667</v>
+      </c>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="79"/>
+      <c r="N4" s="79"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="85" t="n">
+        <f aca="false">P3/15</f>
+        <v>10.6666666666667</v>
+      </c>
+      <c r="Q4" s="85"/>
+      <c r="R4" s="85"/>
+      <c r="S4" s="85"/>
+      <c r="T4" s="85"/>
+      <c r="U4" s="85"/>
+      <c r="V4" s="85"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="86" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="86" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="87" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="88" t="s">
+        <v>115</v>
+      </c>
+      <c r="H5" s="88"/>
+      <c r="I5" s="89" t="s">
+        <v>110</v>
+      </c>
+      <c r="J5" s="89" t="s">
+        <v>111</v>
+      </c>
+      <c r="K5" s="90" t="s">
+        <v>112</v>
+      </c>
+      <c r="L5" s="89" t="s">
+        <v>113</v>
+      </c>
+      <c r="M5" s="89" t="s">
+        <v>114</v>
+      </c>
+      <c r="N5" s="91" t="s">
+        <v>115</v>
+      </c>
+      <c r="O5" s="91"/>
+      <c r="P5" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q5" s="92" t="s">
+        <v>111</v>
+      </c>
+      <c r="R5" s="93" t="s">
+        <v>112</v>
+      </c>
+      <c r="S5" s="92" t="s">
+        <v>113</v>
+      </c>
+      <c r="T5" s="92" t="s">
+        <v>114</v>
+      </c>
+      <c r="U5" s="94" t="s">
+        <v>115</v>
+      </c>
+      <c r="V5" s="94"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0"/>
+      <c r="B6" s="86"/>
+      <c r="C6" s="86"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="95" t="s">
+        <v>116</v>
+      </c>
+      <c r="H6" s="96" t="s">
+        <v>117</v>
+      </c>
+      <c r="I6" s="89"/>
+      <c r="J6" s="89"/>
+      <c r="K6" s="89"/>
+      <c r="L6" s="89"/>
+      <c r="M6" s="89"/>
+      <c r="N6" s="97" t="s">
+        <v>116</v>
+      </c>
+      <c r="O6" s="98" t="s">
+        <v>117</v>
+      </c>
+      <c r="P6" s="92"/>
+      <c r="Q6" s="92"/>
+      <c r="R6" s="92"/>
+      <c r="S6" s="92"/>
+      <c r="T6" s="92"/>
+      <c r="U6" s="99" t="s">
+        <v>116</v>
+      </c>
+      <c r="V6" s="100" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0"/>
+      <c r="B7" s="101" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C7" s="102"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="104" t="n">
+        <v>300</v>
+      </c>
+      <c r="H7" s="105" t="n">
+        <f aca="false">(G7/1.72)/10</f>
+        <v>17.4418604651163</v>
+      </c>
+      <c r="I7" s="106" t="n">
+        <v>46202</v>
+      </c>
+      <c r="J7" s="107"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="108"/>
+      <c r="M7" s="108"/>
+      <c r="N7" s="109" t="n">
+        <v>366</v>
+      </c>
+      <c r="O7" s="110" t="n">
+        <f aca="false">(N7/1.69)/10</f>
+        <v>21.6568047337278</v>
+      </c>
+      <c r="P7" s="111" t="n">
+        <v>46202</v>
+      </c>
+      <c r="Q7" s="112"/>
+      <c r="R7" s="113"/>
+      <c r="S7" s="113"/>
+      <c r="T7" s="113"/>
+      <c r="U7" s="114" t="n">
         <v>280</v>
       </c>
-      <c r="F4" s="76" t="n">
-        <f aca="false">(E4/C4)/10</f>
-        <v>54.6875</v>
+      <c r="V7" s="115" t="n">
+        <f aca="false">(U7/0.51)/10</f>
+        <v>54.9019607843137</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="73"/>
-      <c r="B8" s="73" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" s="73" t="s">
-        <v>111</v>
-      </c>
-      <c r="D8" s="73" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" s="73" t="s">
-        <v>113</v>
+      <c r="A8" s="0"/>
+      <c r="B8" s="116" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C8" s="117"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="119" t="n">
+        <f aca="false">T2</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="105" t="n">
+        <f aca="false">(G8/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="120"/>
+      <c r="J8" s="121"/>
+      <c r="K8" s="122"/>
+      <c r="L8" s="122"/>
+      <c r="M8" s="122"/>
+      <c r="N8" s="123"/>
+      <c r="O8" s="124"/>
+      <c r="P8" s="125"/>
+      <c r="Q8" s="126"/>
+      <c r="R8" s="127"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="127"/>
+      <c r="U8" s="128"/>
+      <c r="V8" s="115" t="n">
+        <f aca="false">(U8/0.51)/10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="73" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="129" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="130"/>
+      <c r="D9" s="131"/>
+      <c r="E9" s="131"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="132" t="n">
+        <f aca="false">SUM(G7:G8)</f>
+        <v>300</v>
+      </c>
+      <c r="H9" s="133" t="n">
+        <f aca="false">SUM(H7:H8)</f>
+        <v>17.4418604651163</v>
+      </c>
+      <c r="I9" s="134"/>
+      <c r="J9" s="135"/>
+      <c r="K9" s="136"/>
+      <c r="L9" s="136"/>
+      <c r="M9" s="136"/>
+      <c r="N9" s="134" t="n">
+        <f aca="false">SUM(N7:N8)</f>
+        <v>366</v>
+      </c>
+      <c r="O9" s="134" t="n">
+        <f aca="false">SUM(O7:O8)</f>
+        <v>21.6568047337278</v>
+      </c>
+      <c r="P9" s="137"/>
+      <c r="Q9" s="138"/>
+      <c r="R9" s="139"/>
+      <c r="S9" s="139"/>
+      <c r="T9" s="139"/>
+      <c r="U9" s="137" t="n">
+        <f aca="false">SUM(U7:U8)</f>
+        <v>280</v>
+      </c>
+      <c r="V9" s="140" t="n">
+        <f aca="false">(U9/0.51)/10</f>
+        <v>54.9019607843137</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="141"/>
+      <c r="C10" s="142"/>
+      <c r="D10" s="143"/>
+      <c r="E10" s="143"/>
+      <c r="F10" s="143" t="e">
+        <f aca="false">G10/C10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G10" s="144"/>
+      <c r="H10" s="105" t="n">
+        <f aca="false">(G10/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="145" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J10" s="146" t="n">
+        <v>17</v>
+      </c>
+      <c r="K10" s="147" t="n">
+        <v>2206.7</v>
+      </c>
+      <c r="L10" s="147" t="n">
+        <v>2608</v>
+      </c>
+      <c r="M10" s="147" t="n">
+        <f aca="false">N10/J10</f>
+        <v>23.5882352941177</v>
+      </c>
+      <c r="N10" s="123" t="n">
+        <v>401</v>
+      </c>
+      <c r="O10" s="124" t="n">
+        <f aca="false">(N10/1.69)/10</f>
+        <v>23.7278106508876</v>
+      </c>
+      <c r="P10" s="148"/>
+      <c r="Q10" s="149"/>
+      <c r="R10" s="150"/>
+      <c r="S10" s="150"/>
+      <c r="T10" s="150" t="e">
+        <f aca="false">U10/Q10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U10" s="128"/>
+      <c r="V10" s="115" t="n">
+        <f aca="false">(U10/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="151"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118"/>
+      <c r="F11" s="143" t="e">
+        <f aca="false">G11/C11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G11" s="144"/>
+      <c r="H11" s="105" t="n">
+        <f aca="false">(G11/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="120"/>
+      <c r="J11" s="121"/>
+      <c r="K11" s="122"/>
+      <c r="L11" s="122"/>
+      <c r="M11" s="147" t="e">
+        <f aca="false">N11/J11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N11" s="123"/>
+      <c r="O11" s="124" t="n">
+        <f aca="false">(N11/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="125"/>
+      <c r="Q11" s="126"/>
+      <c r="R11" s="127"/>
+      <c r="S11" s="127"/>
+      <c r="T11" s="150" t="e">
+        <f aca="false">U11/Q11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U11" s="128"/>
+      <c r="V11" s="115" t="n">
+        <f aca="false">(U11/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="151"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="143" t="e">
+        <f aca="false">G12/C12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G12" s="144"/>
+      <c r="H12" s="105" t="n">
+        <f aca="false">(G12/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="120"/>
+      <c r="J12" s="121"/>
+      <c r="K12" s="122"/>
+      <c r="L12" s="122"/>
+      <c r="M12" s="147" t="e">
+        <f aca="false">N12/J12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N12" s="123"/>
+      <c r="O12" s="124" t="n">
+        <f aca="false">(N12/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="125"/>
+      <c r="Q12" s="126"/>
+      <c r="R12" s="127"/>
+      <c r="S12" s="127"/>
+      <c r="T12" s="150" t="e">
+        <f aca="false">U12/Q12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U12" s="128"/>
+      <c r="V12" s="115" t="n">
+        <f aca="false">(U12/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="151"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="143" t="e">
+        <f aca="false">G13/C13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G13" s="144"/>
+      <c r="H13" s="105" t="n">
+        <f aca="false">(G13/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="120"/>
+      <c r="J13" s="121"/>
+      <c r="K13" s="122"/>
+      <c r="L13" s="122"/>
+      <c r="M13" s="147" t="e">
+        <f aca="false">N13/J13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N13" s="123"/>
+      <c r="O13" s="124" t="n">
+        <f aca="false">(N13/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="125"/>
+      <c r="Q13" s="126"/>
+      <c r="R13" s="127"/>
+      <c r="S13" s="127"/>
+      <c r="T13" s="150" t="e">
+        <f aca="false">U13/Q13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U13" s="128"/>
+      <c r="V13" s="115" t="n">
+        <f aca="false">(U13/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="151"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="143" t="e">
+        <f aca="false">G14/C14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G14" s="144"/>
+      <c r="H14" s="105" t="n">
+        <f aca="false">(G14/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="120"/>
+      <c r="J14" s="121"/>
+      <c r="K14" s="122"/>
+      <c r="L14" s="122"/>
+      <c r="M14" s="147" t="e">
+        <f aca="false">N14/J14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N14" s="123"/>
+      <c r="O14" s="124" t="n">
+        <f aca="false">(N14/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="125"/>
+      <c r="Q14" s="126"/>
+      <c r="R14" s="127"/>
+      <c r="S14" s="127"/>
+      <c r="T14" s="150" t="e">
+        <f aca="false">U14/Q14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U14" s="128"/>
+      <c r="V14" s="115" t="n">
+        <f aca="false">(U14/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="151"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="143" t="e">
+        <f aca="false">G15/C15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G15" s="144"/>
+      <c r="H15" s="105" t="n">
+        <f aca="false">(G15/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="120"/>
+      <c r="J15" s="121"/>
+      <c r="K15" s="122"/>
+      <c r="L15" s="122"/>
+      <c r="M15" s="147" t="e">
+        <f aca="false">N15/J15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N15" s="123"/>
+      <c r="O15" s="124" t="n">
+        <f aca="false">(N15/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="126"/>
+      <c r="R15" s="127"/>
+      <c r="S15" s="127"/>
+      <c r="T15" s="150" t="e">
+        <f aca="false">U15/Q15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U15" s="128"/>
+      <c r="V15" s="115" t="n">
+        <f aca="false">(U15/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="151"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="143" t="e">
+        <f aca="false">G16/C16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G16" s="144"/>
+      <c r="H16" s="105" t="n">
+        <f aca="false">(G16/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="120"/>
+      <c r="J16" s="121"/>
+      <c r="K16" s="122"/>
+      <c r="L16" s="122"/>
+      <c r="M16" s="147" t="e">
+        <f aca="false">N16/J16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N16" s="123"/>
+      <c r="O16" s="124" t="n">
+        <f aca="false">(N16/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="125"/>
+      <c r="Q16" s="126"/>
+      <c r="R16" s="127"/>
+      <c r="S16" s="127"/>
+      <c r="T16" s="150" t="e">
+        <f aca="false">U16/Q16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U16" s="128"/>
+      <c r="V16" s="115" t="n">
+        <f aca="false">(U16/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="151"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="143" t="e">
+        <f aca="false">G17/C17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G17" s="144"/>
+      <c r="H17" s="105" t="n">
+        <f aca="false">(G17/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="120"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="122"/>
+      <c r="L17" s="122"/>
+      <c r="M17" s="147" t="e">
+        <f aca="false">N17/J17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N17" s="123"/>
+      <c r="O17" s="124" t="n">
+        <f aca="false">(N17/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="125"/>
+      <c r="Q17" s="126"/>
+      <c r="R17" s="127"/>
+      <c r="S17" s="127"/>
+      <c r="T17" s="150" t="e">
+        <f aca="false">U17/Q17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U17" s="128"/>
+      <c r="V17" s="115" t="n">
+        <f aca="false">(U17/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="151"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="143" t="e">
+        <f aca="false">G18/C18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G18" s="144"/>
+      <c r="H18" s="105" t="n">
+        <f aca="false">(G18/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="120"/>
+      <c r="J18" s="121"/>
+      <c r="K18" s="122"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="147" t="e">
+        <f aca="false">N18/J18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N18" s="123"/>
+      <c r="O18" s="124" t="n">
+        <f aca="false">(N18/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="125"/>
+      <c r="Q18" s="126"/>
+      <c r="R18" s="127"/>
+      <c r="S18" s="127"/>
+      <c r="T18" s="150" t="e">
+        <f aca="false">U18/Q18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U18" s="128"/>
+      <c r="V18" s="115" t="n">
+        <f aca="false">(U18/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="151"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="143" t="e">
+        <f aca="false">G19/C19</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G19" s="144"/>
+      <c r="H19" s="105" t="n">
+        <f aca="false">(G19/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="120"/>
+      <c r="J19" s="121"/>
+      <c r="K19" s="122"/>
+      <c r="L19" s="122"/>
+      <c r="M19" s="147" t="e">
+        <f aca="false">N19/J19</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N19" s="123"/>
+      <c r="O19" s="124" t="n">
+        <f aca="false">(N19/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="125"/>
+      <c r="Q19" s="126"/>
+      <c r="R19" s="127"/>
+      <c r="S19" s="127"/>
+      <c r="T19" s="150" t="e">
+        <f aca="false">U19/Q19</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U19" s="128"/>
+      <c r="V19" s="115" t="n">
+        <f aca="false">(U19/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="151"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="143" t="e">
+        <f aca="false">G20/C20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G20" s="144"/>
+      <c r="H20" s="105" t="n">
+        <f aca="false">(G20/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="120"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="122"/>
+      <c r="L20" s="122"/>
+      <c r="M20" s="147" t="e">
+        <f aca="false">N20/J20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N20" s="123"/>
+      <c r="O20" s="124" t="n">
+        <f aca="false">(N20/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="125"/>
+      <c r="Q20" s="126"/>
+      <c r="R20" s="127"/>
+      <c r="S20" s="127"/>
+      <c r="T20" s="150" t="e">
+        <f aca="false">U20/Q20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U20" s="128"/>
+      <c r="V20" s="115" t="n">
+        <f aca="false">(U20/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="151"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="143" t="e">
+        <f aca="false">G21/C21</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G21" s="144"/>
+      <c r="H21" s="105" t="n">
+        <f aca="false">(G21/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="120"/>
+      <c r="J21" s="121"/>
+      <c r="K21" s="122"/>
+      <c r="L21" s="122"/>
+      <c r="M21" s="147" t="e">
+        <f aca="false">N21/J21</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N21" s="123"/>
+      <c r="O21" s="124" t="n">
+        <f aca="false">(N21/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P21" s="125"/>
+      <c r="Q21" s="126"/>
+      <c r="R21" s="127"/>
+      <c r="S21" s="127"/>
+      <c r="T21" s="150" t="e">
+        <f aca="false">U21/Q21</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U21" s="128"/>
+      <c r="V21" s="115" t="n">
+        <f aca="false">(U21/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="151"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="143" t="e">
+        <f aca="false">G22/C22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G22" s="144"/>
+      <c r="H22" s="105" t="n">
+        <f aca="false">(G22/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="120"/>
+      <c r="J22" s="121"/>
+      <c r="K22" s="122"/>
+      <c r="L22" s="122"/>
+      <c r="M22" s="147" t="e">
+        <f aca="false">N22/J22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N22" s="123"/>
+      <c r="O22" s="124" t="n">
+        <f aca="false">(N22/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P22" s="125"/>
+      <c r="Q22" s="126"/>
+      <c r="R22" s="127"/>
+      <c r="S22" s="127"/>
+      <c r="T22" s="150" t="e">
+        <f aca="false">U22/Q22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U22" s="128"/>
+      <c r="V22" s="115" t="n">
+        <f aca="false">(U22/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="151"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="143" t="e">
+        <f aca="false">G23/C23</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G23" s="144"/>
+      <c r="H23" s="105" t="n">
+        <f aca="false">(G23/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="120"/>
+      <c r="J23" s="121"/>
+      <c r="K23" s="122"/>
+      <c r="L23" s="122"/>
+      <c r="M23" s="147" t="e">
+        <f aca="false">N23/J23</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N23" s="123"/>
+      <c r="O23" s="124" t="n">
+        <f aca="false">(N23/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P23" s="125"/>
+      <c r="Q23" s="126"/>
+      <c r="R23" s="127"/>
+      <c r="S23" s="127"/>
+      <c r="T23" s="150" t="e">
+        <f aca="false">U23/Q23</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U23" s="128"/>
+      <c r="V23" s="115" t="n">
+        <f aca="false">(U23/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="151"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="143" t="e">
+        <f aca="false">G24/C24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G24" s="144"/>
+      <c r="H24" s="105" t="n">
+        <f aca="false">(G24/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="120"/>
+      <c r="J24" s="121"/>
+      <c r="K24" s="122"/>
+      <c r="L24" s="122"/>
+      <c r="M24" s="147" t="e">
+        <f aca="false">N24/J24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N24" s="123"/>
+      <c r="O24" s="124" t="n">
+        <f aca="false">(N24/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="125"/>
+      <c r="Q24" s="126"/>
+      <c r="R24" s="127"/>
+      <c r="S24" s="127"/>
+      <c r="T24" s="150" t="e">
+        <f aca="false">U24/Q24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U24" s="128"/>
+      <c r="V24" s="115" t="n">
+        <f aca="false">(U24/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="151"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="143" t="e">
+        <f aca="false">G25/C25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G25" s="144"/>
+      <c r="H25" s="105" t="n">
+        <f aca="false">(G25/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="120"/>
+      <c r="J25" s="121"/>
+      <c r="K25" s="122"/>
+      <c r="L25" s="122"/>
+      <c r="M25" s="147" t="e">
+        <f aca="false">N25/J25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N25" s="123"/>
+      <c r="O25" s="124" t="n">
+        <f aca="false">(N25/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="125"/>
+      <c r="Q25" s="126"/>
+      <c r="R25" s="127"/>
+      <c r="S25" s="127"/>
+      <c r="T25" s="150" t="e">
+        <f aca="false">U25/Q25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U25" s="128"/>
+      <c r="V25" s="115" t="n">
+        <f aca="false">(U25/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="151"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="118"/>
+      <c r="F26" s="143" t="e">
+        <f aca="false">G26/C26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G26" s="144"/>
+      <c r="H26" s="105" t="n">
+        <f aca="false">(G26/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="120"/>
+      <c r="J26" s="121"/>
+      <c r="K26" s="122"/>
+      <c r="L26" s="122"/>
+      <c r="M26" s="147" t="e">
+        <f aca="false">N26/J26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N26" s="123"/>
+      <c r="O26" s="124" t="n">
+        <f aca="false">(N26/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P26" s="125"/>
+      <c r="Q26" s="126"/>
+      <c r="R26" s="127"/>
+      <c r="S26" s="127"/>
+      <c r="T26" s="150" t="e">
+        <f aca="false">U26/Q26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U26" s="128"/>
+      <c r="V26" s="115" t="n">
+        <f aca="false">(U26/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="151"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="118"/>
+      <c r="E27" s="118"/>
+      <c r="F27" s="143" t="e">
+        <f aca="false">G27/C27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G27" s="144"/>
+      <c r="H27" s="105" t="n">
+        <f aca="false">(G27/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="120"/>
+      <c r="J27" s="121"/>
+      <c r="K27" s="122"/>
+      <c r="L27" s="122"/>
+      <c r="M27" s="147" t="e">
+        <f aca="false">N27/J27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N27" s="123"/>
+      <c r="O27" s="124" t="n">
+        <f aca="false">(N27/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P27" s="125"/>
+      <c r="Q27" s="126"/>
+      <c r="R27" s="127"/>
+      <c r="S27" s="127"/>
+      <c r="T27" s="150" t="e">
+        <f aca="false">U27/Q27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U27" s="128"/>
+      <c r="V27" s="115" t="n">
+        <f aca="false">(U27/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="151"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="118"/>
+      <c r="E28" s="118"/>
+      <c r="F28" s="143" t="e">
+        <f aca="false">G28/C28</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G28" s="144"/>
+      <c r="H28" s="105" t="n">
+        <f aca="false">(G28/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="120"/>
+      <c r="J28" s="121"/>
+      <c r="K28" s="122"/>
+      <c r="L28" s="122"/>
+      <c r="M28" s="147" t="e">
+        <f aca="false">N28/J28</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N28" s="123"/>
+      <c r="O28" s="124" t="n">
+        <f aca="false">(N28/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P28" s="125"/>
+      <c r="Q28" s="126"/>
+      <c r="R28" s="127"/>
+      <c r="S28" s="127"/>
+      <c r="T28" s="150" t="e">
+        <f aca="false">U28/Q28</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U28" s="128"/>
+      <c r="V28" s="115" t="n">
+        <f aca="false">(U28/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="151"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="118"/>
+      <c r="E29" s="118"/>
+      <c r="F29" s="143" t="e">
+        <f aca="false">G29/C29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G29" s="144"/>
+      <c r="H29" s="105" t="n">
+        <f aca="false">(G29/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="120"/>
+      <c r="J29" s="121"/>
+      <c r="K29" s="122"/>
+      <c r="L29" s="122"/>
+      <c r="M29" s="147" t="e">
+        <f aca="false">N29/J29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N29" s="123"/>
+      <c r="O29" s="124" t="n">
+        <f aca="false">(N29/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P29" s="125"/>
+      <c r="Q29" s="126"/>
+      <c r="R29" s="127"/>
+      <c r="S29" s="127"/>
+      <c r="T29" s="150" t="e">
+        <f aca="false">U29/Q29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U29" s="128"/>
+      <c r="V29" s="115" t="n">
+        <f aca="false">(U29/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="151"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="143" t="e">
+        <f aca="false">G30/C30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G30" s="144"/>
+      <c r="H30" s="105" t="n">
+        <f aca="false">(G30/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="120"/>
+      <c r="J30" s="121"/>
+      <c r="K30" s="122"/>
+      <c r="L30" s="122"/>
+      <c r="M30" s="147" t="e">
+        <f aca="false">N30/J30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N30" s="123"/>
+      <c r="O30" s="124" t="n">
+        <f aca="false">(N30/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P30" s="125"/>
+      <c r="Q30" s="126"/>
+      <c r="R30" s="127"/>
+      <c r="S30" s="127"/>
+      <c r="T30" s="150" t="e">
+        <f aca="false">U30/Q30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U30" s="128"/>
+      <c r="V30" s="115" t="n">
+        <f aca="false">(U30/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="151"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="118"/>
+      <c r="E31" s="118"/>
+      <c r="F31" s="143" t="e">
+        <f aca="false">G31/C31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G31" s="144"/>
+      <c r="H31" s="105" t="n">
+        <f aca="false">(G31/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="120"/>
+      <c r="J31" s="121"/>
+      <c r="K31" s="122"/>
+      <c r="L31" s="122"/>
+      <c r="M31" s="147" t="e">
+        <f aca="false">N31/J31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N31" s="123"/>
+      <c r="O31" s="124" t="n">
+        <f aca="false">(N31/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="125"/>
+      <c r="Q31" s="126"/>
+      <c r="R31" s="127"/>
+      <c r="S31" s="127"/>
+      <c r="T31" s="150" t="e">
+        <f aca="false">U31/Q31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U31" s="128"/>
+      <c r="V31" s="115" t="n">
+        <f aca="false">(U31/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="151"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="143" t="e">
+        <f aca="false">G32/C32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G32" s="144"/>
+      <c r="H32" s="105" t="n">
+        <f aca="false">(G32/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="120"/>
+      <c r="J32" s="121"/>
+      <c r="K32" s="122"/>
+      <c r="L32" s="122"/>
+      <c r="M32" s="147" t="e">
+        <f aca="false">N32/J32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N32" s="123"/>
+      <c r="O32" s="124" t="n">
+        <f aca="false">(N32/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P32" s="125"/>
+      <c r="Q32" s="126"/>
+      <c r="R32" s="127"/>
+      <c r="S32" s="127"/>
+      <c r="T32" s="150" t="e">
+        <f aca="false">U32/Q32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U32" s="128"/>
+      <c r="V32" s="115" t="n">
+        <f aca="false">(U32/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="151"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="118"/>
+      <c r="E33" s="118"/>
+      <c r="F33" s="143" t="e">
+        <f aca="false">G33/C33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G33" s="144"/>
+      <c r="H33" s="105" t="n">
+        <f aca="false">(G33/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="120"/>
+      <c r="J33" s="121"/>
+      <c r="K33" s="122"/>
+      <c r="L33" s="122"/>
+      <c r="M33" s="147" t="e">
+        <f aca="false">N33/J33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N33" s="123"/>
+      <c r="O33" s="124" t="n">
+        <f aca="false">(N33/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P33" s="125"/>
+      <c r="Q33" s="126"/>
+      <c r="R33" s="127"/>
+      <c r="S33" s="127"/>
+      <c r="T33" s="150" t="e">
+        <f aca="false">U33/Q33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U33" s="128"/>
+      <c r="V33" s="115" t="n">
+        <f aca="false">(U33/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="151"/>
+      <c r="C34" s="117"/>
+      <c r="D34" s="118"/>
+      <c r="E34" s="118"/>
+      <c r="F34" s="143" t="e">
+        <f aca="false">G34/C34</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G34" s="144"/>
+      <c r="H34" s="105" t="n">
+        <f aca="false">(G34/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="120"/>
+      <c r="J34" s="121"/>
+      <c r="K34" s="122"/>
+      <c r="L34" s="122"/>
+      <c r="M34" s="147" t="e">
+        <f aca="false">N34/J34</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N34" s="123"/>
+      <c r="O34" s="124" t="n">
+        <f aca="false">(N34/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P34" s="125"/>
+      <c r="Q34" s="126"/>
+      <c r="R34" s="127"/>
+      <c r="S34" s="127"/>
+      <c r="T34" s="150" t="e">
+        <f aca="false">U34/Q34</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U34" s="128"/>
+      <c r="V34" s="115" t="n">
+        <f aca="false">(U34/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="151"/>
+      <c r="C35" s="117"/>
+      <c r="D35" s="118"/>
+      <c r="E35" s="118"/>
+      <c r="F35" s="143" t="e">
+        <f aca="false">G35/C35</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G35" s="144"/>
+      <c r="H35" s="105" t="n">
+        <f aca="false">(G35/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="120"/>
+      <c r="J35" s="121"/>
+      <c r="K35" s="122"/>
+      <c r="L35" s="122"/>
+      <c r="M35" s="147" t="e">
+        <f aca="false">N35/J35</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N35" s="123"/>
+      <c r="O35" s="124" t="n">
+        <f aca="false">(N35/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P35" s="125"/>
+      <c r="Q35" s="126"/>
+      <c r="R35" s="127"/>
+      <c r="S35" s="127"/>
+      <c r="T35" s="150" t="e">
+        <f aca="false">U35/Q35</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U35" s="128"/>
+      <c r="V35" s="115" t="n">
+        <f aca="false">(U35/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="152"/>
+      <c r="C36" s="153"/>
+      <c r="D36" s="154"/>
+      <c r="E36" s="154"/>
+      <c r="F36" s="143" t="e">
+        <f aca="false">G36/C36</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G36" s="155"/>
+      <c r="H36" s="105" t="n">
+        <f aca="false">(G36/1.72)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="156"/>
+      <c r="J36" s="157"/>
+      <c r="K36" s="158"/>
+      <c r="L36" s="158"/>
+      <c r="M36" s="147" t="e">
+        <f aca="false">N36/J36</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N36" s="159"/>
+      <c r="O36" s="124" t="n">
+        <f aca="false">(N36/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P36" s="160"/>
+      <c r="Q36" s="161"/>
+      <c r="R36" s="162"/>
+      <c r="S36" s="162"/>
+      <c r="T36" s="150" t="e">
+        <f aca="false">U36/Q36</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U36" s="163"/>
+      <c r="V36" s="115" t="n">
+        <f aca="false">(U36/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="164"/>
+      <c r="C39" s="164" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="164" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" s="165" t="n">
         <v>70</v>
       </c>
-      <c r="C9" s="22" t="n">
-        <v>14</v>
-      </c>
-      <c r="D9" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="E9" s="22" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="73" t="s">
-        <v>115</v>
-      </c>
-      <c r="B10" s="22" t="n">
+    </row>
+    <row r="41" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="164" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" s="165" t="n">
         <v>32</v>
       </c>
-      <c r="C10" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G13" s="77" t="s">
-        <v>102</v>
-      </c>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="78" t="s">
-        <v>103</v>
-      </c>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="79" t="s">
-        <v>104</v>
-      </c>
-      <c r="N13" s="79"/>
-      <c r="O13" s="79"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G14" s="80" t="s">
-        <v>116</v>
-      </c>
-      <c r="H14" s="81" t="s">
-        <v>117</v>
-      </c>
-      <c r="I14" s="81"/>
-      <c r="J14" s="82" t="s">
-        <v>116</v>
-      </c>
-      <c r="K14" s="83" t="s">
-        <v>117</v>
-      </c>
-      <c r="L14" s="83"/>
-      <c r="M14" s="84" t="s">
-        <v>116</v>
-      </c>
-      <c r="N14" s="85" t="s">
-        <v>117</v>
-      </c>
-      <c r="O14" s="85"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G15" s="80"/>
-      <c r="H15" s="86" t="s">
-        <v>118</v>
-      </c>
-      <c r="I15" s="87" t="s">
-        <v>119</v>
-      </c>
-      <c r="J15" s="82"/>
-      <c r="K15" s="88" t="s">
-        <v>118</v>
-      </c>
-      <c r="L15" s="89" t="s">
-        <v>119</v>
-      </c>
-      <c r="M15" s="84"/>
-      <c r="N15" s="90" t="s">
-        <v>118</v>
-      </c>
-      <c r="O15" s="91" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" s="101" customFormat="true" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="73"/>
-      <c r="B16" s="73"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="92" t="n">
-        <v>46198</v>
-      </c>
-      <c r="H16" s="93" t="n">
-        <v>300</v>
-      </c>
-      <c r="I16" s="94" t="n">
-        <f aca="false">(H16/C2)/10</f>
-        <v>17.4216027874564</v>
-      </c>
-      <c r="J16" s="95" t="n">
-        <v>46202</v>
-      </c>
-      <c r="K16" s="96" t="n">
-        <v>366</v>
-      </c>
-      <c r="L16" s="97" t="n">
-        <f aca="false">(K16/C3)/10</f>
-        <v>21.6953171310018</v>
-      </c>
-      <c r="M16" s="98" t="n">
-        <v>46199</v>
-      </c>
-      <c r="N16" s="99" t="n">
-        <f aca="false">E4</f>
-        <v>280</v>
-      </c>
-      <c r="O16" s="100" t="n">
-        <f aca="false">(N16/C4)/10</f>
-        <v>54.6875</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="102"/>
-      <c r="B17" s="103"/>
-      <c r="C17" s="103"/>
-      <c r="D17" s="103"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="101"/>
-      <c r="G17" s="104" t="n">
-        <v>46200</v>
-      </c>
-      <c r="H17" s="105" t="n">
-        <f aca="false">E2</f>
-        <v>474.428571428571</v>
-      </c>
-      <c r="I17" s="94" t="n">
-        <f aca="false">(H17/C2)/10</f>
-        <v>27.5510204081633</v>
-      </c>
-      <c r="J17" s="106"/>
-      <c r="K17" s="107"/>
-      <c r="L17" s="108"/>
-      <c r="M17" s="109"/>
-      <c r="N17" s="110"/>
-      <c r="O17" s="111"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="G18" s="112" t="s">
-        <v>120</v>
-      </c>
-      <c r="H18" s="113" t="n">
-        <f aca="false">SUM(H16:H17)</f>
-        <v>774.428571428571</v>
-      </c>
-      <c r="I18" s="114" t="n">
-        <f aca="false">SUM(I16:I17)</f>
-        <v>44.9726231956197</v>
-      </c>
-      <c r="J18" s="114"/>
-      <c r="K18" s="114" t="n">
-        <f aca="false">SUM(K16:K17)</f>
-        <v>366</v>
-      </c>
-      <c r="L18" s="114" t="n">
-        <f aca="false">SUM(L16:L17)</f>
-        <v>21.6953171310018</v>
-      </c>
-      <c r="M18" s="114"/>
-      <c r="N18" s="114" t="n">
-        <f aca="false">SUM(N16:N17)</f>
-        <v>280</v>
-      </c>
-      <c r="O18" s="114" t="n">
-        <f aca="false">SUM(O16:O17)</f>
-        <v>54.6875</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="70"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="94" t="n">
-        <f aca="false">(H19/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="106"/>
-      <c r="K19" s="107"/>
-      <c r="L19" s="108"/>
-      <c r="M19" s="109"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="111"/>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="70"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="94" t="n">
-        <f aca="false">(H20/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="106"/>
-      <c r="K20" s="107"/>
-      <c r="L20" s="108"/>
-      <c r="M20" s="109"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="111"/>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="70"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="70"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="94" t="n">
-        <f aca="false">(H21/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="106"/>
-      <c r="K21" s="107"/>
-      <c r="L21" s="108"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="110"/>
-      <c r="O21" s="111"/>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="70"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="105"/>
-      <c r="I22" s="94" t="n">
-        <f aca="false">(H22/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="106"/>
-      <c r="K22" s="107"/>
-      <c r="L22" s="108"/>
-      <c r="M22" s="109"/>
-      <c r="N22" s="110"/>
-      <c r="O22" s="111"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="70"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
-      <c r="G23" s="104"/>
-      <c r="H23" s="105"/>
-      <c r="I23" s="94" t="n">
-        <f aca="false">(H23/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="106"/>
-      <c r="K23" s="107"/>
-      <c r="L23" s="108"/>
-      <c r="M23" s="109"/>
-      <c r="N23" s="110"/>
-      <c r="O23" s="111"/>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="70"/>
-      <c r="C24" s="70"/>
-      <c r="D24" s="70"/>
-      <c r="G24" s="104"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="94" t="n">
-        <f aca="false">(H24/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="106"/>
-      <c r="K24" s="107"/>
-      <c r="L24" s="108"/>
-      <c r="M24" s="109"/>
-      <c r="N24" s="110"/>
-      <c r="O24" s="111"/>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="70"/>
-      <c r="C25" s="70"/>
-      <c r="D25" s="70"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="94" t="n">
-        <f aca="false">(H25/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="106"/>
-      <c r="K25" s="107"/>
-      <c r="L25" s="108"/>
-      <c r="M25" s="109"/>
-      <c r="N25" s="110"/>
-      <c r="O25" s="111"/>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="70"/>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
-      <c r="G26" s="104"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="94" t="n">
-        <f aca="false">(H26/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="106"/>
-      <c r="K26" s="107"/>
-      <c r="L26" s="108"/>
-      <c r="M26" s="109"/>
-      <c r="N26" s="110"/>
-      <c r="O26" s="111"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="70"/>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
-      <c r="G27" s="104"/>
-      <c r="H27" s="105"/>
-      <c r="I27" s="94" t="n">
-        <f aca="false">(H27/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="106"/>
-      <c r="K27" s="107"/>
-      <c r="L27" s="108"/>
-      <c r="M27" s="109"/>
-      <c r="N27" s="110"/>
-      <c r="O27" s="111"/>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="70"/>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="105"/>
-      <c r="I28" s="94" t="n">
-        <f aca="false">(H28/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="106"/>
-      <c r="K28" s="107"/>
-      <c r="L28" s="108"/>
-      <c r="M28" s="109"/>
-      <c r="N28" s="110"/>
-      <c r="O28" s="111"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="70"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="70"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="105"/>
-      <c r="I29" s="94" t="n">
-        <f aca="false">(H29/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="106"/>
-      <c r="K29" s="107"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="109"/>
-      <c r="N29" s="110"/>
-      <c r="O29" s="111"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="70"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="105"/>
-      <c r="I30" s="94" t="n">
-        <f aca="false">(H30/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="106"/>
-      <c r="K30" s="107"/>
-      <c r="L30" s="108"/>
-      <c r="M30" s="109"/>
-      <c r="N30" s="110"/>
-      <c r="O30" s="111"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="70"/>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="105"/>
-      <c r="I31" s="94" t="n">
-        <f aca="false">(H31/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J31" s="106"/>
-      <c r="K31" s="107"/>
-      <c r="L31" s="108"/>
-      <c r="M31" s="109"/>
-      <c r="N31" s="110"/>
-      <c r="O31" s="111"/>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="70"/>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="105"/>
-      <c r="I32" s="94" t="n">
-        <f aca="false">(H32/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="106"/>
-      <c r="K32" s="107"/>
-      <c r="L32" s="108"/>
-      <c r="M32" s="109"/>
-      <c r="N32" s="110"/>
-      <c r="O32" s="111"/>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="70"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="G33" s="104"/>
-      <c r="H33" s="105"/>
-      <c r="I33" s="94" t="n">
-        <f aca="false">(H33/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="106"/>
-      <c r="K33" s="107"/>
-      <c r="L33" s="108"/>
-      <c r="M33" s="109"/>
-      <c r="N33" s="110"/>
-      <c r="O33" s="111"/>
-    </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="70"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
-      <c r="G34" s="104"/>
-      <c r="H34" s="105"/>
-      <c r="I34" s="94" t="n">
-        <f aca="false">(H34/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="106"/>
-      <c r="K34" s="107"/>
-      <c r="L34" s="108"/>
-      <c r="M34" s="109"/>
-      <c r="N34" s="110"/>
-      <c r="O34" s="111"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="115"/>
-      <c r="C35" s="115"/>
-      <c r="D35" s="115"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="105"/>
-      <c r="I35" s="94" t="n">
-        <f aca="false">(H35/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="106"/>
-      <c r="K35" s="107"/>
-      <c r="L35" s="108"/>
-      <c r="M35" s="109"/>
-      <c r="N35" s="110"/>
-      <c r="O35" s="111"/>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="115"/>
-      <c r="C36" s="115"/>
-      <c r="D36" s="115"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="105"/>
-      <c r="I36" s="94" t="n">
-        <f aca="false">(H36/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="106"/>
-      <c r="K36" s="107"/>
-      <c r="L36" s="108"/>
-      <c r="M36" s="109"/>
-      <c r="N36" s="110"/>
-      <c r="O36" s="111"/>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="104"/>
-      <c r="H37" s="105"/>
-      <c r="I37" s="94" t="n">
-        <f aca="false">(H37/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="106"/>
-      <c r="K37" s="107"/>
-      <c r="L37" s="108"/>
-      <c r="M37" s="109"/>
-      <c r="N37" s="110"/>
-      <c r="O37" s="111"/>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="104"/>
-      <c r="H38" s="105"/>
-      <c r="I38" s="94" t="n">
-        <f aca="false">(H38/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="106"/>
-      <c r="K38" s="107"/>
-      <c r="L38" s="108"/>
-      <c r="M38" s="109"/>
-      <c r="N38" s="110"/>
-      <c r="O38" s="111"/>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="104"/>
-      <c r="H39" s="105"/>
-      <c r="I39" s="94" t="n">
-        <f aca="false">(H39/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="106"/>
-      <c r="K39" s="107"/>
-      <c r="L39" s="108"/>
-      <c r="M39" s="109"/>
-      <c r="N39" s="110"/>
-      <c r="O39" s="111"/>
-    </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="104"/>
-      <c r="H40" s="105"/>
-      <c r="I40" s="94" t="n">
-        <f aca="false">(H40/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="106"/>
-      <c r="K40" s="107"/>
-      <c r="L40" s="108"/>
-      <c r="M40" s="109"/>
-      <c r="N40" s="110"/>
-      <c r="O40" s="111"/>
-    </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="104"/>
-      <c r="H41" s="105"/>
-      <c r="I41" s="94" t="n">
-        <f aca="false">(H41/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J41" s="106"/>
-      <c r="K41" s="107"/>
-      <c r="L41" s="108"/>
-      <c r="M41" s="109"/>
-      <c r="N41" s="110"/>
-      <c r="O41" s="111"/>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="104"/>
-      <c r="H42" s="105"/>
-      <c r="I42" s="94" t="n">
-        <f aca="false">(H42/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J42" s="106"/>
-      <c r="K42" s="107"/>
-      <c r="L42" s="108"/>
-      <c r="M42" s="109"/>
-      <c r="N42" s="110"/>
-      <c r="O42" s="111"/>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G43" s="104"/>
-      <c r="H43" s="105"/>
-      <c r="I43" s="94" t="n">
-        <f aca="false">(H43/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J43" s="106"/>
-      <c r="K43" s="107"/>
-      <c r="L43" s="108"/>
-      <c r="M43" s="109"/>
-      <c r="N43" s="110"/>
-      <c r="O43" s="111"/>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G44" s="104"/>
-      <c r="H44" s="105"/>
-      <c r="I44" s="94" t="n">
-        <f aca="false">(H44/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J44" s="106"/>
-      <c r="K44" s="107"/>
-      <c r="L44" s="108"/>
-      <c r="M44" s="109"/>
-      <c r="N44" s="110"/>
-      <c r="O44" s="111"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G45" s="116"/>
-      <c r="H45" s="105"/>
-      <c r="I45" s="94" t="n">
-        <f aca="false">(H45/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J45" s="117"/>
-      <c r="K45" s="118"/>
-      <c r="L45" s="119"/>
-      <c r="M45" s="120"/>
-      <c r="N45" s="121"/>
-      <c r="O45" s="122"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:O14"/>
+  <mergeCells count="30">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="P2:V2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="I3:O3"/>
+    <mergeCell ref="P3:V3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="I4:O4"/>
+    <mergeCell ref="P4:V4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="U5:V5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -4291,796 +5155,1497 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFDDDDDD"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:V1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="15.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="16.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="22" width="20.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="22" width="21.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="22" width="16.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="22" width="20.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="70" width="15.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="71" width="14.92"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="9" style="71" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="10" style="72" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="71" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="13" style="72" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="14" style="71" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.66"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="73"/>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="72"/>
       <c r="B1" s="74" t="s">
-        <v>105</v>
-      </c>
-      <c r="C1" s="74" t="s">
-        <v>106</v>
-      </c>
-      <c r="D1" s="74" t="s">
-        <v>121</v>
-      </c>
-      <c r="E1" s="74" t="s">
-        <v>108</v>
-      </c>
-      <c r="F1" s="74" t="s">
-        <v>109</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="75" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="76" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
+      <c r="V1" s="76"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71" t="n">
+      <c r="A2" s="77" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="78" t="n">
         <v>0.7</v>
       </c>
-      <c r="D2" s="75" t="n">
-        <v>12</v>
-      </c>
-      <c r="E2" s="75" t="n">
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="166" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
+      <c r="L2" s="166"/>
+      <c r="M2" s="166"/>
+      <c r="N2" s="166"/>
+      <c r="O2" s="166"/>
+      <c r="P2" s="80" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="72"/>
+      <c r="B3" s="86" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="86" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="87" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="88" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" s="88"/>
+      <c r="I3" s="89" t="s">
+        <v>110</v>
+      </c>
+      <c r="J3" s="89" t="s">
+        <v>111</v>
+      </c>
+      <c r="K3" s="90" t="s">
+        <v>112</v>
+      </c>
+      <c r="L3" s="89" t="s">
+        <v>113</v>
+      </c>
+      <c r="M3" s="89" t="s">
+        <v>114</v>
+      </c>
+      <c r="N3" s="91" t="s">
+        <v>115</v>
+      </c>
+      <c r="O3" s="91"/>
+      <c r="P3" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q3" s="92" t="s">
+        <v>111</v>
+      </c>
+      <c r="R3" s="93" t="s">
+        <v>112</v>
+      </c>
+      <c r="S3" s="92" t="s">
+        <v>113</v>
+      </c>
+      <c r="T3" s="92" t="s">
+        <v>114</v>
+      </c>
+      <c r="U3" s="94" t="s">
+        <v>115</v>
+      </c>
+      <c r="V3" s="94"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="95" t="s">
+        <v>116</v>
+      </c>
+      <c r="H4" s="96" t="s">
+        <v>117</v>
+      </c>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="97" t="s">
+        <v>116</v>
+      </c>
+      <c r="O4" s="98" t="s">
+        <v>117</v>
+      </c>
+      <c r="P4" s="92"/>
+      <c r="Q4" s="92"/>
+      <c r="R4" s="92"/>
+      <c r="S4" s="92"/>
+      <c r="T4" s="92"/>
+      <c r="U4" s="99" t="s">
+        <v>116</v>
+      </c>
+      <c r="V4" s="100" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="101" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C5" s="102"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="104" t="n">
         <v>362</v>
       </c>
-      <c r="F2" s="76" t="n">
-        <f aca="false">(E2/C2)/10</f>
+      <c r="H5" s="105" t="n">
+        <f aca="false">(G5/0.7)/10</f>
         <v>51.7142857142857</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71" t="n">
-        <f aca="false">(B9*B3)/10000</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="75" t="e">
-        <f aca="false">B3/C9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E3" s="75" t="e">
-        <f aca="false">E9*D3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F3" s="76" t="e">
-        <f aca="false">(E3/C3)/10</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="69" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71" t="n">
-        <f aca="false">(B10*B4)/10000</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="75" t="e">
-        <f aca="false">B4/C10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E4" s="75" t="e">
-        <f aca="false">E10*D4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F4" s="76" t="e">
-        <f aca="false">(E4/C4)/10</f>
-        <v>#DIV/0!</v>
+      <c r="I5" s="106"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="108"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="109"/>
+      <c r="O5" s="110" t="n">
+        <f aca="false">(N5/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="111"/>
+      <c r="Q5" s="112"/>
+      <c r="R5" s="113"/>
+      <c r="S5" s="113"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="114"/>
+      <c r="V5" s="115" t="n">
+        <f aca="false">(U5/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="116"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="105" t="n">
+        <f aca="false">(G6/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="120"/>
+      <c r="J6" s="121"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="122"/>
+      <c r="N6" s="123"/>
+      <c r="O6" s="124"/>
+      <c r="P6" s="125"/>
+      <c r="Q6" s="126"/>
+      <c r="R6" s="127"/>
+      <c r="S6" s="127"/>
+      <c r="T6" s="127"/>
+      <c r="U6" s="128"/>
+      <c r="V6" s="115" t="n">
+        <f aca="false">(U6/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="72"/>
+      <c r="B7" s="129" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="130"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="132" t="n">
+        <f aca="false">SUM(G5:G6)</f>
+        <v>362</v>
+      </c>
+      <c r="H7" s="133" t="n">
+        <f aca="false">(G7/0.7)/10</f>
+        <v>51.7142857142857</v>
+      </c>
+      <c r="I7" s="134"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="136"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="136"/>
+      <c r="N7" s="134" t="n">
+        <f aca="false">SUM(N5:N6)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="134" t="n">
+        <f aca="false">SUM(O5:O6)</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="137"/>
+      <c r="Q7" s="138"/>
+      <c r="R7" s="139"/>
+      <c r="S7" s="139"/>
+      <c r="T7" s="139"/>
+      <c r="U7" s="137" t="n">
+        <f aca="false">SUM(U5:U6)</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="140" t="n">
+        <f aca="false">(U7/0.51)/10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="73"/>
-      <c r="B8" s="73" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" s="73" t="s">
-        <v>111</v>
-      </c>
-      <c r="D8" s="73" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" s="73" t="s">
-        <v>113</v>
+      <c r="A8" s="72"/>
+      <c r="B8" s="141"/>
+      <c r="C8" s="142"/>
+      <c r="D8" s="143"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="143" t="e">
+        <f aca="false">G8/C8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G8" s="144"/>
+      <c r="H8" s="105" t="n">
+        <f aca="false">(G8/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="145" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J8" s="146" t="n">
+        <v>17</v>
+      </c>
+      <c r="K8" s="167" t="n">
+        <v>52645</v>
+      </c>
+      <c r="L8" s="147" t="n">
+        <v>52931</v>
+      </c>
+      <c r="M8" s="147" t="n">
+        <f aca="false">N8/J8</f>
+        <v>17.1176470588235</v>
+      </c>
+      <c r="N8" s="123" t="n">
+        <v>291</v>
+      </c>
+      <c r="O8" s="124" t="n">
+        <f aca="false">(N8/0.7)/10</f>
+        <v>41.5714285714286</v>
+      </c>
+      <c r="P8" s="148"/>
+      <c r="Q8" s="149"/>
+      <c r="R8" s="150"/>
+      <c r="S8" s="150"/>
+      <c r="T8" s="150" t="e">
+        <f aca="false">U8/Q8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U8" s="128"/>
+      <c r="V8" s="115" t="n">
+        <f aca="false">(U8/0.1)/10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="73"/>
-      <c r="E9" s="1" t="n">
-        <f aca="false">E2/D2</f>
-        <v>30.1666666666667</v>
+      <c r="A9" s="72"/>
+      <c r="B9" s="151"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="143" t="e">
+        <f aca="false">G9/C9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G9" s="144"/>
+      <c r="H9" s="105" t="n">
+        <f aca="false">(G9/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="120"/>
+      <c r="J9" s="121"/>
+      <c r="K9" s="122"/>
+      <c r="L9" s="122"/>
+      <c r="M9" s="147" t="e">
+        <f aca="false">N9/J9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N9" s="123"/>
+      <c r="O9" s="124" t="n">
+        <f aca="false">(N9/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="125"/>
+      <c r="Q9" s="126"/>
+      <c r="R9" s="127"/>
+      <c r="S9" s="127"/>
+      <c r="T9" s="150" t="e">
+        <f aca="false">U9/Q9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U9" s="128"/>
+      <c r="V9" s="115" t="n">
+        <f aca="false">(U9/0.51)/10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="73"/>
+      <c r="A10" s="72"/>
+      <c r="B10" s="151"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
+      <c r="F10" s="143" t="e">
+        <f aca="false">G10/C10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G10" s="144"/>
+      <c r="H10" s="105" t="n">
+        <f aca="false">(G10/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="120"/>
+      <c r="J10" s="121"/>
+      <c r="K10" s="122"/>
+      <c r="L10" s="122"/>
+      <c r="M10" s="147" t="e">
+        <f aca="false">N10/J10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N10" s="123"/>
+      <c r="O10" s="124" t="n">
+        <f aca="false">(N10/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P10" s="125"/>
+      <c r="Q10" s="126"/>
+      <c r="R10" s="127"/>
+      <c r="S10" s="127"/>
+      <c r="T10" s="150" t="e">
+        <f aca="false">U10/Q10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U10" s="128"/>
+      <c r="V10" s="115" t="n">
+        <f aca="false">(U10/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="72"/>
+      <c r="B11" s="151"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118"/>
+      <c r="F11" s="143" t="e">
+        <f aca="false">G11/C11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G11" s="144"/>
+      <c r="H11" s="105" t="n">
+        <f aca="false">(G11/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="120"/>
+      <c r="J11" s="121"/>
+      <c r="K11" s="122"/>
+      <c r="L11" s="122"/>
+      <c r="M11" s="147" t="e">
+        <f aca="false">N11/J11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N11" s="123"/>
+      <c r="O11" s="124" t="n">
+        <f aca="false">(N11/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="125"/>
+      <c r="Q11" s="126"/>
+      <c r="R11" s="127"/>
+      <c r="S11" s="127"/>
+      <c r="T11" s="150" t="e">
+        <f aca="false">U11/Q11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U11" s="128"/>
+      <c r="V11" s="115" t="n">
+        <f aca="false">(U11/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="72"/>
+      <c r="B12" s="151"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="143" t="e">
+        <f aca="false">G12/C12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G12" s="144"/>
+      <c r="H12" s="105" t="n">
+        <f aca="false">(G12/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="120"/>
+      <c r="J12" s="121"/>
+      <c r="K12" s="122"/>
+      <c r="L12" s="122"/>
+      <c r="M12" s="147" t="e">
+        <f aca="false">N12/J12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N12" s="123"/>
+      <c r="O12" s="124" t="n">
+        <f aca="false">(N12/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="125"/>
+      <c r="Q12" s="126"/>
+      <c r="R12" s="127"/>
+      <c r="S12" s="127"/>
+      <c r="T12" s="150" t="e">
+        <f aca="false">U12/Q12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U12" s="128"/>
+      <c r="V12" s="115" t="n">
+        <f aca="false">(U12/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G13" s="77" t="s">
-        <v>102</v>
-      </c>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="78" t="s">
-        <v>103</v>
-      </c>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="79" t="s">
-        <v>104</v>
-      </c>
-      <c r="N13" s="79"/>
-      <c r="O13" s="79"/>
+      <c r="A13" s="72"/>
+      <c r="B13" s="151"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="143" t="e">
+        <f aca="false">G13/C13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G13" s="144"/>
+      <c r="H13" s="105" t="n">
+        <f aca="false">(G13/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="120"/>
+      <c r="J13" s="121"/>
+      <c r="K13" s="122"/>
+      <c r="L13" s="122"/>
+      <c r="M13" s="147" t="e">
+        <f aca="false">N13/J13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N13" s="123"/>
+      <c r="O13" s="124" t="n">
+        <f aca="false">(N13/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="125"/>
+      <c r="Q13" s="126"/>
+      <c r="R13" s="127"/>
+      <c r="S13" s="127"/>
+      <c r="T13" s="150" t="e">
+        <f aca="false">U13/Q13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U13" s="128"/>
+      <c r="V13" s="115" t="n">
+        <f aca="false">(U13/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G14" s="80" t="s">
-        <v>116</v>
-      </c>
-      <c r="H14" s="81" t="s">
-        <v>117</v>
-      </c>
-      <c r="I14" s="81"/>
-      <c r="J14" s="82" t="s">
-        <v>116</v>
-      </c>
-      <c r="K14" s="83" t="s">
-        <v>117</v>
-      </c>
-      <c r="L14" s="83"/>
-      <c r="M14" s="84" t="s">
-        <v>116</v>
-      </c>
-      <c r="N14" s="85" t="s">
-        <v>117</v>
-      </c>
-      <c r="O14" s="85"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="151"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="143" t="e">
+        <f aca="false">G14/C14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G14" s="144"/>
+      <c r="H14" s="105" t="n">
+        <f aca="false">(G14/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="120"/>
+      <c r="J14" s="121"/>
+      <c r="K14" s="122"/>
+      <c r="L14" s="122"/>
+      <c r="M14" s="147" t="e">
+        <f aca="false">N14/J14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N14" s="123"/>
+      <c r="O14" s="124" t="n">
+        <f aca="false">(N14/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="125"/>
+      <c r="Q14" s="126"/>
+      <c r="R14" s="127"/>
+      <c r="S14" s="127"/>
+      <c r="T14" s="150" t="e">
+        <f aca="false">U14/Q14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U14" s="128"/>
+      <c r="V14" s="115" t="n">
+        <f aca="false">(U14/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G15" s="80"/>
-      <c r="H15" s="86" t="s">
-        <v>118</v>
-      </c>
-      <c r="I15" s="87" t="s">
-        <v>119</v>
-      </c>
-      <c r="J15" s="82"/>
-      <c r="K15" s="88" t="s">
-        <v>118</v>
-      </c>
-      <c r="L15" s="89" t="s">
-        <v>119</v>
-      </c>
-      <c r="M15" s="84"/>
-      <c r="N15" s="90" t="s">
-        <v>118</v>
-      </c>
-      <c r="O15" s="91" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="73"/>
-      <c r="B16" s="73"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
-      <c r="G16" s="92" t="n">
-        <v>46202</v>
-      </c>
-      <c r="H16" s="94" t="n">
-        <f aca="false">E2</f>
-        <v>362</v>
-      </c>
-      <c r="I16" s="94" t="n">
-        <f aca="false">F2</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J16" s="95"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="97" t="e">
-        <f aca="false">(K16/C3)/10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M16" s="98" t="n">
-        <v>46199</v>
-      </c>
-      <c r="N16" s="99" t="e">
-        <f aca="false">E4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O16" s="100" t="e">
-        <f aca="false">(N16/C4)/10</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="102"/>
-      <c r="B17" s="103"/>
-      <c r="C17" s="103"/>
-      <c r="D17" s="103"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="101"/>
-      <c r="G17" s="92"/>
+      <c r="A15" s="72"/>
+      <c r="B15" s="151"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="143" t="e">
+        <f aca="false">G15/C15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G15" s="144"/>
+      <c r="H15" s="105" t="n">
+        <f aca="false">(G15/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="120"/>
+      <c r="J15" s="121"/>
+      <c r="K15" s="122"/>
+      <c r="L15" s="122"/>
+      <c r="M15" s="147" t="e">
+        <f aca="false">N15/J15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N15" s="123"/>
+      <c r="O15" s="124" t="n">
+        <f aca="false">(N15/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="126"/>
+      <c r="R15" s="127"/>
+      <c r="S15" s="127"/>
+      <c r="T15" s="150" t="e">
+        <f aca="false">U15/Q15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U15" s="128"/>
+      <c r="V15" s="115" t="n">
+        <f aca="false">(U15/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="72"/>
+      <c r="B16" s="151"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="143" t="e">
+        <f aca="false">G16/C16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G16" s="144"/>
+      <c r="H16" s="105" t="n">
+        <f aca="false">(G16/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="120"/>
+      <c r="J16" s="121"/>
+      <c r="K16" s="122"/>
+      <c r="L16" s="122"/>
+      <c r="M16" s="147" t="e">
+        <f aca="false">N16/J16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N16" s="123"/>
+      <c r="O16" s="124" t="n">
+        <f aca="false">(N16/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="125"/>
+      <c r="Q16" s="126"/>
+      <c r="R16" s="127"/>
+      <c r="S16" s="127"/>
+      <c r="T16" s="150" t="e">
+        <f aca="false">U16/Q16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U16" s="128"/>
+      <c r="V16" s="115" t="n">
+        <f aca="false">(U16/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="72"/>
+      <c r="B17" s="151"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="143" t="e">
+        <f aca="false">G17/C17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G17" s="144"/>
       <c r="H17" s="105" t="n">
-        <f aca="false">E2</f>
-        <v>362</v>
-      </c>
-      <c r="I17" s="94" t="n">
-        <f aca="false">(H17/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J17" s="106"/>
-      <c r="K17" s="107"/>
-      <c r="L17" s="108"/>
-      <c r="M17" s="109"/>
-      <c r="N17" s="110"/>
-      <c r="O17" s="111"/>
+        <f aca="false">(G17/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="120"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="122"/>
+      <c r="L17" s="122"/>
+      <c r="M17" s="147" t="e">
+        <f aca="false">N17/J17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N17" s="123"/>
+      <c r="O17" s="124" t="n">
+        <f aca="false">(N17/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="125"/>
+      <c r="Q17" s="126"/>
+      <c r="R17" s="127"/>
+      <c r="S17" s="127"/>
+      <c r="T17" s="150" t="e">
+        <f aca="false">U17/Q17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U17" s="128"/>
+      <c r="V17" s="115" t="n">
+        <f aca="false">(U17/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="G18" s="104"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="151"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="143" t="e">
+        <f aca="false">G18/C18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G18" s="144"/>
       <c r="H18" s="105" t="n">
-        <f aca="false">H17</f>
-        <v>362</v>
-      </c>
-      <c r="I18" s="94" t="n">
-        <f aca="false">(H18/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J18" s="106"/>
-      <c r="K18" s="107"/>
-      <c r="L18" s="108"/>
-      <c r="M18" s="109"/>
-      <c r="N18" s="110"/>
-      <c r="O18" s="111"/>
+        <f aca="false">(G18/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="120"/>
+      <c r="J18" s="121"/>
+      <c r="K18" s="122"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="147" t="e">
+        <f aca="false">N18/J18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N18" s="123"/>
+      <c r="O18" s="124" t="n">
+        <f aca="false">(N18/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="125"/>
+      <c r="Q18" s="126"/>
+      <c r="R18" s="127"/>
+      <c r="S18" s="127"/>
+      <c r="T18" s="150" t="e">
+        <f aca="false">U18/Q18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U18" s="128"/>
+      <c r="V18" s="115" t="n">
+        <f aca="false">(U18/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="70"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
-      <c r="G19" s="104"/>
+      <c r="A19" s="72"/>
+      <c r="B19" s="151"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="143" t="e">
+        <f aca="false">G19/C19</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G19" s="144"/>
       <c r="H19" s="105" t="n">
-        <f aca="false">H18</f>
-        <v>362</v>
-      </c>
-      <c r="I19" s="94" t="n">
-        <f aca="false">(H19/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J19" s="106"/>
-      <c r="K19" s="107"/>
-      <c r="L19" s="108"/>
-      <c r="M19" s="109"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="111"/>
+        <f aca="false">(G19/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="120"/>
+      <c r="J19" s="121"/>
+      <c r="K19" s="122"/>
+      <c r="L19" s="122"/>
+      <c r="M19" s="147" t="e">
+        <f aca="false">N19/J19</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N19" s="123"/>
+      <c r="O19" s="124" t="n">
+        <f aca="false">(N19/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="125"/>
+      <c r="Q19" s="126"/>
+      <c r="R19" s="127"/>
+      <c r="S19" s="127"/>
+      <c r="T19" s="150" t="e">
+        <f aca="false">U19/Q19</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U19" s="128"/>
+      <c r="V19" s="115" t="n">
+        <f aca="false">(U19/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="70"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="G20" s="104"/>
+      <c r="A20" s="72"/>
+      <c r="B20" s="151"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="143" t="e">
+        <f aca="false">G20/C20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G20" s="144"/>
       <c r="H20" s="105" t="n">
-        <f aca="false">H19</f>
-        <v>362</v>
-      </c>
-      <c r="I20" s="94" t="n">
-        <f aca="false">(H20/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J20" s="106"/>
-      <c r="K20" s="107"/>
-      <c r="L20" s="108"/>
-      <c r="M20" s="109"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="111"/>
+        <f aca="false">(G20/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="120"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="122"/>
+      <c r="L20" s="122"/>
+      <c r="M20" s="147" t="e">
+        <f aca="false">N20/J20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N20" s="123"/>
+      <c r="O20" s="124" t="n">
+        <f aca="false">(N20/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="125"/>
+      <c r="Q20" s="126"/>
+      <c r="R20" s="127"/>
+      <c r="S20" s="127"/>
+      <c r="T20" s="150" t="e">
+        <f aca="false">U20/Q20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U20" s="128"/>
+      <c r="V20" s="115" t="n">
+        <f aca="false">(U20/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="70"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="70"/>
-      <c r="G21" s="104"/>
+      <c r="A21" s="72"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="143" t="e">
+        <f aca="false">G21/C21</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G21" s="144"/>
       <c r="H21" s="105" t="n">
-        <f aca="false">H20</f>
-        <v>362</v>
-      </c>
-      <c r="I21" s="94" t="n">
-        <f aca="false">(H21/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J21" s="106"/>
-      <c r="K21" s="107"/>
-      <c r="L21" s="108"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="110"/>
-      <c r="O21" s="111"/>
+        <f aca="false">(G21/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="120"/>
+      <c r="J21" s="121"/>
+      <c r="K21" s="122"/>
+      <c r="L21" s="122"/>
+      <c r="M21" s="147" t="e">
+        <f aca="false">N21/J21</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N21" s="123"/>
+      <c r="O21" s="124" t="n">
+        <f aca="false">(N21/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P21" s="125"/>
+      <c r="Q21" s="126"/>
+      <c r="R21" s="127"/>
+      <c r="S21" s="127"/>
+      <c r="T21" s="150" t="e">
+        <f aca="false">U21/Q21</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U21" s="128"/>
+      <c r="V21" s="115" t="n">
+        <f aca="false">(U21/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="70"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
-      <c r="G22" s="104"/>
+      <c r="A22" s="72"/>
+      <c r="B22" s="151"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="143" t="e">
+        <f aca="false">G22/C22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G22" s="144"/>
       <c r="H22" s="105" t="n">
-        <f aca="false">H21</f>
-        <v>362</v>
-      </c>
-      <c r="I22" s="94" t="n">
-        <f aca="false">(H22/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J22" s="106"/>
-      <c r="K22" s="107"/>
-      <c r="L22" s="108"/>
-      <c r="M22" s="109"/>
-      <c r="N22" s="110"/>
-      <c r="O22" s="111"/>
+        <f aca="false">(G22/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="120"/>
+      <c r="J22" s="121"/>
+      <c r="K22" s="122"/>
+      <c r="L22" s="122"/>
+      <c r="M22" s="147" t="e">
+        <f aca="false">N22/J22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N22" s="123"/>
+      <c r="O22" s="124" t="n">
+        <f aca="false">(N22/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P22" s="125"/>
+      <c r="Q22" s="126"/>
+      <c r="R22" s="127"/>
+      <c r="S22" s="127"/>
+      <c r="T22" s="150" t="e">
+        <f aca="false">U22/Q22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U22" s="128"/>
+      <c r="V22" s="115" t="n">
+        <f aca="false">(U22/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="70"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
-      <c r="G23" s="104"/>
+      <c r="A23" s="72"/>
+      <c r="B23" s="151"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="143" t="e">
+        <f aca="false">G23/C23</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G23" s="144"/>
       <c r="H23" s="105" t="n">
-        <f aca="false">H22</f>
-        <v>362</v>
-      </c>
-      <c r="I23" s="94" t="n">
-        <f aca="false">(H23/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J23" s="106"/>
-      <c r="K23" s="107"/>
-      <c r="L23" s="108"/>
-      <c r="M23" s="109"/>
-      <c r="N23" s="110"/>
-      <c r="O23" s="111"/>
+        <f aca="false">(G23/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="120"/>
+      <c r="J23" s="121"/>
+      <c r="K23" s="122"/>
+      <c r="L23" s="122"/>
+      <c r="M23" s="147" t="e">
+        <f aca="false">N23/J23</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N23" s="123"/>
+      <c r="O23" s="124" t="n">
+        <f aca="false">(N23/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P23" s="125"/>
+      <c r="Q23" s="126"/>
+      <c r="R23" s="127"/>
+      <c r="S23" s="127"/>
+      <c r="T23" s="150" t="e">
+        <f aca="false">U23/Q23</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U23" s="128"/>
+      <c r="V23" s="115" t="n">
+        <f aca="false">(U23/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="70"/>
-      <c r="C24" s="70"/>
-      <c r="D24" s="70"/>
-      <c r="G24" s="104"/>
+      <c r="A24" s="72"/>
+      <c r="B24" s="151"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="143" t="e">
+        <f aca="false">G24/C24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G24" s="144"/>
       <c r="H24" s="105" t="n">
-        <f aca="false">H23</f>
-        <v>362</v>
-      </c>
-      <c r="I24" s="94" t="n">
-        <f aca="false">(H24/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J24" s="106"/>
-      <c r="K24" s="107"/>
-      <c r="L24" s="108"/>
-      <c r="M24" s="109"/>
-      <c r="N24" s="110"/>
-      <c r="O24" s="111"/>
+        <f aca="false">(G24/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="120"/>
+      <c r="J24" s="121"/>
+      <c r="K24" s="122"/>
+      <c r="L24" s="122"/>
+      <c r="M24" s="147" t="e">
+        <f aca="false">N24/J24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N24" s="123"/>
+      <c r="O24" s="124" t="n">
+        <f aca="false">(N24/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="125"/>
+      <c r="Q24" s="126"/>
+      <c r="R24" s="127"/>
+      <c r="S24" s="127"/>
+      <c r="T24" s="150" t="e">
+        <f aca="false">U24/Q24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U24" s="128"/>
+      <c r="V24" s="115" t="n">
+        <f aca="false">(U24/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="70"/>
-      <c r="C25" s="70"/>
-      <c r="D25" s="70"/>
-      <c r="G25" s="104"/>
+      <c r="A25" s="72"/>
+      <c r="B25" s="151"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="143" t="e">
+        <f aca="false">G25/C25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G25" s="144"/>
       <c r="H25" s="105" t="n">
-        <f aca="false">H24</f>
-        <v>362</v>
-      </c>
-      <c r="I25" s="94" t="n">
-        <f aca="false">(H25/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J25" s="106"/>
-      <c r="K25" s="107"/>
-      <c r="L25" s="108"/>
-      <c r="M25" s="109"/>
-      <c r="N25" s="110"/>
-      <c r="O25" s="111"/>
+        <f aca="false">(G25/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="120"/>
+      <c r="J25" s="121"/>
+      <c r="K25" s="122"/>
+      <c r="L25" s="122"/>
+      <c r="M25" s="147" t="e">
+        <f aca="false">N25/J25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N25" s="123"/>
+      <c r="O25" s="124" t="n">
+        <f aca="false">(N25/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="125"/>
+      <c r="Q25" s="126"/>
+      <c r="R25" s="127"/>
+      <c r="S25" s="127"/>
+      <c r="T25" s="150" t="e">
+        <f aca="false">U25/Q25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U25" s="128"/>
+      <c r="V25" s="115" t="n">
+        <f aca="false">(U25/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="70"/>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
-      <c r="G26" s="104"/>
+      <c r="A26" s="72"/>
+      <c r="B26" s="151"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="118"/>
+      <c r="F26" s="143" t="e">
+        <f aca="false">G26/C26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G26" s="144"/>
       <c r="H26" s="105" t="n">
-        <f aca="false">H25</f>
-        <v>362</v>
-      </c>
-      <c r="I26" s="94" t="n">
-        <f aca="false">(H26/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J26" s="106"/>
-      <c r="K26" s="107"/>
-      <c r="L26" s="108"/>
-      <c r="M26" s="109"/>
-      <c r="N26" s="110"/>
-      <c r="O26" s="111"/>
+        <f aca="false">(G26/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="120"/>
+      <c r="J26" s="121"/>
+      <c r="K26" s="122"/>
+      <c r="L26" s="122"/>
+      <c r="M26" s="147" t="e">
+        <f aca="false">N26/J26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N26" s="123"/>
+      <c r="O26" s="124" t="n">
+        <f aca="false">(N26/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P26" s="125"/>
+      <c r="Q26" s="126"/>
+      <c r="R26" s="127"/>
+      <c r="S26" s="127"/>
+      <c r="T26" s="150" t="e">
+        <f aca="false">U26/Q26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U26" s="128"/>
+      <c r="V26" s="115" t="n">
+        <f aca="false">(U26/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="70"/>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
-      <c r="G27" s="104"/>
+      <c r="A27" s="72"/>
+      <c r="B27" s="151"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="118"/>
+      <c r="E27" s="118"/>
+      <c r="F27" s="143" t="e">
+        <f aca="false">G27/C27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G27" s="144"/>
       <c r="H27" s="105" t="n">
-        <f aca="false">H26</f>
-        <v>362</v>
-      </c>
-      <c r="I27" s="94" t="n">
-        <f aca="false">(H27/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J27" s="106"/>
-      <c r="K27" s="107"/>
-      <c r="L27" s="108"/>
-      <c r="M27" s="109"/>
-      <c r="N27" s="110"/>
-      <c r="O27" s="111"/>
+        <f aca="false">(G27/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="120"/>
+      <c r="J27" s="121"/>
+      <c r="K27" s="122"/>
+      <c r="L27" s="122"/>
+      <c r="M27" s="147" t="e">
+        <f aca="false">N27/J27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N27" s="123"/>
+      <c r="O27" s="124" t="n">
+        <f aca="false">(N27/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P27" s="125"/>
+      <c r="Q27" s="126"/>
+      <c r="R27" s="127"/>
+      <c r="S27" s="127"/>
+      <c r="T27" s="150" t="e">
+        <f aca="false">U27/Q27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U27" s="128"/>
+      <c r="V27" s="115" t="n">
+        <f aca="false">(U27/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="70"/>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
-      <c r="G28" s="104"/>
+      <c r="A28" s="72"/>
+      <c r="B28" s="151"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="118"/>
+      <c r="E28" s="118"/>
+      <c r="F28" s="143" t="e">
+        <f aca="false">G28/C28</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G28" s="144"/>
       <c r="H28" s="105" t="n">
-        <f aca="false">H27</f>
-        <v>362</v>
-      </c>
-      <c r="I28" s="94" t="n">
-        <f aca="false">(H28/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J28" s="106"/>
-      <c r="K28" s="107"/>
-      <c r="L28" s="108"/>
-      <c r="M28" s="109"/>
-      <c r="N28" s="110"/>
-      <c r="O28" s="111"/>
+        <f aca="false">(G28/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="120"/>
+      <c r="J28" s="121"/>
+      <c r="K28" s="122"/>
+      <c r="L28" s="122"/>
+      <c r="M28" s="147" t="e">
+        <f aca="false">N28/J28</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N28" s="123"/>
+      <c r="O28" s="124" t="n">
+        <f aca="false">(N28/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P28" s="125"/>
+      <c r="Q28" s="126"/>
+      <c r="R28" s="127"/>
+      <c r="S28" s="127"/>
+      <c r="T28" s="150" t="e">
+        <f aca="false">U28/Q28</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U28" s="128"/>
+      <c r="V28" s="115" t="n">
+        <f aca="false">(U28/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="70"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="70"/>
-      <c r="G29" s="104"/>
+      <c r="A29" s="72"/>
+      <c r="B29" s="151"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="118"/>
+      <c r="E29" s="118"/>
+      <c r="F29" s="143" t="e">
+        <f aca="false">G29/C29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G29" s="144"/>
       <c r="H29" s="105" t="n">
-        <f aca="false">H28</f>
-        <v>362</v>
-      </c>
-      <c r="I29" s="94" t="n">
-        <f aca="false">(H29/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J29" s="106"/>
-      <c r="K29" s="107"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="109"/>
-      <c r="N29" s="110"/>
-      <c r="O29" s="111"/>
+        <f aca="false">(G29/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="120"/>
+      <c r="J29" s="121"/>
+      <c r="K29" s="122"/>
+      <c r="L29" s="122"/>
+      <c r="M29" s="147" t="e">
+        <f aca="false">N29/J29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N29" s="123"/>
+      <c r="O29" s="124" t="n">
+        <f aca="false">(N29/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P29" s="125"/>
+      <c r="Q29" s="126"/>
+      <c r="R29" s="127"/>
+      <c r="S29" s="127"/>
+      <c r="T29" s="150" t="e">
+        <f aca="false">U29/Q29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U29" s="128"/>
+      <c r="V29" s="115" t="n">
+        <f aca="false">(U29/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="70"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="G30" s="104"/>
+      <c r="A30" s="72"/>
+      <c r="B30" s="151"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="143" t="e">
+        <f aca="false">G30/C30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G30" s="144"/>
       <c r="H30" s="105" t="n">
-        <f aca="false">H29</f>
-        <v>362</v>
-      </c>
-      <c r="I30" s="94" t="n">
-        <f aca="false">(H30/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J30" s="106"/>
-      <c r="K30" s="107"/>
-      <c r="L30" s="108"/>
-      <c r="M30" s="109"/>
-      <c r="N30" s="110"/>
-      <c r="O30" s="111"/>
+        <f aca="false">(G30/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="120"/>
+      <c r="J30" s="121"/>
+      <c r="K30" s="122"/>
+      <c r="L30" s="122"/>
+      <c r="M30" s="147" t="e">
+        <f aca="false">N30/J30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N30" s="123"/>
+      <c r="O30" s="124" t="n">
+        <f aca="false">(N30/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P30" s="125"/>
+      <c r="Q30" s="126"/>
+      <c r="R30" s="127"/>
+      <c r="S30" s="127"/>
+      <c r="T30" s="150" t="e">
+        <f aca="false">U30/Q30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U30" s="128"/>
+      <c r="V30" s="115" t="n">
+        <f aca="false">(U30/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="70"/>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
-      <c r="G31" s="104"/>
+      <c r="A31" s="72"/>
+      <c r="B31" s="151"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="118"/>
+      <c r="E31" s="118"/>
+      <c r="F31" s="143" t="e">
+        <f aca="false">G31/C31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G31" s="144"/>
       <c r="H31" s="105" t="n">
-        <f aca="false">H30</f>
-        <v>362</v>
-      </c>
-      <c r="I31" s="94" t="n">
-        <f aca="false">(H31/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J31" s="106"/>
-      <c r="K31" s="107"/>
-      <c r="L31" s="108"/>
-      <c r="M31" s="109"/>
-      <c r="N31" s="110"/>
-      <c r="O31" s="111"/>
+        <f aca="false">(G31/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="120"/>
+      <c r="J31" s="121"/>
+      <c r="K31" s="122"/>
+      <c r="L31" s="122"/>
+      <c r="M31" s="147" t="e">
+        <f aca="false">N31/J31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N31" s="123"/>
+      <c r="O31" s="124" t="n">
+        <f aca="false">(N31/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="125"/>
+      <c r="Q31" s="126"/>
+      <c r="R31" s="127"/>
+      <c r="S31" s="127"/>
+      <c r="T31" s="150" t="e">
+        <f aca="false">U31/Q31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U31" s="128"/>
+      <c r="V31" s="115" t="n">
+        <f aca="false">(U31/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="70"/>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
-      <c r="G32" s="104"/>
+      <c r="A32" s="72"/>
+      <c r="B32" s="151"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="143" t="e">
+        <f aca="false">G32/C32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G32" s="144"/>
       <c r="H32" s="105" t="n">
-        <f aca="false">H31</f>
-        <v>362</v>
-      </c>
-      <c r="I32" s="94" t="n">
-        <f aca="false">(H32/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J32" s="106"/>
-      <c r="K32" s="107"/>
-      <c r="L32" s="108"/>
-      <c r="M32" s="109"/>
-      <c r="N32" s="110"/>
-      <c r="O32" s="111"/>
+        <f aca="false">(G32/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="120"/>
+      <c r="J32" s="121"/>
+      <c r="K32" s="122"/>
+      <c r="L32" s="122"/>
+      <c r="M32" s="147" t="e">
+        <f aca="false">N32/J32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N32" s="123"/>
+      <c r="O32" s="124" t="n">
+        <f aca="false">(N32/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P32" s="125"/>
+      <c r="Q32" s="126"/>
+      <c r="R32" s="127"/>
+      <c r="S32" s="127"/>
+      <c r="T32" s="150" t="e">
+        <f aca="false">U32/Q32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U32" s="128"/>
+      <c r="V32" s="115" t="n">
+        <f aca="false">(U32/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="70"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="G33" s="104"/>
+      <c r="A33" s="72"/>
+      <c r="B33" s="151"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="118"/>
+      <c r="E33" s="118"/>
+      <c r="F33" s="143" t="e">
+        <f aca="false">G33/C33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G33" s="144"/>
       <c r="H33" s="105" t="n">
-        <f aca="false">H32</f>
-        <v>362</v>
-      </c>
-      <c r="I33" s="94" t="n">
-        <f aca="false">(H33/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J33" s="106"/>
-      <c r="K33" s="107"/>
-      <c r="L33" s="108"/>
-      <c r="M33" s="109"/>
-      <c r="N33" s="110"/>
-      <c r="O33" s="111"/>
+        <f aca="false">(G33/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="120"/>
+      <c r="J33" s="121"/>
+      <c r="K33" s="122"/>
+      <c r="L33" s="122"/>
+      <c r="M33" s="147" t="e">
+        <f aca="false">N33/J33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N33" s="123"/>
+      <c r="O33" s="124" t="n">
+        <f aca="false">(N33/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P33" s="125"/>
+      <c r="Q33" s="126"/>
+      <c r="R33" s="127"/>
+      <c r="S33" s="127"/>
+      <c r="T33" s="150" t="e">
+        <f aca="false">U33/Q33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U33" s="128"/>
+      <c r="V33" s="115" t="n">
+        <f aca="false">(U33/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="70"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
-      <c r="G34" s="104"/>
+      <c r="A34" s="72"/>
+      <c r="B34" s="152"/>
+      <c r="C34" s="153"/>
+      <c r="D34" s="154"/>
+      <c r="E34" s="154"/>
+      <c r="F34" s="143" t="e">
+        <f aca="false">G34/C34</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G34" s="155"/>
       <c r="H34" s="105" t="n">
-        <f aca="false">H33</f>
-        <v>362</v>
-      </c>
-      <c r="I34" s="94" t="n">
-        <f aca="false">(H34/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J34" s="106"/>
-      <c r="K34" s="107"/>
-      <c r="L34" s="108"/>
-      <c r="M34" s="109"/>
-      <c r="N34" s="110"/>
-      <c r="O34" s="111"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="115"/>
-      <c r="C35" s="115"/>
-      <c r="D35" s="115"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="105" t="n">
-        <f aca="false">H34</f>
-        <v>362</v>
-      </c>
-      <c r="I35" s="94" t="n">
-        <f aca="false">(H35/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J35" s="106"/>
-      <c r="K35" s="107"/>
-      <c r="L35" s="108"/>
-      <c r="M35" s="109"/>
-      <c r="N35" s="110"/>
-      <c r="O35" s="111"/>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="115"/>
-      <c r="C36" s="115"/>
-      <c r="D36" s="115"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="105" t="n">
-        <f aca="false">H35</f>
-        <v>362</v>
-      </c>
-      <c r="I36" s="94" t="n">
-        <f aca="false">(H36/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J36" s="106"/>
-      <c r="K36" s="107"/>
-      <c r="L36" s="108"/>
-      <c r="M36" s="109"/>
-      <c r="N36" s="110"/>
-      <c r="O36" s="111"/>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="104"/>
-      <c r="H37" s="105" t="n">
-        <f aca="false">H36</f>
-        <v>362</v>
-      </c>
-      <c r="I37" s="94" t="n">
-        <f aca="false">(H37/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J37" s="106"/>
-      <c r="K37" s="107"/>
-      <c r="L37" s="108"/>
-      <c r="M37" s="109"/>
-      <c r="N37" s="110"/>
-      <c r="O37" s="111"/>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="104"/>
-      <c r="H38" s="105" t="n">
-        <f aca="false">H37</f>
-        <v>362</v>
-      </c>
-      <c r="I38" s="94" t="n">
-        <f aca="false">(H38/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J38" s="106"/>
-      <c r="K38" s="107"/>
-      <c r="L38" s="108"/>
-      <c r="M38" s="109"/>
-      <c r="N38" s="110"/>
-      <c r="O38" s="111"/>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="104"/>
-      <c r="H39" s="105" t="n">
-        <f aca="false">H38</f>
-        <v>362</v>
-      </c>
-      <c r="I39" s="94" t="n">
-        <f aca="false">(H39/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J39" s="106"/>
-      <c r="K39" s="107"/>
-      <c r="L39" s="108"/>
-      <c r="M39" s="109"/>
-      <c r="N39" s="110"/>
-      <c r="O39" s="111"/>
-    </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="104"/>
-      <c r="H40" s="105" t="n">
-        <f aca="false">H39</f>
-        <v>362</v>
-      </c>
-      <c r="I40" s="94" t="n">
-        <f aca="false">(H40/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J40" s="106"/>
-      <c r="K40" s="107"/>
-      <c r="L40" s="108"/>
-      <c r="M40" s="109"/>
-      <c r="N40" s="110"/>
-      <c r="O40" s="111"/>
-    </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="104"/>
-      <c r="H41" s="105" t="n">
-        <f aca="false">H40</f>
-        <v>362</v>
-      </c>
-      <c r="I41" s="94" t="n">
-        <f aca="false">(H41/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J41" s="106"/>
-      <c r="K41" s="107"/>
-      <c r="L41" s="108"/>
-      <c r="M41" s="109"/>
-      <c r="N41" s="110"/>
-      <c r="O41" s="111"/>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="104"/>
-      <c r="H42" s="105" t="n">
-        <f aca="false">H41</f>
-        <v>362</v>
-      </c>
-      <c r="I42" s="94" t="n">
-        <f aca="false">(H42/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J42" s="106"/>
-      <c r="K42" s="107"/>
-      <c r="L42" s="108"/>
-      <c r="M42" s="109"/>
-      <c r="N42" s="110"/>
-      <c r="O42" s="111"/>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G43" s="104"/>
-      <c r="H43" s="105" t="n">
-        <f aca="false">H42</f>
-        <v>362</v>
-      </c>
-      <c r="I43" s="94" t="n">
-        <f aca="false">(H43/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J43" s="106"/>
-      <c r="K43" s="107"/>
-      <c r="L43" s="108"/>
-      <c r="M43" s="109"/>
-      <c r="N43" s="110"/>
-      <c r="O43" s="111"/>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G44" s="104"/>
-      <c r="H44" s="105" t="n">
-        <f aca="false">H43</f>
-        <v>362</v>
-      </c>
-      <c r="I44" s="94" t="n">
-        <f aca="false">(H44/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J44" s="106"/>
-      <c r="K44" s="107"/>
-      <c r="L44" s="108"/>
-      <c r="M44" s="109"/>
-      <c r="N44" s="110"/>
-      <c r="O44" s="111"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G45" s="116"/>
-      <c r="H45" s="105" t="n">
-        <f aca="false">H44</f>
-        <v>362</v>
-      </c>
-      <c r="I45" s="94" t="n">
-        <f aca="false">(H45/C2)/10</f>
-        <v>51.7142857142857</v>
-      </c>
-      <c r="J45" s="117"/>
-      <c r="K45" s="118"/>
-      <c r="L45" s="119"/>
-      <c r="M45" s="120"/>
-      <c r="N45" s="121"/>
-      <c r="O45" s="122"/>
-    </row>
+        <f aca="false">(G34/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="156"/>
+      <c r="J34" s="157"/>
+      <c r="K34" s="158"/>
+      <c r="L34" s="158"/>
+      <c r="M34" s="147" t="e">
+        <f aca="false">N34/J34</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N34" s="159"/>
+      <c r="O34" s="124" t="n">
+        <f aca="false">(N34/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P34" s="160"/>
+      <c r="Q34" s="161"/>
+      <c r="R34" s="162"/>
+      <c r="S34" s="162"/>
+      <c r="T34" s="150" t="e">
+        <f aca="false">U34/Q34</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U34" s="163"/>
+      <c r="V34" s="115" t="n">
+        <f aca="false">(U34/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:O14"/>
+  <mergeCells count="24">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="P2:V2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="U3:V3"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -5095,641 +6660,1483 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFDDDDDD"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:V1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="15.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="16.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="22" width="20.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="22" width="21.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="22" width="16.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="22" width="20.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="70" width="15.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="71" width="14.92"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="9" style="71" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="10" style="72" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="71" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.66"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="73"/>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="72"/>
       <c r="B1" s="74" t="s">
-        <v>105</v>
-      </c>
-      <c r="C1" s="74" t="s">
-        <v>106</v>
-      </c>
-      <c r="D1" s="74" t="s">
-        <v>121</v>
-      </c>
-      <c r="E1" s="74" t="s">
-        <v>108</v>
-      </c>
-      <c r="F1" s="74" t="s">
-        <v>109</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="75" t="s">
+        <v>126</v>
+      </c>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="76" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
+      <c r="V1" s="76"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="67" t="s">
-        <v>122</v>
-      </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="76" t="n">
-        <f aca="false">(E2/C2)/10</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="68" t="s">
-        <v>123</v>
-      </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="76" t="n">
-        <f aca="false">(E3/C3)/10</f>
+      <c r="A2" s="77" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="78" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="166" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
+      <c r="L2" s="166"/>
+      <c r="M2" s="166"/>
+      <c r="N2" s="166"/>
+      <c r="O2" s="166"/>
+      <c r="P2" s="80" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="72"/>
+      <c r="B3" s="86" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="86" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="87" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="88" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" s="88"/>
+      <c r="I3" s="89" t="s">
+        <v>110</v>
+      </c>
+      <c r="J3" s="89" t="s">
+        <v>111</v>
+      </c>
+      <c r="K3" s="90" t="s">
+        <v>112</v>
+      </c>
+      <c r="L3" s="89" t="s">
+        <v>113</v>
+      </c>
+      <c r="M3" s="89" t="s">
+        <v>114</v>
+      </c>
+      <c r="N3" s="91" t="s">
+        <v>115</v>
+      </c>
+      <c r="O3" s="91"/>
+      <c r="P3" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q3" s="92" t="s">
+        <v>111</v>
+      </c>
+      <c r="R3" s="93" t="s">
+        <v>112</v>
+      </c>
+      <c r="S3" s="92" t="s">
+        <v>113</v>
+      </c>
+      <c r="T3" s="92" t="s">
+        <v>114</v>
+      </c>
+      <c r="U3" s="94" t="s">
+        <v>115</v>
+      </c>
+      <c r="V3" s="94"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="95" t="s">
+        <v>116</v>
+      </c>
+      <c r="H4" s="96" t="s">
+        <v>117</v>
+      </c>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="97" t="s">
+        <v>116</v>
+      </c>
+      <c r="O4" s="98" t="s">
+        <v>117</v>
+      </c>
+      <c r="P4" s="92"/>
+      <c r="Q4" s="92"/>
+      <c r="R4" s="92"/>
+      <c r="S4" s="92"/>
+      <c r="T4" s="92"/>
+      <c r="U4" s="99" t="s">
+        <v>116</v>
+      </c>
+      <c r="V4" s="100" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="101"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="105" t="n">
+        <f aca="false">(G5/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="106"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="108"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="109"/>
+      <c r="O5" s="110" t="n">
+        <f aca="false">(N5/1.69)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="111"/>
+      <c r="Q5" s="112"/>
+      <c r="R5" s="113"/>
+      <c r="S5" s="113"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="114"/>
+      <c r="V5" s="115" t="n">
+        <f aca="false">(U5/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="116"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="105" t="n">
+        <f aca="false">(G6/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="120"/>
+      <c r="J6" s="121"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="122"/>
+      <c r="N6" s="123"/>
+      <c r="O6" s="124"/>
+      <c r="P6" s="125"/>
+      <c r="Q6" s="126"/>
+      <c r="R6" s="127"/>
+      <c r="S6" s="127"/>
+      <c r="T6" s="127"/>
+      <c r="U6" s="128"/>
+      <c r="V6" s="115" t="n">
+        <f aca="false">(U6/0.51)/10</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="73"/>
-      <c r="B7" s="73" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="73" t="s">
-        <v>111</v>
-      </c>
-      <c r="D7" s="73" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" s="73" t="s">
-        <v>113</v>
+      <c r="A7" s="72"/>
+      <c r="B7" s="129" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="130"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="132" t="n">
+        <f aca="false">SUM(G5:G6)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="133" t="n">
+        <f aca="false">(G7/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="134"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="136"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="136"/>
+      <c r="N7" s="134" t="n">
+        <f aca="false">SUM(N5:N6)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="134" t="n">
+        <f aca="false">SUM(O5:O6)</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="137"/>
+      <c r="Q7" s="138"/>
+      <c r="R7" s="139"/>
+      <c r="S7" s="139"/>
+      <c r="T7" s="139"/>
+      <c r="U7" s="137" t="n">
+        <f aca="false">SUM(U5:U6)</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="140" t="n">
+        <f aca="false">(U7/0.51)/10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="73"/>
-      <c r="E8" s="1" t="e">
-        <f aca="false">E2/D2</f>
-        <v>#DIV/0!</v>
+      <c r="A8" s="72"/>
+      <c r="B8" s="141"/>
+      <c r="C8" s="142"/>
+      <c r="D8" s="143"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="143" t="e">
+        <f aca="false">G8/C8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G8" s="144"/>
+      <c r="H8" s="105" t="n">
+        <f aca="false">(G8/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="145"/>
+      <c r="J8" s="146"/>
+      <c r="K8" s="167"/>
+      <c r="L8" s="147"/>
+      <c r="M8" s="147" t="e">
+        <f aca="false">N8/J8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" s="123"/>
+      <c r="O8" s="124" t="n">
+        <f aca="false">(N8/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="148"/>
+      <c r="Q8" s="149"/>
+      <c r="R8" s="150"/>
+      <c r="S8" s="150"/>
+      <c r="T8" s="150" t="e">
+        <f aca="false">U8/Q8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U8" s="128"/>
+      <c r="V8" s="115" t="n">
+        <f aca="false">(U8/0.1)/10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="73"/>
+      <c r="A9" s="72"/>
+      <c r="B9" s="151"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="143" t="e">
+        <f aca="false">G9/C9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G9" s="144"/>
+      <c r="H9" s="105" t="n">
+        <f aca="false">(G9/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="120"/>
+      <c r="J9" s="121"/>
+      <c r="K9" s="122"/>
+      <c r="L9" s="122"/>
+      <c r="M9" s="147" t="e">
+        <f aca="false">N9/J9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N9" s="123"/>
+      <c r="O9" s="124" t="n">
+        <f aca="false">(N9/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="125"/>
+      <c r="Q9" s="126"/>
+      <c r="R9" s="127"/>
+      <c r="S9" s="127"/>
+      <c r="T9" s="150" t="e">
+        <f aca="false">U9/Q9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U9" s="128"/>
+      <c r="V9" s="115" t="n">
+        <f aca="false">(U9/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="72"/>
+      <c r="B10" s="151"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
+      <c r="F10" s="143" t="e">
+        <f aca="false">G10/C10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G10" s="144"/>
+      <c r="H10" s="105" t="n">
+        <f aca="false">(G10/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="120"/>
+      <c r="J10" s="121"/>
+      <c r="K10" s="122"/>
+      <c r="L10" s="122"/>
+      <c r="M10" s="147" t="e">
+        <f aca="false">N10/J10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N10" s="123"/>
+      <c r="O10" s="124" t="n">
+        <f aca="false">(N10/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P10" s="125"/>
+      <c r="Q10" s="126"/>
+      <c r="R10" s="127"/>
+      <c r="S10" s="127"/>
+      <c r="T10" s="150" t="e">
+        <f aca="false">U10/Q10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U10" s="128"/>
+      <c r="V10" s="115" t="n">
+        <f aca="false">(U10/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="72"/>
+      <c r="B11" s="151"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118"/>
+      <c r="F11" s="143" t="e">
+        <f aca="false">G11/C11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G11" s="144"/>
+      <c r="H11" s="105" t="n">
+        <f aca="false">(G11/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="120"/>
+      <c r="J11" s="121"/>
+      <c r="K11" s="122"/>
+      <c r="L11" s="122"/>
+      <c r="M11" s="147" t="e">
+        <f aca="false">N11/J11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N11" s="123"/>
+      <c r="O11" s="124" t="n">
+        <f aca="false">(N11/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="125"/>
+      <c r="Q11" s="126"/>
+      <c r="R11" s="127"/>
+      <c r="S11" s="127"/>
+      <c r="T11" s="150" t="e">
+        <f aca="false">U11/Q11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U11" s="128"/>
+      <c r="V11" s="115" t="n">
+        <f aca="false">(U11/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G12" s="77" t="s">
-        <v>122</v>
-      </c>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="78" t="s">
-        <v>123</v>
-      </c>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
+      <c r="A12" s="72"/>
+      <c r="B12" s="151"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="143" t="e">
+        <f aca="false">G12/C12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G12" s="144"/>
+      <c r="H12" s="105" t="n">
+        <f aca="false">(G12/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="120"/>
+      <c r="J12" s="121"/>
+      <c r="K12" s="122"/>
+      <c r="L12" s="122"/>
+      <c r="M12" s="147" t="e">
+        <f aca="false">N12/J12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N12" s="123"/>
+      <c r="O12" s="124" t="n">
+        <f aca="false">(N12/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="125"/>
+      <c r="Q12" s="126"/>
+      <c r="R12" s="127"/>
+      <c r="S12" s="127"/>
+      <c r="T12" s="150" t="e">
+        <f aca="false">U12/Q12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U12" s="128"/>
+      <c r="V12" s="115" t="n">
+        <f aca="false">(U12/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G13" s="80" t="s">
-        <v>116</v>
-      </c>
-      <c r="H13" s="81" t="s">
-        <v>117</v>
-      </c>
-      <c r="I13" s="81"/>
-      <c r="J13" s="82" t="s">
-        <v>116</v>
-      </c>
-      <c r="K13" s="83" t="s">
-        <v>117</v>
-      </c>
-      <c r="L13" s="83"/>
+      <c r="A13" s="72"/>
+      <c r="B13" s="151"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="143" t="e">
+        <f aca="false">G13/C13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G13" s="144"/>
+      <c r="H13" s="105" t="n">
+        <f aca="false">(G13/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="120"/>
+      <c r="J13" s="121"/>
+      <c r="K13" s="122"/>
+      <c r="L13" s="122"/>
+      <c r="M13" s="147" t="e">
+        <f aca="false">N13/J13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N13" s="123"/>
+      <c r="O13" s="124" t="n">
+        <f aca="false">(N13/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="125"/>
+      <c r="Q13" s="126"/>
+      <c r="R13" s="127"/>
+      <c r="S13" s="127"/>
+      <c r="T13" s="150" t="e">
+        <f aca="false">U13/Q13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U13" s="128"/>
+      <c r="V13" s="115" t="n">
+        <f aca="false">(U13/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G14" s="80"/>
-      <c r="H14" s="86" t="s">
-        <v>118</v>
-      </c>
-      <c r="I14" s="87" t="s">
-        <v>119</v>
-      </c>
-      <c r="J14" s="82"/>
-      <c r="K14" s="88" t="s">
-        <v>118</v>
-      </c>
-      <c r="L14" s="89" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="73"/>
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="G15" s="92" t="n">
-        <v>46202</v>
-      </c>
-      <c r="H15" s="94" t="n">
-        <f aca="false">E2</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="94" t="n">
-        <f aca="false">F2</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="95"/>
-      <c r="K15" s="96"/>
-      <c r="L15" s="97" t="n">
-        <f aca="false">(K15/C3)/10</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="102"/>
-      <c r="B16" s="103"/>
-      <c r="C16" s="103"/>
-      <c r="D16" s="103"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="101"/>
-      <c r="G16" s="92"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="151"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="143" t="e">
+        <f aca="false">G14/C14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G14" s="144"/>
+      <c r="H14" s="105" t="n">
+        <f aca="false">(G14/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="120"/>
+      <c r="J14" s="121"/>
+      <c r="K14" s="122"/>
+      <c r="L14" s="122"/>
+      <c r="M14" s="147" t="e">
+        <f aca="false">N14/J14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N14" s="123"/>
+      <c r="O14" s="124" t="n">
+        <f aca="false">(N14/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="125"/>
+      <c r="Q14" s="126"/>
+      <c r="R14" s="127"/>
+      <c r="S14" s="127"/>
+      <c r="T14" s="150" t="e">
+        <f aca="false">U14/Q14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U14" s="128"/>
+      <c r="V14" s="115" t="n">
+        <f aca="false">(U14/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="72"/>
+      <c r="B15" s="151"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="143" t="e">
+        <f aca="false">G15/C15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G15" s="144"/>
+      <c r="H15" s="105" t="n">
+        <f aca="false">(G15/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="120"/>
+      <c r="J15" s="121"/>
+      <c r="K15" s="122"/>
+      <c r="L15" s="122"/>
+      <c r="M15" s="147" t="e">
+        <f aca="false">N15/J15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N15" s="123"/>
+      <c r="O15" s="124" t="n">
+        <f aca="false">(N15/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="125"/>
+      <c r="Q15" s="126"/>
+      <c r="R15" s="127"/>
+      <c r="S15" s="127"/>
+      <c r="T15" s="150" t="e">
+        <f aca="false">U15/Q15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U15" s="128"/>
+      <c r="V15" s="115" t="n">
+        <f aca="false">(U15/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="72"/>
+      <c r="B16" s="151"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="143" t="e">
+        <f aca="false">G16/C16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G16" s="144"/>
       <c r="H16" s="105" t="n">
-        <f aca="false">E2</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="94" t="n">
-        <f aca="false">(H16/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="106"/>
-      <c r="K16" s="107"/>
-      <c r="L16" s="108"/>
+        <f aca="false">(G16/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="120"/>
+      <c r="J16" s="121"/>
+      <c r="K16" s="122"/>
+      <c r="L16" s="122"/>
+      <c r="M16" s="147" t="e">
+        <f aca="false">N16/J16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N16" s="123"/>
+      <c r="O16" s="124" t="n">
+        <f aca="false">(N16/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="125"/>
+      <c r="Q16" s="126"/>
+      <c r="R16" s="127"/>
+      <c r="S16" s="127"/>
+      <c r="T16" s="150" t="e">
+        <f aca="false">U16/Q16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U16" s="128"/>
+      <c r="V16" s="115" t="n">
+        <f aca="false">(U16/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="70"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="G17" s="104"/>
+      <c r="A17" s="72"/>
+      <c r="B17" s="151"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="143" t="e">
+        <f aca="false">G17/C17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G17" s="144"/>
       <c r="H17" s="105" t="n">
-        <f aca="false">H16</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="94" t="n">
-        <f aca="false">(H17/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="106"/>
-      <c r="K17" s="107"/>
-      <c r="L17" s="108"/>
+        <f aca="false">(G17/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="120"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="122"/>
+      <c r="L17" s="122"/>
+      <c r="M17" s="147" t="e">
+        <f aca="false">N17/J17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N17" s="123"/>
+      <c r="O17" s="124" t="n">
+        <f aca="false">(N17/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="125"/>
+      <c r="Q17" s="126"/>
+      <c r="R17" s="127"/>
+      <c r="S17" s="127"/>
+      <c r="T17" s="150" t="e">
+        <f aca="false">U17/Q17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U17" s="128"/>
+      <c r="V17" s="115" t="n">
+        <f aca="false">(U17/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="G18" s="104"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="151"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="143" t="e">
+        <f aca="false">G18/C18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G18" s="144"/>
       <c r="H18" s="105" t="n">
-        <f aca="false">H17</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="94" t="n">
-        <f aca="false">(H18/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="106"/>
-      <c r="K18" s="107"/>
-      <c r="L18" s="108"/>
+        <f aca="false">(G18/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="120"/>
+      <c r="J18" s="121"/>
+      <c r="K18" s="122"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="147" t="e">
+        <f aca="false">N18/J18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N18" s="123"/>
+      <c r="O18" s="124" t="n">
+        <f aca="false">(N18/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="125"/>
+      <c r="Q18" s="126"/>
+      <c r="R18" s="127"/>
+      <c r="S18" s="127"/>
+      <c r="T18" s="150" t="e">
+        <f aca="false">U18/Q18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U18" s="128"/>
+      <c r="V18" s="115" t="n">
+        <f aca="false">(U18/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="70"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
-      <c r="G19" s="104"/>
+      <c r="A19" s="72"/>
+      <c r="B19" s="151"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="143" t="e">
+        <f aca="false">G19/C19</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G19" s="144"/>
       <c r="H19" s="105" t="n">
-        <f aca="false">H18</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="94" t="n">
-        <f aca="false">(H19/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="106"/>
-      <c r="K19" s="107"/>
-      <c r="L19" s="108"/>
+        <f aca="false">(G19/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="120"/>
+      <c r="J19" s="121"/>
+      <c r="K19" s="122"/>
+      <c r="L19" s="122"/>
+      <c r="M19" s="147" t="e">
+        <f aca="false">N19/J19</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N19" s="123"/>
+      <c r="O19" s="124" t="n">
+        <f aca="false">(N19/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="125"/>
+      <c r="Q19" s="126"/>
+      <c r="R19" s="127"/>
+      <c r="S19" s="127"/>
+      <c r="T19" s="150" t="e">
+        <f aca="false">U19/Q19</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U19" s="128"/>
+      <c r="V19" s="115" t="n">
+        <f aca="false">(U19/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="70"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="G20" s="104"/>
+      <c r="A20" s="72"/>
+      <c r="B20" s="151"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="143" t="e">
+        <f aca="false">G20/C20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G20" s="144"/>
       <c r="H20" s="105" t="n">
-        <f aca="false">H19</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="94" t="n">
-        <f aca="false">(H20/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="106"/>
-      <c r="K20" s="107"/>
-      <c r="L20" s="108"/>
+        <f aca="false">(G20/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="120"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="122"/>
+      <c r="L20" s="122"/>
+      <c r="M20" s="147" t="e">
+        <f aca="false">N20/J20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N20" s="123"/>
+      <c r="O20" s="124" t="n">
+        <f aca="false">(N20/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="125"/>
+      <c r="Q20" s="126"/>
+      <c r="R20" s="127"/>
+      <c r="S20" s="127"/>
+      <c r="T20" s="150" t="e">
+        <f aca="false">U20/Q20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U20" s="128"/>
+      <c r="V20" s="115" t="n">
+        <f aca="false">(U20/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="70"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="70"/>
-      <c r="G21" s="104"/>
+      <c r="A21" s="72"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="143" t="e">
+        <f aca="false">G21/C21</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G21" s="144"/>
       <c r="H21" s="105" t="n">
-        <f aca="false">H20</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="94" t="n">
-        <f aca="false">(H21/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="106"/>
-      <c r="K21" s="107"/>
-      <c r="L21" s="108"/>
+        <f aca="false">(G21/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="120"/>
+      <c r="J21" s="121"/>
+      <c r="K21" s="122"/>
+      <c r="L21" s="122"/>
+      <c r="M21" s="147" t="e">
+        <f aca="false">N21/J21</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N21" s="123"/>
+      <c r="O21" s="124" t="n">
+        <f aca="false">(N21/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P21" s="125"/>
+      <c r="Q21" s="126"/>
+      <c r="R21" s="127"/>
+      <c r="S21" s="127"/>
+      <c r="T21" s="150" t="e">
+        <f aca="false">U21/Q21</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U21" s="128"/>
+      <c r="V21" s="115" t="n">
+        <f aca="false">(U21/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="70"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
-      <c r="G22" s="104"/>
+      <c r="A22" s="72"/>
+      <c r="B22" s="151"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="143" t="e">
+        <f aca="false">G22/C22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G22" s="144"/>
       <c r="H22" s="105" t="n">
-        <f aca="false">H21</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="94" t="n">
-        <f aca="false">(H22/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="106"/>
-      <c r="K22" s="107"/>
-      <c r="L22" s="108"/>
+        <f aca="false">(G22/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="120"/>
+      <c r="J22" s="121"/>
+      <c r="K22" s="122"/>
+      <c r="L22" s="122"/>
+      <c r="M22" s="147" t="e">
+        <f aca="false">N22/J22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N22" s="123"/>
+      <c r="O22" s="124" t="n">
+        <f aca="false">(N22/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P22" s="125"/>
+      <c r="Q22" s="126"/>
+      <c r="R22" s="127"/>
+      <c r="S22" s="127"/>
+      <c r="T22" s="150" t="e">
+        <f aca="false">U22/Q22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U22" s="128"/>
+      <c r="V22" s="115" t="n">
+        <f aca="false">(U22/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="70"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
-      <c r="G23" s="104"/>
+      <c r="A23" s="72"/>
+      <c r="B23" s="151"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="143" t="e">
+        <f aca="false">G23/C23</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G23" s="144"/>
       <c r="H23" s="105" t="n">
-        <f aca="false">H22</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="94" t="n">
-        <f aca="false">(H23/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="106"/>
-      <c r="K23" s="107"/>
-      <c r="L23" s="108"/>
+        <f aca="false">(G23/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="120"/>
+      <c r="J23" s="121"/>
+      <c r="K23" s="122"/>
+      <c r="L23" s="122"/>
+      <c r="M23" s="147" t="e">
+        <f aca="false">N23/J23</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N23" s="123"/>
+      <c r="O23" s="124" t="n">
+        <f aca="false">(N23/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P23" s="125"/>
+      <c r="Q23" s="126"/>
+      <c r="R23" s="127"/>
+      <c r="S23" s="127"/>
+      <c r="T23" s="150" t="e">
+        <f aca="false">U23/Q23</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U23" s="128"/>
+      <c r="V23" s="115" t="n">
+        <f aca="false">(U23/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="70"/>
-      <c r="C24" s="70"/>
-      <c r="D24" s="70"/>
-      <c r="G24" s="104"/>
+      <c r="A24" s="72"/>
+      <c r="B24" s="151"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="143" t="e">
+        <f aca="false">G24/C24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G24" s="144"/>
       <c r="H24" s="105" t="n">
-        <f aca="false">H23</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="94" t="n">
-        <f aca="false">(H24/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="106"/>
-      <c r="K24" s="107"/>
-      <c r="L24" s="108"/>
+        <f aca="false">(G24/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="120"/>
+      <c r="J24" s="121"/>
+      <c r="K24" s="122"/>
+      <c r="L24" s="122"/>
+      <c r="M24" s="147" t="e">
+        <f aca="false">N24/J24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N24" s="123"/>
+      <c r="O24" s="124" t="n">
+        <f aca="false">(N24/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="125"/>
+      <c r="Q24" s="126"/>
+      <c r="R24" s="127"/>
+      <c r="S24" s="127"/>
+      <c r="T24" s="150" t="e">
+        <f aca="false">U24/Q24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U24" s="128"/>
+      <c r="V24" s="115" t="n">
+        <f aca="false">(U24/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="70"/>
-      <c r="C25" s="70"/>
-      <c r="D25" s="70"/>
-      <c r="G25" s="104"/>
+      <c r="A25" s="72"/>
+      <c r="B25" s="151"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="143" t="e">
+        <f aca="false">G25/C25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G25" s="144"/>
       <c r="H25" s="105" t="n">
-        <f aca="false">H24</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="94" t="n">
-        <f aca="false">(H25/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="106"/>
-      <c r="K25" s="107"/>
-      <c r="L25" s="108"/>
+        <f aca="false">(G25/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="120"/>
+      <c r="J25" s="121"/>
+      <c r="K25" s="122"/>
+      <c r="L25" s="122"/>
+      <c r="M25" s="147" t="e">
+        <f aca="false">N25/J25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N25" s="123"/>
+      <c r="O25" s="124" t="n">
+        <f aca="false">(N25/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="125"/>
+      <c r="Q25" s="126"/>
+      <c r="R25" s="127"/>
+      <c r="S25" s="127"/>
+      <c r="T25" s="150" t="e">
+        <f aca="false">U25/Q25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U25" s="128"/>
+      <c r="V25" s="115" t="n">
+        <f aca="false">(U25/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="70"/>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
-      <c r="G26" s="104"/>
+      <c r="A26" s="72"/>
+      <c r="B26" s="151"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="118"/>
+      <c r="F26" s="143" t="e">
+        <f aca="false">G26/C26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G26" s="144"/>
       <c r="H26" s="105" t="n">
-        <f aca="false">H25</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="94" t="n">
-        <f aca="false">(H26/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="106"/>
-      <c r="K26" s="107"/>
-      <c r="L26" s="108"/>
+        <f aca="false">(G26/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="120"/>
+      <c r="J26" s="121"/>
+      <c r="K26" s="122"/>
+      <c r="L26" s="122"/>
+      <c r="M26" s="147" t="e">
+        <f aca="false">N26/J26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N26" s="123"/>
+      <c r="O26" s="124" t="n">
+        <f aca="false">(N26/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P26" s="125"/>
+      <c r="Q26" s="126"/>
+      <c r="R26" s="127"/>
+      <c r="S26" s="127"/>
+      <c r="T26" s="150" t="e">
+        <f aca="false">U26/Q26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U26" s="128"/>
+      <c r="V26" s="115" t="n">
+        <f aca="false">(U26/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="70"/>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
-      <c r="G27" s="104"/>
+      <c r="A27" s="72"/>
+      <c r="B27" s="151"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="118"/>
+      <c r="E27" s="118"/>
+      <c r="F27" s="143" t="e">
+        <f aca="false">G27/C27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G27" s="144"/>
       <c r="H27" s="105" t="n">
-        <f aca="false">H26</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="94" t="n">
-        <f aca="false">(H27/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="106"/>
-      <c r="K27" s="107"/>
-      <c r="L27" s="108"/>
+        <f aca="false">(G27/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="120"/>
+      <c r="J27" s="121"/>
+      <c r="K27" s="122"/>
+      <c r="L27" s="122"/>
+      <c r="M27" s="147" t="e">
+        <f aca="false">N27/J27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N27" s="123"/>
+      <c r="O27" s="124" t="n">
+        <f aca="false">(N27/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P27" s="125"/>
+      <c r="Q27" s="126"/>
+      <c r="R27" s="127"/>
+      <c r="S27" s="127"/>
+      <c r="T27" s="150" t="e">
+        <f aca="false">U27/Q27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U27" s="128"/>
+      <c r="V27" s="115" t="n">
+        <f aca="false">(U27/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="70"/>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
-      <c r="G28" s="104"/>
+      <c r="A28" s="72"/>
+      <c r="B28" s="151"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="118"/>
+      <c r="E28" s="118"/>
+      <c r="F28" s="143" t="e">
+        <f aca="false">G28/C28</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G28" s="144"/>
       <c r="H28" s="105" t="n">
-        <f aca="false">H27</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="94" t="n">
-        <f aca="false">(H28/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="106"/>
-      <c r="K28" s="107"/>
-      <c r="L28" s="108"/>
+        <f aca="false">(G28/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="120"/>
+      <c r="J28" s="121"/>
+      <c r="K28" s="122"/>
+      <c r="L28" s="122"/>
+      <c r="M28" s="147" t="e">
+        <f aca="false">N28/J28</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N28" s="123"/>
+      <c r="O28" s="124" t="n">
+        <f aca="false">(N28/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P28" s="125"/>
+      <c r="Q28" s="126"/>
+      <c r="R28" s="127"/>
+      <c r="S28" s="127"/>
+      <c r="T28" s="150" t="e">
+        <f aca="false">U28/Q28</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U28" s="128"/>
+      <c r="V28" s="115" t="n">
+        <f aca="false">(U28/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="70"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="70"/>
-      <c r="G29" s="104"/>
+      <c r="A29" s="72"/>
+      <c r="B29" s="151"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="118"/>
+      <c r="E29" s="118"/>
+      <c r="F29" s="143" t="e">
+        <f aca="false">G29/C29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G29" s="144"/>
       <c r="H29" s="105" t="n">
-        <f aca="false">H28</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="94" t="n">
-        <f aca="false">(H29/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="106"/>
-      <c r="K29" s="107"/>
-      <c r="L29" s="108"/>
+        <f aca="false">(G29/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="120"/>
+      <c r="J29" s="121"/>
+      <c r="K29" s="122"/>
+      <c r="L29" s="122"/>
+      <c r="M29" s="147" t="e">
+        <f aca="false">N29/J29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N29" s="123"/>
+      <c r="O29" s="124" t="n">
+        <f aca="false">(N29/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P29" s="125"/>
+      <c r="Q29" s="126"/>
+      <c r="R29" s="127"/>
+      <c r="S29" s="127"/>
+      <c r="T29" s="150" t="e">
+        <f aca="false">U29/Q29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U29" s="128"/>
+      <c r="V29" s="115" t="n">
+        <f aca="false">(U29/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="70"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="G30" s="104"/>
+      <c r="A30" s="72"/>
+      <c r="B30" s="151"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="143" t="e">
+        <f aca="false">G30/C30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G30" s="144"/>
       <c r="H30" s="105" t="n">
-        <f aca="false">H29</f>
-        <v>0</v>
-      </c>
-      <c r="I30" s="94" t="n">
-        <f aca="false">(H30/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="106"/>
-      <c r="K30" s="107"/>
-      <c r="L30" s="108"/>
+        <f aca="false">(G30/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="120"/>
+      <c r="J30" s="121"/>
+      <c r="K30" s="122"/>
+      <c r="L30" s="122"/>
+      <c r="M30" s="147" t="e">
+        <f aca="false">N30/J30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N30" s="123"/>
+      <c r="O30" s="124" t="n">
+        <f aca="false">(N30/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P30" s="125"/>
+      <c r="Q30" s="126"/>
+      <c r="R30" s="127"/>
+      <c r="S30" s="127"/>
+      <c r="T30" s="150" t="e">
+        <f aca="false">U30/Q30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U30" s="128"/>
+      <c r="V30" s="115" t="n">
+        <f aca="false">(U30/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="70"/>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
-      <c r="G31" s="104"/>
+      <c r="A31" s="72"/>
+      <c r="B31" s="151"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="118"/>
+      <c r="E31" s="118"/>
+      <c r="F31" s="143" t="e">
+        <f aca="false">G31/C31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G31" s="144"/>
       <c r="H31" s="105" t="n">
-        <f aca="false">H30</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="94" t="n">
-        <f aca="false">(H31/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J31" s="106"/>
-      <c r="K31" s="107"/>
-      <c r="L31" s="108"/>
+        <f aca="false">(G31/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="120"/>
+      <c r="J31" s="121"/>
+      <c r="K31" s="122"/>
+      <c r="L31" s="122"/>
+      <c r="M31" s="147" t="e">
+        <f aca="false">N31/J31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N31" s="123"/>
+      <c r="O31" s="124" t="n">
+        <f aca="false">(N31/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="125"/>
+      <c r="Q31" s="126"/>
+      <c r="R31" s="127"/>
+      <c r="S31" s="127"/>
+      <c r="T31" s="150" t="e">
+        <f aca="false">U31/Q31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U31" s="128"/>
+      <c r="V31" s="115" t="n">
+        <f aca="false">(U31/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="70"/>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
-      <c r="G32" s="104"/>
+      <c r="A32" s="72"/>
+      <c r="B32" s="151"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="143" t="e">
+        <f aca="false">G32/C32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G32" s="144"/>
       <c r="H32" s="105" t="n">
-        <f aca="false">H31</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="94" t="n">
-        <f aca="false">(H32/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="106"/>
-      <c r="K32" s="107"/>
-      <c r="L32" s="108"/>
+        <f aca="false">(G32/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="120"/>
+      <c r="J32" s="121"/>
+      <c r="K32" s="122"/>
+      <c r="L32" s="122"/>
+      <c r="M32" s="147" t="e">
+        <f aca="false">N32/J32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N32" s="123"/>
+      <c r="O32" s="124" t="n">
+        <f aca="false">(N32/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P32" s="125"/>
+      <c r="Q32" s="126"/>
+      <c r="R32" s="127"/>
+      <c r="S32" s="127"/>
+      <c r="T32" s="150" t="e">
+        <f aca="false">U32/Q32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U32" s="128"/>
+      <c r="V32" s="115" t="n">
+        <f aca="false">(U32/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="70"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="G33" s="104"/>
+      <c r="A33" s="72"/>
+      <c r="B33" s="151"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="118"/>
+      <c r="E33" s="118"/>
+      <c r="F33" s="143" t="e">
+        <f aca="false">G33/C33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G33" s="144"/>
       <c r="H33" s="105" t="n">
-        <f aca="false">H32</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="94" t="n">
-        <f aca="false">(H33/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="106"/>
-      <c r="K33" s="107"/>
-      <c r="L33" s="108"/>
+        <f aca="false">(G33/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="120"/>
+      <c r="J33" s="121"/>
+      <c r="K33" s="122"/>
+      <c r="L33" s="122"/>
+      <c r="M33" s="147" t="e">
+        <f aca="false">N33/J33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N33" s="123"/>
+      <c r="O33" s="124" t="n">
+        <f aca="false">(N33/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P33" s="125"/>
+      <c r="Q33" s="126"/>
+      <c r="R33" s="127"/>
+      <c r="S33" s="127"/>
+      <c r="T33" s="150" t="e">
+        <f aca="false">U33/Q33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U33" s="128"/>
+      <c r="V33" s="115" t="n">
+        <f aca="false">(U33/0.51)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="115"/>
-      <c r="C34" s="115"/>
-      <c r="D34" s="115"/>
-      <c r="G34" s="104"/>
+      <c r="A34" s="72"/>
+      <c r="B34" s="152"/>
+      <c r="C34" s="153"/>
+      <c r="D34" s="154"/>
+      <c r="E34" s="154"/>
+      <c r="F34" s="143" t="e">
+        <f aca="false">G34/C34</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G34" s="155"/>
       <c r="H34" s="105" t="n">
-        <f aca="false">H33</f>
-        <v>0</v>
-      </c>
-      <c r="I34" s="94" t="n">
-        <f aca="false">(H34/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="106"/>
-      <c r="K34" s="107"/>
-      <c r="L34" s="108"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="115"/>
-      <c r="C35" s="115"/>
-      <c r="D35" s="115"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="105" t="n">
-        <f aca="false">H34</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="94" t="n">
-        <f aca="false">(H35/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="106"/>
-      <c r="K35" s="107"/>
-      <c r="L35" s="108"/>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G36" s="104"/>
-      <c r="H36" s="105" t="n">
-        <f aca="false">H35</f>
-        <v>0</v>
-      </c>
-      <c r="I36" s="94" t="n">
-        <f aca="false">(H36/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="106"/>
-      <c r="K36" s="107"/>
-      <c r="L36" s="108"/>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G37" s="104"/>
-      <c r="H37" s="105" t="n">
-        <f aca="false">H36</f>
-        <v>0</v>
-      </c>
-      <c r="I37" s="94" t="n">
-        <f aca="false">(H37/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="106"/>
-      <c r="K37" s="107"/>
-      <c r="L37" s="108"/>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="104"/>
-      <c r="H38" s="105" t="n">
-        <f aca="false">H37</f>
-        <v>0</v>
-      </c>
-      <c r="I38" s="94" t="n">
-        <f aca="false">(H38/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="106"/>
-      <c r="K38" s="107"/>
-      <c r="L38" s="108"/>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G39" s="104"/>
-      <c r="H39" s="105" t="n">
-        <f aca="false">H38</f>
-        <v>0</v>
-      </c>
-      <c r="I39" s="94" t="n">
-        <f aca="false">(H39/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="106"/>
-      <c r="K39" s="107"/>
-      <c r="L39" s="108"/>
-    </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G40" s="104"/>
-      <c r="H40" s="105" t="n">
-        <f aca="false">H39</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="94" t="n">
-        <f aca="false">(H40/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="106"/>
-      <c r="K40" s="107"/>
-      <c r="L40" s="108"/>
-    </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G41" s="104"/>
-      <c r="H41" s="105" t="n">
-        <f aca="false">H40</f>
-        <v>0</v>
-      </c>
-      <c r="I41" s="94" t="n">
-        <f aca="false">(H41/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J41" s="106"/>
-      <c r="K41" s="107"/>
-      <c r="L41" s="108"/>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G42" s="104"/>
-      <c r="H42" s="105" t="n">
-        <f aca="false">H41</f>
-        <v>0</v>
-      </c>
-      <c r="I42" s="94" t="n">
-        <f aca="false">(H42/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J42" s="106"/>
-      <c r="K42" s="107"/>
-      <c r="L42" s="108"/>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G43" s="104"/>
-      <c r="H43" s="105" t="n">
-        <f aca="false">H42</f>
-        <v>0</v>
-      </c>
-      <c r="I43" s="94" t="n">
-        <f aca="false">(H43/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J43" s="106"/>
-      <c r="K43" s="107"/>
-      <c r="L43" s="108"/>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G44" s="116"/>
-      <c r="H44" s="105" t="n">
-        <f aca="false">H43</f>
-        <v>0</v>
-      </c>
-      <c r="I44" s="94" t="n">
-        <f aca="false">(H44/C2)/10</f>
-        <v>0</v>
-      </c>
-      <c r="J44" s="117"/>
-      <c r="K44" s="118"/>
-      <c r="L44" s="119"/>
-    </row>
+        <f aca="false">(G34/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="156"/>
+      <c r="J34" s="157"/>
+      <c r="K34" s="158"/>
+      <c r="L34" s="158"/>
+      <c r="M34" s="147" t="e">
+        <f aca="false">N34/J34</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N34" s="159"/>
+      <c r="O34" s="124" t="n">
+        <f aca="false">(N34/0.7)/10</f>
+        <v>0</v>
+      </c>
+      <c r="P34" s="160"/>
+      <c r="Q34" s="161"/>
+      <c r="R34" s="162"/>
+      <c r="S34" s="162"/>
+      <c r="T34" s="150" t="e">
+        <f aca="false">U34/Q34</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U34" s="163"/>
+      <c r="V34" s="115" t="n">
+        <f aca="false">(U34/0.51)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:L13"/>
+  <mergeCells count="24">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="P2:V2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="U3:V3"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -5744,416 +8151,1002 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFCCCCCC"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:J34"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:O34"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.87"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="72"/>
+      <c r="B1" s="74" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="75" t="s">
+        <v>129</v>
+      </c>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+    </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="77" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="78" t="s">
-        <v>103</v>
-      </c>
+      <c r="A2" s="77" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
       <c r="F2" s="78"/>
       <c r="G2" s="78"/>
-      <c r="H2" s="79" t="s">
-        <v>104</v>
-      </c>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="80" t="s">
+      <c r="H2" s="78"/>
+      <c r="I2" s="166" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
+      <c r="L2" s="166"/>
+      <c r="M2" s="166"/>
+      <c r="N2" s="166"/>
+      <c r="O2" s="166"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="72"/>
+      <c r="B3" s="86" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="86" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="87" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="88" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" s="88"/>
+      <c r="I3" s="89" t="s">
+        <v>110</v>
+      </c>
+      <c r="J3" s="89" t="s">
+        <v>111</v>
+      </c>
+      <c r="K3" s="90" t="s">
+        <v>112</v>
+      </c>
+      <c r="L3" s="89" t="s">
+        <v>113</v>
+      </c>
+      <c r="M3" s="89" t="s">
+        <v>114</v>
+      </c>
+      <c r="N3" s="91" t="s">
+        <v>115</v>
+      </c>
+      <c r="O3" s="91"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="95" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="H4" s="96" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="81"/>
-      <c r="E3" s="82" t="s">
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="97" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="83" t="s">
+      <c r="O4" s="98" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="83"/>
-      <c r="H3" s="84" t="s">
-        <v>116</v>
-      </c>
-      <c r="I3" s="85" t="s">
-        <v>117</v>
-      </c>
-      <c r="J3" s="85"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="80"/>
-      <c r="C4" s="86" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="101" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C5" s="102"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="105" t="n">
+        <f aca="false">(G5/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="106"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="108"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="109"/>
+      <c r="O5" s="110" t="n">
+        <f aca="false">(N5/0.6)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="116"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="105" t="n">
+        <f aca="false">(G6/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="120"/>
+      <c r="J6" s="121"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="122"/>
+      <c r="N6" s="123"/>
+      <c r="O6" s="110" t="n">
+        <f aca="false">(N6/0.6)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="72"/>
+      <c r="B7" s="129" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="87" t="s">
-        <v>119</v>
-      </c>
-      <c r="E4" s="82"/>
-      <c r="F4" s="88" t="s">
-        <v>118</v>
-      </c>
-      <c r="G4" s="89" t="s">
-        <v>119</v>
-      </c>
-      <c r="H4" s="84"/>
-      <c r="I4" s="90" t="s">
-        <v>118</v>
-      </c>
-      <c r="J4" s="91" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="123"/>
-      <c r="C5" s="124"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="125"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="129"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="130"/>
-      <c r="C6" s="131"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="132"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="134"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="136"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="130"/>
-      <c r="C7" s="131"/>
+      <c r="C7" s="130"/>
       <c r="D7" s="131"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="133"/>
-      <c r="H7" s="134"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="136"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="132" t="n">
+        <f aca="false">SUM(G5:G6)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="133" t="n">
+        <f aca="false">SUM(H5:H6)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="134"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="136"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="136"/>
+      <c r="N7" s="134" t="n">
+        <f aca="false">SUM(N5:N6)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="168" t="n">
+        <f aca="false">SUM(O5:O6)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="130"/>
-      <c r="C8" s="131"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="133"/>
-      <c r="G8" s="133"/>
-      <c r="H8" s="134"/>
-      <c r="I8" s="135"/>
-      <c r="J8" s="136"/>
+      <c r="A8" s="72"/>
+      <c r="B8" s="141"/>
+      <c r="C8" s="142"/>
+      <c r="D8" s="143"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="143" t="e">
+        <f aca="false">G8/C8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G8" s="144"/>
+      <c r="H8" s="105" t="n">
+        <f aca="false">(G8/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="145"/>
+      <c r="J8" s="146"/>
+      <c r="K8" s="167"/>
+      <c r="L8" s="147"/>
+      <c r="M8" s="147" t="e">
+        <f aca="false">N8/J8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" s="123"/>
+      <c r="O8" s="110" t="n">
+        <f aca="false">(N8/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="130"/>
-      <c r="C9" s="131"/>
-      <c r="D9" s="131"/>
-      <c r="E9" s="132"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="134"/>
-      <c r="I9" s="135"/>
-      <c r="J9" s="136"/>
+      <c r="A9" s="72"/>
+      <c r="B9" s="151"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="143" t="e">
+        <f aca="false">G9/C9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G9" s="144"/>
+      <c r="H9" s="105" t="n">
+        <f aca="false">(G9/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="120"/>
+      <c r="J9" s="121"/>
+      <c r="K9" s="122"/>
+      <c r="L9" s="122"/>
+      <c r="M9" s="147" t="e">
+        <f aca="false">N9/J9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N9" s="123"/>
+      <c r="O9" s="110" t="n">
+        <f aca="false">(N9/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="130"/>
-      <c r="C10" s="131"/>
-      <c r="D10" s="131"/>
-      <c r="E10" s="132"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="133"/>
-      <c r="H10" s="134"/>
-      <c r="I10" s="135"/>
-      <c r="J10" s="136"/>
+      <c r="A10" s="72"/>
+      <c r="B10" s="151"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
+      <c r="F10" s="143" t="e">
+        <f aca="false">G10/C10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G10" s="144"/>
+      <c r="H10" s="105" t="n">
+        <f aca="false">(G10/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="120"/>
+      <c r="J10" s="121"/>
+      <c r="K10" s="122"/>
+      <c r="L10" s="122"/>
+      <c r="M10" s="147" t="e">
+        <f aca="false">N10/J10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N10" s="123"/>
+      <c r="O10" s="110" t="n">
+        <f aca="false">(N10/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="130"/>
-      <c r="C11" s="131"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="133"/>
-      <c r="H11" s="134"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="136"/>
+      <c r="A11" s="72"/>
+      <c r="B11" s="151"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118"/>
+      <c r="F11" s="143" t="e">
+        <f aca="false">G11/C11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G11" s="144"/>
+      <c r="H11" s="105" t="n">
+        <f aca="false">(G11/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="120"/>
+      <c r="J11" s="121"/>
+      <c r="K11" s="122"/>
+      <c r="L11" s="122"/>
+      <c r="M11" s="147" t="e">
+        <f aca="false">N11/J11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N11" s="123"/>
+      <c r="O11" s="110" t="n">
+        <f aca="false">(N11/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="130"/>
-      <c r="C12" s="131"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="132"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="133"/>
-      <c r="H12" s="134"/>
-      <c r="I12" s="135"/>
-      <c r="J12" s="136"/>
+      <c r="A12" s="72"/>
+      <c r="B12" s="151"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="143" t="e">
+        <f aca="false">G12/C12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G12" s="144"/>
+      <c r="H12" s="105" t="n">
+        <f aca="false">(G12/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="120"/>
+      <c r="J12" s="121"/>
+      <c r="K12" s="122"/>
+      <c r="L12" s="122"/>
+      <c r="M12" s="147" t="e">
+        <f aca="false">N12/J12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N12" s="123"/>
+      <c r="O12" s="110" t="n">
+        <f aca="false">(N12/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="130"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="133"/>
-      <c r="H13" s="134"/>
-      <c r="I13" s="135"/>
-      <c r="J13" s="136"/>
+      <c r="A13" s="72"/>
+      <c r="B13" s="151"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="143" t="e">
+        <f aca="false">G13/C13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G13" s="144"/>
+      <c r="H13" s="105" t="n">
+        <f aca="false">(G13/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="120"/>
+      <c r="J13" s="121"/>
+      <c r="K13" s="122"/>
+      <c r="L13" s="122"/>
+      <c r="M13" s="147" t="e">
+        <f aca="false">N13/J13</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N13" s="123"/>
+      <c r="O13" s="110" t="n">
+        <f aca="false">(N13/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="130"/>
-      <c r="C14" s="131"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="132"/>
-      <c r="F14" s="133"/>
-      <c r="G14" s="133"/>
-      <c r="H14" s="134"/>
-      <c r="I14" s="135"/>
-      <c r="J14" s="136"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="130"/>
-      <c r="C15" s="131"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="134"/>
-      <c r="I15" s="135"/>
-      <c r="J15" s="136"/>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="130"/>
-      <c r="C16" s="131"/>
-      <c r="D16" s="131"/>
-      <c r="E16" s="132"/>
-      <c r="F16" s="133"/>
-      <c r="G16" s="133"/>
-      <c r="H16" s="134"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="136"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="151"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="143" t="e">
+        <f aca="false">G14/C14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G14" s="144"/>
+      <c r="H14" s="105" t="n">
+        <f aca="false">(G14/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="120"/>
+      <c r="J14" s="121"/>
+      <c r="K14" s="122"/>
+      <c r="L14" s="122"/>
+      <c r="M14" s="147" t="e">
+        <f aca="false">N14/J14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N14" s="123"/>
+      <c r="O14" s="110" t="n">
+        <f aca="false">(N14/0.6)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="72"/>
+      <c r="B15" s="151"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="143" t="e">
+        <f aca="false">G15/C15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G15" s="144"/>
+      <c r="H15" s="105" t="n">
+        <f aca="false">(G15/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="120"/>
+      <c r="J15" s="121"/>
+      <c r="K15" s="122"/>
+      <c r="L15" s="122"/>
+      <c r="M15" s="147" t="e">
+        <f aca="false">N15/J15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N15" s="123"/>
+      <c r="O15" s="110" t="n">
+        <f aca="false">(N15/0.6)/10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="72"/>
+      <c r="B16" s="151"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="143" t="e">
+        <f aca="false">G16/C16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G16" s="144"/>
+      <c r="H16" s="105" t="n">
+        <f aca="false">(G16/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="120"/>
+      <c r="J16" s="121"/>
+      <c r="K16" s="122"/>
+      <c r="L16" s="122"/>
+      <c r="M16" s="147" t="e">
+        <f aca="false">N16/J16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N16" s="123"/>
+      <c r="O16" s="110" t="n">
+        <f aca="false">(N16/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="130"/>
-      <c r="C17" s="131"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="132"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="133"/>
-      <c r="H17" s="134"/>
-      <c r="I17" s="135"/>
-      <c r="J17" s="136"/>
+      <c r="A17" s="72"/>
+      <c r="B17" s="151"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="143" t="e">
+        <f aca="false">G17/C17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G17" s="144"/>
+      <c r="H17" s="105" t="n">
+        <f aca="false">(G17/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="120"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="122"/>
+      <c r="L17" s="122"/>
+      <c r="M17" s="147" t="e">
+        <f aca="false">N17/J17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N17" s="123"/>
+      <c r="O17" s="110" t="n">
+        <f aca="false">(N17/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="130"/>
-      <c r="C18" s="131"/>
-      <c r="D18" s="131"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="133"/>
-      <c r="G18" s="133"/>
-      <c r="H18" s="134"/>
-      <c r="I18" s="135"/>
-      <c r="J18" s="136"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="151"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="143" t="e">
+        <f aca="false">G18/C18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G18" s="144"/>
+      <c r="H18" s="105" t="n">
+        <f aca="false">(G18/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="120"/>
+      <c r="J18" s="121"/>
+      <c r="K18" s="122"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="147" t="e">
+        <f aca="false">N18/J18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N18" s="123"/>
+      <c r="O18" s="110" t="n">
+        <f aca="false">(N18/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="130"/>
-      <c r="C19" s="131"/>
-      <c r="D19" s="131"/>
-      <c r="E19" s="132"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="134"/>
-      <c r="I19" s="135"/>
-      <c r="J19" s="136"/>
+      <c r="A19" s="72"/>
+      <c r="B19" s="151"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="143" t="e">
+        <f aca="false">G19/C19</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G19" s="144"/>
+      <c r="H19" s="105" t="n">
+        <f aca="false">(G19/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="120"/>
+      <c r="J19" s="121"/>
+      <c r="K19" s="122"/>
+      <c r="L19" s="122"/>
+      <c r="M19" s="147" t="e">
+        <f aca="false">N19/J19</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N19" s="123"/>
+      <c r="O19" s="110" t="n">
+        <f aca="false">(N19/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="130"/>
-      <c r="C20" s="131"/>
-      <c r="D20" s="131"/>
-      <c r="E20" s="132"/>
-      <c r="F20" s="133"/>
-      <c r="G20" s="133"/>
-      <c r="H20" s="134"/>
-      <c r="I20" s="135"/>
-      <c r="J20" s="136"/>
+      <c r="A20" s="72"/>
+      <c r="B20" s="151"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="143" t="e">
+        <f aca="false">G20/C20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G20" s="144"/>
+      <c r="H20" s="105" t="n">
+        <f aca="false">(G20/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="120"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="122"/>
+      <c r="L20" s="122"/>
+      <c r="M20" s="147" t="e">
+        <f aca="false">N20/J20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N20" s="123"/>
+      <c r="O20" s="110" t="n">
+        <f aca="false">(N20/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="130"/>
-      <c r="C21" s="131"/>
-      <c r="D21" s="131"/>
-      <c r="E21" s="132"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="134"/>
-      <c r="I21" s="135"/>
-      <c r="J21" s="136"/>
+      <c r="A21" s="72"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="143" t="e">
+        <f aca="false">G21/C21</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G21" s="144"/>
+      <c r="H21" s="105" t="n">
+        <f aca="false">(G21/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="120"/>
+      <c r="J21" s="121"/>
+      <c r="K21" s="122"/>
+      <c r="L21" s="122"/>
+      <c r="M21" s="147" t="e">
+        <f aca="false">N21/J21</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N21" s="123"/>
+      <c r="O21" s="110" t="n">
+        <f aca="false">(N21/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="130"/>
-      <c r="C22" s="131"/>
-      <c r="D22" s="131"/>
-      <c r="E22" s="132"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="133"/>
-      <c r="H22" s="134"/>
-      <c r="I22" s="135"/>
-      <c r="J22" s="136"/>
+      <c r="A22" s="72"/>
+      <c r="B22" s="151"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="143" t="e">
+        <f aca="false">G22/C22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G22" s="144"/>
+      <c r="H22" s="105" t="n">
+        <f aca="false">(G22/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="120"/>
+      <c r="J22" s="121"/>
+      <c r="K22" s="122"/>
+      <c r="L22" s="122"/>
+      <c r="M22" s="147" t="e">
+        <f aca="false">N22/J22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N22" s="123"/>
+      <c r="O22" s="110" t="n">
+        <f aca="false">(N22/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="130"/>
-      <c r="C23" s="131"/>
-      <c r="D23" s="131"/>
-      <c r="E23" s="132"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="134"/>
-      <c r="I23" s="135"/>
-      <c r="J23" s="136"/>
+      <c r="A23" s="72"/>
+      <c r="B23" s="151"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="143" t="e">
+        <f aca="false">G23/C23</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G23" s="144"/>
+      <c r="H23" s="105" t="n">
+        <f aca="false">(G23/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="120"/>
+      <c r="J23" s="121"/>
+      <c r="K23" s="122"/>
+      <c r="L23" s="122"/>
+      <c r="M23" s="147" t="e">
+        <f aca="false">N23/J23</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N23" s="123"/>
+      <c r="O23" s="110" t="n">
+        <f aca="false">(N23/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="130"/>
-      <c r="C24" s="131"/>
-      <c r="D24" s="131"/>
-      <c r="E24" s="132"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="134"/>
-      <c r="I24" s="135"/>
-      <c r="J24" s="136"/>
+      <c r="A24" s="72"/>
+      <c r="B24" s="151"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="143" t="e">
+        <f aca="false">G24/C24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G24" s="144"/>
+      <c r="H24" s="105" t="n">
+        <f aca="false">(G24/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="120"/>
+      <c r="J24" s="121"/>
+      <c r="K24" s="122"/>
+      <c r="L24" s="122"/>
+      <c r="M24" s="147" t="e">
+        <f aca="false">N24/J24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N24" s="123"/>
+      <c r="O24" s="110" t="n">
+        <f aca="false">(N24/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="130"/>
-      <c r="C25" s="131"/>
-      <c r="D25" s="131"/>
-      <c r="E25" s="132"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="133"/>
-      <c r="H25" s="134"/>
-      <c r="I25" s="135"/>
-      <c r="J25" s="136"/>
+      <c r="A25" s="72"/>
+      <c r="B25" s="151"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="143" t="e">
+        <f aca="false">G25/C25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G25" s="144"/>
+      <c r="H25" s="105" t="n">
+        <f aca="false">(G25/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="120"/>
+      <c r="J25" s="121"/>
+      <c r="K25" s="122"/>
+      <c r="L25" s="122"/>
+      <c r="M25" s="147" t="e">
+        <f aca="false">N25/J25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N25" s="123"/>
+      <c r="O25" s="110" t="n">
+        <f aca="false">(N25/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="130"/>
-      <c r="C26" s="131"/>
-      <c r="D26" s="131"/>
-      <c r="E26" s="132"/>
-      <c r="F26" s="133"/>
-      <c r="G26" s="133"/>
-      <c r="H26" s="134"/>
-      <c r="I26" s="135"/>
-      <c r="J26" s="136"/>
+      <c r="A26" s="72"/>
+      <c r="B26" s="151"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="118"/>
+      <c r="F26" s="143" t="e">
+        <f aca="false">G26/C26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G26" s="144"/>
+      <c r="H26" s="105" t="n">
+        <f aca="false">(G26/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="120"/>
+      <c r="J26" s="121"/>
+      <c r="K26" s="122"/>
+      <c r="L26" s="122"/>
+      <c r="M26" s="147" t="e">
+        <f aca="false">N26/J26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N26" s="123"/>
+      <c r="O26" s="110" t="n">
+        <f aca="false">(N26/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="130"/>
-      <c r="C27" s="131"/>
-      <c r="D27" s="131"/>
-      <c r="E27" s="132"/>
-      <c r="F27" s="133"/>
-      <c r="G27" s="133"/>
-      <c r="H27" s="134"/>
-      <c r="I27" s="135"/>
-      <c r="J27" s="136"/>
+      <c r="A27" s="72"/>
+      <c r="B27" s="151"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="118"/>
+      <c r="E27" s="118"/>
+      <c r="F27" s="143" t="e">
+        <f aca="false">G27/C27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G27" s="144"/>
+      <c r="H27" s="105" t="n">
+        <f aca="false">(G27/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="120"/>
+      <c r="J27" s="121"/>
+      <c r="K27" s="122"/>
+      <c r="L27" s="122"/>
+      <c r="M27" s="147" t="e">
+        <f aca="false">N27/J27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N27" s="123"/>
+      <c r="O27" s="110" t="n">
+        <f aca="false">(N27/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="130"/>
-      <c r="C28" s="131"/>
-      <c r="D28" s="131"/>
-      <c r="E28" s="132"/>
-      <c r="F28" s="133"/>
-      <c r="G28" s="133"/>
-      <c r="H28" s="134"/>
-      <c r="I28" s="135"/>
-      <c r="J28" s="136"/>
+      <c r="A28" s="72"/>
+      <c r="B28" s="151"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="118"/>
+      <c r="E28" s="118"/>
+      <c r="F28" s="143" t="e">
+        <f aca="false">G28/C28</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G28" s="144"/>
+      <c r="H28" s="105" t="n">
+        <f aca="false">(G28/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="120"/>
+      <c r="J28" s="121"/>
+      <c r="K28" s="122"/>
+      <c r="L28" s="122"/>
+      <c r="M28" s="147" t="e">
+        <f aca="false">N28/J28</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N28" s="123"/>
+      <c r="O28" s="110" t="n">
+        <f aca="false">(N28/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="130"/>
-      <c r="C29" s="131"/>
-      <c r="D29" s="131"/>
-      <c r="E29" s="132"/>
-      <c r="F29" s="133"/>
-      <c r="G29" s="133"/>
-      <c r="H29" s="134"/>
-      <c r="I29" s="135"/>
-      <c r="J29" s="136"/>
+      <c r="A29" s="72"/>
+      <c r="B29" s="151"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="118"/>
+      <c r="E29" s="118"/>
+      <c r="F29" s="143" t="e">
+        <f aca="false">G29/C29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G29" s="144"/>
+      <c r="H29" s="105" t="n">
+        <f aca="false">(G29/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="120"/>
+      <c r="J29" s="121"/>
+      <c r="K29" s="122"/>
+      <c r="L29" s="122"/>
+      <c r="M29" s="147" t="e">
+        <f aca="false">N29/J29</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N29" s="123"/>
+      <c r="O29" s="110" t="n">
+        <f aca="false">(N29/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="130"/>
-      <c r="C30" s="131"/>
-      <c r="D30" s="131"/>
-      <c r="E30" s="132"/>
-      <c r="F30" s="133"/>
-      <c r="G30" s="133"/>
-      <c r="H30" s="134"/>
-      <c r="I30" s="135"/>
-      <c r="J30" s="136"/>
+      <c r="A30" s="72"/>
+      <c r="B30" s="151"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="143" t="e">
+        <f aca="false">G30/C30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G30" s="144"/>
+      <c r="H30" s="105" t="n">
+        <f aca="false">(G30/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="120"/>
+      <c r="J30" s="121"/>
+      <c r="K30" s="122"/>
+      <c r="L30" s="122"/>
+      <c r="M30" s="147" t="e">
+        <f aca="false">N30/J30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N30" s="123"/>
+      <c r="O30" s="110" t="n">
+        <f aca="false">(N30/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="130"/>
-      <c r="C31" s="131"/>
-      <c r="D31" s="131"/>
-      <c r="E31" s="132"/>
-      <c r="F31" s="133"/>
-      <c r="G31" s="133"/>
-      <c r="H31" s="134"/>
-      <c r="I31" s="135"/>
-      <c r="J31" s="136"/>
+      <c r="A31" s="72"/>
+      <c r="B31" s="151"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="118"/>
+      <c r="E31" s="118"/>
+      <c r="F31" s="143" t="e">
+        <f aca="false">G31/C31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G31" s="144"/>
+      <c r="H31" s="105" t="n">
+        <f aca="false">(G31/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="120"/>
+      <c r="J31" s="121"/>
+      <c r="K31" s="122"/>
+      <c r="L31" s="122"/>
+      <c r="M31" s="147" t="e">
+        <f aca="false">N31/J31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N31" s="123"/>
+      <c r="O31" s="110" t="n">
+        <f aca="false">(N31/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="130"/>
-      <c r="C32" s="131"/>
-      <c r="D32" s="131"/>
-      <c r="E32" s="132"/>
-      <c r="F32" s="133"/>
-      <c r="G32" s="133"/>
-      <c r="H32" s="134"/>
-      <c r="I32" s="135"/>
-      <c r="J32" s="136"/>
+      <c r="A32" s="72"/>
+      <c r="B32" s="151"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="143" t="e">
+        <f aca="false">G32/C32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G32" s="144"/>
+      <c r="H32" s="105" t="n">
+        <f aca="false">(G32/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="120"/>
+      <c r="J32" s="121"/>
+      <c r="K32" s="122"/>
+      <c r="L32" s="122"/>
+      <c r="M32" s="147" t="e">
+        <f aca="false">N32/J32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N32" s="123"/>
+      <c r="O32" s="110" t="n">
+        <f aca="false">(N32/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="130"/>
-      <c r="C33" s="131"/>
-      <c r="D33" s="131"/>
-      <c r="E33" s="132"/>
-      <c r="F33" s="133"/>
-      <c r="G33" s="133"/>
-      <c r="H33" s="134"/>
-      <c r="I33" s="135"/>
-      <c r="J33" s="136"/>
+      <c r="A33" s="72"/>
+      <c r="B33" s="151"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="118"/>
+      <c r="E33" s="118"/>
+      <c r="F33" s="143" t="e">
+        <f aca="false">G33/C33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G33" s="144"/>
+      <c r="H33" s="105" t="n">
+        <f aca="false">(G33/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="120"/>
+      <c r="J33" s="121"/>
+      <c r="K33" s="122"/>
+      <c r="L33" s="122"/>
+      <c r="M33" s="147" t="e">
+        <f aca="false">N33/J33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N33" s="123"/>
+      <c r="O33" s="110" t="n">
+        <f aca="false">(N33/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="137"/>
-      <c r="C34" s="138"/>
-      <c r="D34" s="138"/>
-      <c r="E34" s="139"/>
-      <c r="F34" s="140"/>
-      <c r="G34" s="140"/>
-      <c r="H34" s="141"/>
-      <c r="I34" s="142"/>
-      <c r="J34" s="143"/>
+      <c r="A34" s="72"/>
+      <c r="B34" s="152"/>
+      <c r="C34" s="153"/>
+      <c r="D34" s="154"/>
+      <c r="E34" s="154"/>
+      <c r="F34" s="143" t="e">
+        <f aca="false">G34/C34</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G34" s="155"/>
+      <c r="H34" s="105" t="n">
+        <f aca="false">(G34/0.5)/10</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="156"/>
+      <c r="J34" s="157"/>
+      <c r="K34" s="158"/>
+      <c r="L34" s="158"/>
+      <c r="M34" s="147" t="e">
+        <f aca="false">N34/J34</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N34" s="159"/>
+      <c r="O34" s="110" t="n">
+        <f aca="false">(N34/0.6)/10</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
+  <mergeCells count="16">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="I2:O2"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:O3"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
